--- a/AAII_Financials/Quarterly/XOM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/XOM_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
@@ -656,395 +656,407 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="32" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="33" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42825</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42735</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>81688000</v>
+      </c>
+      <c r="E8" s="3">
         <v>88570000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>80795000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>83644000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>93164000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>106512000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>111265000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>87734000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>81305000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>71892000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>65943000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>57552000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>45738000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>45425000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>32277000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>55134000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>63024000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>63422000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>67491000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>61646000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>68253000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>74187000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>71456000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>65436000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>50832000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>59350000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>56026000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>56474000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>40396000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>56767000</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>56245000</v>
+      </c>
+      <c r="E9" s="3">
         <v>61772000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>56458000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>55439000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>61126000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>71514000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>76299000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>62629000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>56272000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>48464000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>45800000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>40663000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>32041000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>31053000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>20964000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>40380000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>44254000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>44138000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>48464000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>43771000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>46957000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>50873000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>50245000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>44779000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>28979000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>45248000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>43843000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>43267000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>21193000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>41181000</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>25443000</v>
+      </c>
+      <c r="E10" s="3">
         <v>26798000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>24337000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>28205000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>32038000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>34998000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>34966000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>25105000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>25033000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>23428000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>20143000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>16889000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>13697000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>14372000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>11313000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>14754000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>18770000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>19284000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>19027000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>17875000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>21296000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>23314000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>21211000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>20657000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>21853000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>14102000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>12183000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>13207000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>19203000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>15586000</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1077,100 +1089,104 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>139000</v>
+      </c>
+      <c r="E12" s="3">
         <v>338000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>133000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>141000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>348000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>218000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>286000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>173000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>524000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>190000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>176000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>164000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>595000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>188000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>214000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>288000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>357000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>299000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>333000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>280000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>555000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>292000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>332000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>287000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>703000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>284000</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>514000</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>289000</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>340000</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>327000</v>
       </c>
     </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1261,8 +1277,11 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1275,8 +1294,8 @@
       <c r="F14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
+      <c r="G14" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="H14" s="3">
         <v>0</v>
@@ -1285,10 +1304,10 @@
         <v>0</v>
       </c>
       <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3">
         <v>4600000</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>24</v>
@@ -1299,26 +1318,26 @@
       <c r="N14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="O14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="P14" s="3">
         <v>24875000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>62000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>64000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>910000</v>
-      </c>
-      <c r="S14" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="T14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
+      <c r="U14" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="V14" s="3">
         <v>0</v>
@@ -1353,100 +1372,106 @@
       <c r="AF14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>7740000</v>
+      </c>
+      <c r="E15" s="3">
         <v>4415000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>4242000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>4244000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>5064000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>5642000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>4451000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>4283000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>5661000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>4990000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>4952000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>5004000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>5416000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>4921000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>4852000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>4909000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>4923000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>4873000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>4631000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>4571000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>5028000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>4658000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>4589000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>4470000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>5842000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>4880000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>4652000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>4519000</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>8117000</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>4605000</v>
       </c>
     </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1476,192 +1501,199 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>71956000</v>
+      </c>
+      <c r="E17" s="3">
         <v>76159000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>70272000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>69063000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>74720000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>85513000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>89826000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>81528000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>73015000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>63966000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>61181000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>55297000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>72840000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>46292000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>33928000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>56167000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>60527000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>60061000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>64243000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>59155000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>63559000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>67325000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>66842000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>60767000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>48832000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>55406000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>53763000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>52607000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>42224000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>55345000</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>9732000</v>
+      </c>
+      <c r="E18" s="3">
         <v>12411000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>10523000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>14581000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>18444000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>20999000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>21439000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>6206000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>8290000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>7926000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>4762000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>2255000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-27102000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-867000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-1651000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-1033000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>2497000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>3361000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>3248000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>2491000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>4694000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>6862000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>4614000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>4669000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>2000000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>3944000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>2263000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>3867000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-1828000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>1422000</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1694,468 +1726,484 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>1165000</v>
+      </c>
+      <c r="E20" s="3">
         <v>1457000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>1382000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>2381000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>605000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>4632000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>3688000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>2538000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>3660000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>1894000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>1799000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>1595000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>802000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>774000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>328000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>1024000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>4149000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>1627000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>1600000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>1979000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>3642000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>2418000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>2045000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>2775000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>1203000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>1750000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>2051000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>2197000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>2640000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>1910000</v>
       </c>
     </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>18637000</v>
+      </c>
+      <c r="E21" s="3">
         <v>18283000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>16147000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>21206000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>24113000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>31273000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>29578000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>13027000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>17611000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>14810000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>11513000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>8854000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>3991000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>4890000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>3593000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>5810000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>11569000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>9861000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>9479000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>9041000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>13364000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>13938000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>11248000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>11914000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>9045000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>10574000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>8966000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>10583000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>8929000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>7937000</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>272000</v>
+      </c>
+      <c r="E22" s="3">
         <v>169000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>249000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>159000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>207000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>209000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>194000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>188000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>221000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>214000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>254000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>258000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>313000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>279000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>317000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>249000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>232000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>267000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>216000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>181000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>215000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>200000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>147000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>204000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>186000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>111000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>158000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>146000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>195000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>106000</v>
       </c>
     </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>10625000</v>
+      </c>
+      <c r="E23" s="3">
         <v>13699000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>11656000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>16803000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>18842000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>25422000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>24933000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>8556000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>11729000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>9606000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>6307000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>3592000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-26613000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-372000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-1640000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-258000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>6414000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>4721000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>4632000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>4289000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>8121000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>9080000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>6512000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>7240000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>3017000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>5583000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>4156000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>5918000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>617000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>3226000</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>2637000</v>
+      </c>
+      <c r="E24" s="3">
         <v>4353000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>3503000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>4960000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>5817000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>5224000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>6359000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>2806000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>2703000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>2664000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1526000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>796000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-5985000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>337000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-471000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>512000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>1424000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>1474000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>1241000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>1883000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>1936000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>2634000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>2526000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>2457000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>550000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>1498000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>892000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>1828000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-1407000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>337000</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2246,192 +2294,201 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>7988000</v>
+      </c>
+      <c r="E26" s="3">
         <v>9346000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>8153000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>11843000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>13025000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>20198000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>18574000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>5750000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>9026000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>6942000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>4781000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>2796000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-20628000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-709000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-1169000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-770000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>4990000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>3247000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>3391000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>2406000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>6185000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>6446000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>3986000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>4783000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>2467000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>4085000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>3264000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>4090000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>2024000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>2889000</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>7606000</v>
+      </c>
+      <c r="E27" s="3">
         <v>9070000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>7880000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>11430000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>12720000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>19660000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>17850000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>5480000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>8817000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>6750000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>4690000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>2730000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-20095000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-680000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-1080000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-610000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>4950000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>3170000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>3130000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>2350000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>5979000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>6240000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>3950000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>4650000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>2438000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>3970000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>3350000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>4010000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>1680000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>2650000</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -2522,13 +2579,16 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>24</v>
+      <c r="D29" s="3">
+        <v>24000</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>24</v>
@@ -2536,11 +2596,11 @@
       <c r="F29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="G29" s="3">
+      <c r="G29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H29" s="3">
         <v>30000</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="I29" s="3" t="s">
         <v>24</v>
@@ -2548,11 +2608,11 @@
       <c r="J29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="K29" s="3">
+      <c r="K29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L29" s="3">
         <v>53000</v>
-      </c>
-      <c r="L29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="M29" s="3" t="s">
         <v>24</v>
@@ -2560,11 +2620,11 @@
       <c r="N29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="O29" s="3">
+      <c r="O29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="P29" s="3">
         <v>25000</v>
-      </c>
-      <c r="P29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="Q29" s="3" t="s">
         <v>24</v>
@@ -2572,11 +2632,11 @@
       <c r="R29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="S29" s="3">
+      <c r="S29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="T29" s="3">
         <v>740000</v>
-      </c>
-      <c r="T29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="U29" s="3" t="s">
         <v>24</v>
@@ -2584,11 +2644,11 @@
       <c r="V29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="W29" s="3">
+      <c r="W29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="X29" s="3">
         <v>21000</v>
-      </c>
-      <c r="X29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="Y29" s="3" t="s">
         <v>24</v>
@@ -2596,11 +2656,11 @@
       <c r="Z29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AA29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AB29" s="3">
         <v>5942000</v>
-      </c>
-      <c r="AB29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AC29" s="3" t="s">
         <v>24</v>
@@ -2614,8 +2674,11 @@
       <c r="AF29" s="3" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2706,8 +2769,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2798,192 +2864,201 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-1165000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-1457000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-1382000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-2381000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-605000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-4632000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-3688000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-2538000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-3660000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-1894000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-1799000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-1595000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-802000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-774000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-328000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-1024000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-4149000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-1627000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-1600000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-1979000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-3642000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-2418000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-2045000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-2775000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-1203000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-1750000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-2051000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-2197000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-2640000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-1910000</v>
       </c>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>7630000</v>
+      </c>
+      <c r="E33" s="3">
         <v>9070000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>7880000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>11430000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>12750000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>19660000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>17850000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>5480000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>8870000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>6750000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>4690000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>2730000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-20070000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-680000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-1080000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-610000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>5690000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>3170000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>3130000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>2350000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>6000000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>6240000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>3950000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>4650000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>8380000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>3970000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>3350000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>4010000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>1680000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>2650000</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3074,197 +3149,206 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>7630000</v>
+      </c>
+      <c r="E35" s="3">
         <v>9070000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>7880000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>11430000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>12750000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>19660000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>17850000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>5480000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>8870000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>6750000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>4690000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>2730000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-20070000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-680000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-1080000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-610000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>5690000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>3170000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>3130000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>2350000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>6000000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>6240000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>3950000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>4650000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>8380000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>3970000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>3350000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>4010000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>1680000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>2650000</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42825</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42735</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3297,8 +3381,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3331,100 +3416,104 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>31539000</v>
+      </c>
+      <c r="E41" s="3">
         <v>32944000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>29528000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>32651000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>29640000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>30407000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>18861000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>11074000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>6802000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>4768000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>3465000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>3515000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>4364000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>8832000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>12576000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>11412000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>3089000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>5351000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>4213000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>4586000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>3042000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>5669000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>3430000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>4125000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>3177000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>4266000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>4042000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>4897000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>3657000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>5093000</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3515,560 +3604,581 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3" t="s">
-        <v>24</v>
+      <c r="D43" s="3">
+        <v>0</v>
       </c>
       <c r="E43" s="3">
-        <v>35915000</v>
+        <v>0</v>
       </c>
       <c r="F43" s="3">
-        <v>38808000</v>
+        <v>0</v>
       </c>
       <c r="G43" s="3">
-        <v>41749000</v>
+        <v>0</v>
       </c>
       <c r="H43" s="3">
-        <v>42411000</v>
+        <v>0</v>
       </c>
       <c r="I43" s="3">
-        <v>48063000</v>
+        <v>0</v>
       </c>
       <c r="J43" s="3">
+        <v>0</v>
+      </c>
+      <c r="K43" s="3">
         <v>42142000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>32383000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>29516000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>28540000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>24755000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>20581000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>19974000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>19036000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>20871000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>26966000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>25308000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>27132000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>27105000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>24701000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>27880000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>26993000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>24686000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>25597000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>23263000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>21289000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>21842000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>21394000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>20388000</v>
       </c>
     </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>25120000</v>
+      </c>
+      <c r="E44" s="3">
         <v>24450000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>24249000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>23642000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>24435000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>24096000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>23585000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>22177000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>18780000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>19607000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>19275000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>18357000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>18850000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>17885000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>19657000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>16501000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>18528000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>17590000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>18835000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>18332000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>18958000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>18761000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>18483000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>18048000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>16992000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>16743000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>15305000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>14873000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>15080000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>15342000</v>
       </c>
     </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1935000</v>
+      </c>
+      <c r="E45" s="3">
         <v>1934000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>2068000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2123000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1807000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>2375000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>2654000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1862000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1189000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1664000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1562000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1568000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1098000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>2002000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1747000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1465000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1469000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1759000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1563000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1553000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1272000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1665000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1649000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1456000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1368000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1480000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1544000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1519000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>1285000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>2122000</v>
       </c>
     </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>96609000</v>
+      </c>
+      <c r="E46" s="3">
         <v>101142000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>91760000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>97224000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>97631000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>99289000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>93163000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>77255000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>59154000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>55555000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>52842000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>48195000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>44893000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>48693000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>53016000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>50249000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>50052000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>50008000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>51743000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>51576000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>47973000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>53975000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>50555000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>48315000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>47134000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>45752000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>42180000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>43131000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>41416000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>42945000</v>
       </c>
     </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>47630000</v>
+      </c>
+      <c r="E47" s="3">
         <v>48066000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>47273000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>49044000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>49793000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>50235000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>46820000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>46329000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>45195000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>45641000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>44774000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>44181000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>43515000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>43609000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>43192000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>42981000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>43164000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>42920000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>42533000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>42068000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>40790000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>40427000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>39691000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>40350000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>39160000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>37649000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>37719000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>38268000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>35102000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>35553000</v>
       </c>
     </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>214940000</v>
+      </c>
+      <c r="E48" s="3">
         <v>205862000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>206736000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>206023000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>204692000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>203102000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>209159000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>212773000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>216552000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>218795000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>223012000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>224641000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>227553000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>250496000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>250524000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>248409000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>259651000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>257065000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>257118000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>253003000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>247101000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>249153000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>248209000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>250352000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>252630000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>255556000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>252987000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>253147000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>244224000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>251923000</v>
       </c>
     </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4159,8 +4269,11 @@
       <c r="AF49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4251,8 +4364,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4343,100 +4459,106 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>17138000</v>
+      </c>
+      <c r="E52" s="3">
         <v>17189000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>17479000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>17080000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>16951000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>17526000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>18632000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>18414000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>18022000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>16697000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>16661000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>16753000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>16789000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>15245000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>14763000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>14165000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>9730000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>9368000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>9335000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>9542000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>10332000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>11073000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>10335000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>9809000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>9767000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>10470000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>10126000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>9663000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>9572000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>8965000</v>
       </c>
     </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4527,100 +4649,106 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>376317000</v>
+      </c>
+      <c r="E54" s="3">
         <v>372259000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>363248000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>369371000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>369067000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>370152000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>367774000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>354771000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>338923000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>336688000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>337289000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>333770000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>332750000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>358043000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>361495000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>355804000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>362597000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>359361000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>360729000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>356189000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>346196000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>354628000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>348790000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>348826000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>348691000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>349427000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>343012000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>344209000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>330314000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>339386000</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4653,8 +4781,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4687,560 +4816,579 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>58037000</v>
+      </c>
+      <c r="E57" s="3">
         <v>62257000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>54404000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>59935000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>63197000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>62550000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>67958000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>63501000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>50766000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>47257000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>45780000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>41017000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>35221000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>33340000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>33216000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>35815000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>40605000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>39336000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>40324000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>41190000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>37268000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>41714000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>38490000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>37207000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>36796000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>34698000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>31100000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>32069000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>31193000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>30027000</v>
       </c>
     </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>4090000</v>
+      </c>
+      <c r="E58" s="3">
         <v>4743000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>3929000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2296000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>634000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>6182000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>7367000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>4886000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>4276000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>12966000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>15293000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>18185000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>20458000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>21911000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>22952000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>27755000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>20593000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>21219000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>26227000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>21828000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>17258000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>19413000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>20500000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>19836000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>17930000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>15741000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>17185000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>18483000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>13830000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>17239000</v>
       </c>
     </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>3189000</v>
+      </c>
+      <c r="E59" s="3">
         <v>4186000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>3482000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>4435000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>5214000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>5325000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>4785000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>3672000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1601000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1633000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1165000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>948000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>684000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1217000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1102000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1203000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2791000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>3640000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>3736000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>3614000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>2612000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>4161000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>3457000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>3263000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>3045000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>3338000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>2664000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>2822000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>2615000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>2755000</v>
       </c>
     </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>65316000</v>
+      </c>
+      <c r="E60" s="3">
         <v>71186000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>61815000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>66666000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>69045000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>74057000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>80110000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>72059000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>56643000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>61856000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>62238000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>60150000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>56363000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>56468000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>57270000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>64773000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>63989000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>64195000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>70287000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>66632000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>57138000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>65288000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>62447000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>60306000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>57771000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>53777000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>50949000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>53374000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>47638000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>50021000</v>
       </c>
     </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>37483000</v>
+      </c>
+      <c r="E61" s="3">
         <v>36510000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>37567000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>39150000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>40559000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>39246000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>39516000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>42651000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>43428000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>43639000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>45319000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>45137000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>47182000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>46888000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>46563000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>31857000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>26481000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>26089000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>19141000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>19177000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>20538000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>20624000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>20720000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>20781000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>24406000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>24869000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>24750000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>25124000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>28932000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>28916000</v>
       </c>
     </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>60980000</v>
+      </c>
+      <c r="E62" s="3">
         <v>57030000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>56869000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>57141000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>56990000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>63806000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>63640000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>63535000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>63169000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>63687000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>64176000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>64382000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>65075000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>70075000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>70509000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>70431000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>73189000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>71968000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>72836000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>72359000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>69992000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>71885000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>72090000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>72828000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>72014000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>81583000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>81475000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>81940000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>79914000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>83439000</v>
       </c>
     </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5331,8 +5479,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -5423,8 +5574,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5515,100 +5669,106 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>171515000</v>
+      </c>
+      <c r="E66" s="3">
         <v>172556000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>164202000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>170686000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>174018000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>184052000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>190458000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>185556000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>170346000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>176099000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>178718000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>176796000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>175600000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>180643000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>181312000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>173725000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>170947000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>169446000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>169352000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>164967000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>154402000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>164263000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>161568000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>160631000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>161003000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>167151000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>163834000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>167058000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>162989000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>168789000</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5641,8 +5801,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5733,8 +5894,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5825,8 +5989,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5917,8 +6084,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6009,100 +6179,106 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>453927000</v>
+      </c>
+      <c r="E72" s="3">
         <v>450138000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>444731000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>440552000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>432860000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>423877000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>407902000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>393779000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>392059000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>386952000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>383922000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>382953000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>383943000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>407728000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>412124000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>416919000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>421341000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>419367000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>419913000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>420498000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>421653000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>419155000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>416418000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>415970000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>414540000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>409449000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>408768000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>408707000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>407831000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>409284000</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6193,8 +6369,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6285,8 +6464,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6377,100 +6559,106 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>204802000</v>
+      </c>
+      <c r="E76" s="3">
         <v>199703000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>199046000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>198685000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>195049000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>186100000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>177316000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>169215000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>168577000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>160589000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>158571000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>156974000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>157150000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>177400000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>180183000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>182079000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>191650000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>189915000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>191377000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>191222000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>191794000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>190365000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>187222000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>188195000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>187688000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>182276000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>179178000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>177151000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>167325000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>170597000</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6561,197 +6749,206 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42825</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42735</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>7630000</v>
+      </c>
+      <c r="E81" s="3">
         <v>9070000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>7880000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>11430000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>12750000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>19660000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>17850000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>5480000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>8870000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>6750000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>4690000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>2730000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-20070000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-680000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-1080000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-610000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>5690000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>3170000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>3130000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>2350000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>6000000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>6240000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>3950000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>4650000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>8380000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>3970000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>3350000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>4010000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>1680000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>2650000</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6784,100 +6981,104 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>7740000</v>
+      </c>
+      <c r="E83" s="3">
         <v>4415000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>4242000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>4244000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>5064000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>5642000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>4451000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>4283000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>5661000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>4990000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>4952000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>5004000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>30291000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>4983000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>4916000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>5819000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>4923000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>4873000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>4631000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>4571000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>5028000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>4658000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>4589000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>4470000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>5842000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>4880000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>4652000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>4519000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>8117000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>4605000</v>
       </c>
     </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6968,8 +7169,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7060,8 +7264,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7152,8 +7359,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7244,8 +7454,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7336,100 +7549,106 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>13682000</v>
+      </c>
+      <c r="E89" s="3">
         <v>15963000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>9383000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>16341000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>17621000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>24425000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>19963000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>14788000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>17124000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>12091000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>9650000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>9264000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>4005000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>4389000</v>
       </c>
-      <c r="Q89" s="3">
-        <v>0</v>
-      </c>
       <c r="R89" s="3">
+        <v>0</v>
+      </c>
+      <c r="S89" s="3">
         <v>6274000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>6352000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>9079000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>5947000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>8338000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>8607000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>11108000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>7780000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>8519000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>7411000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>7535000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>6947000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>8173000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>7396000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>5355000</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7462,100 +7681,104 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-6228000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-4920000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-5359000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-5412000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-5783000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-4876000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-3837000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-3911000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-4089000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-2840000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-2747000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-2400000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-3629000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-3291000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-4417000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-5945000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-6704000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-6285000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-6173000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-5199000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-6094000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-5204000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-4927000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-3349000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-4501000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-4913000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-3098000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-2890000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-3887000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-3404000</v>
       </c>
     </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7646,8 +7869,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7738,100 +7964,106 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-5714000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-4279000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-4356000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-4925000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-5355000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-2378000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-3064000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-3945000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-2110000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-3054000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-2716000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-2355000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-3302000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-3709000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-5081000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-6367000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-4264000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-6150000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-6877000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-5793000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-5584000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-3907000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-5096000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-1859000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-6536000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-2555000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-2878000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-3761000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-1672000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-3235000</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7864,82 +8096,83 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-3839000</v>
+      </c>
+      <c r="E96" s="3">
         <v>-3663000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>-3701000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>-3738000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-3767000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-3685000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-3727000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-3760000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-3763000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-3720000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-3721000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-3720000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-3715000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-3716000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-3715000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-3719000</v>
-      </c>
-      <c r="S96" s="3">
-        <v>-3716000</v>
       </c>
       <c r="T96" s="3">
         <v>-3716000</v>
       </c>
       <c r="U96" s="3">
+        <v>-3716000</v>
+      </c>
+      <c r="V96" s="3">
         <v>-3715000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-3505000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-3502000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-3503000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-3502000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-3291000</v>
-      </c>
-      <c r="AA96" s="3">
-        <v>-3289000</v>
       </c>
       <c r="AB96" s="3">
         <v>-3289000</v>
@@ -7948,16 +8181,19 @@
         <v>-3289000</v>
       </c>
       <c r="AD96" s="3">
+        <v>-3289000</v>
+      </c>
+      <c r="AE96" s="3">
         <v>-3134000</v>
-      </c>
-      <c r="AE96" s="3">
-        <v>-3133000</v>
       </c>
       <c r="AF96" s="3">
         <v>-3133000</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>-3133000</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8048,8 +8284,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8140,8 +8379,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8232,280 +8474,292 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-9555000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-8059000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-8176000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-8507000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-13937000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-9793000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-8671000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-6713000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-12959000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-7657000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-7022000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-7785000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-5283000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-4494000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>6277000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>8785000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-4456000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-1666000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>548000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-1044000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-5501000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-4959000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-3244000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-5742000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-1837000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-4988000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-5059000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-3246000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-6746000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-1296000</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>182000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-209000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>30000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>102000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>872000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-651000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-441000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>142000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-21000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-77000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>38000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>27000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>112000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>70000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-32000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-369000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>106000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-125000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>9000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>43000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-149000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-3000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-135000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>30000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-127000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>232000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>135000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>74000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-414000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-89000</v>
       </c>
     </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1405000</v>
+      </c>
+      <c r="E102" s="3">
         <v>3416000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-3119000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>3011000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-799000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>11603000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>7787000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>4272000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>2034000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>1303000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-50000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-849000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-4468000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-3744000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>1164000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>8323000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-2262000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>1138000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-373000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>1544000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-2627000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>2239000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-695000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>948000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-1089000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>224000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-855000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>1240000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-1436000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>735000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/XOM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/XOM_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="92">
   <si>
     <t>XOM</t>
   </si>
@@ -656,407 +656,419 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="33" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="34" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42916</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42825</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42735</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>80411000</v>
+      </c>
+      <c r="E8" s="3">
         <v>81688000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>88570000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>80795000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>83644000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>93164000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>106512000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>111265000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>87734000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>81305000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>71892000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>65943000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>57552000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>45738000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>45425000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>32277000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>55134000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>63024000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>63422000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>67491000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>61646000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>68253000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>74187000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>71456000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>65436000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>50832000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>59350000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>56026000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>56474000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>40396000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>56767000</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>56692000</v>
+      </c>
+      <c r="E9" s="3">
         <v>56245000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>61772000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>56458000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>55439000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>61126000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>71514000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>76299000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>62629000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>56272000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>48464000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>45800000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>40663000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>32041000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>31053000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>20964000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>40380000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>44254000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>44138000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>48464000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>43771000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>46957000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>50873000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>50245000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>44779000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>28979000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>45248000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>43843000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>43267000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>21193000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>41181000</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>23719000</v>
+      </c>
+      <c r="E10" s="3">
         <v>25443000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>26798000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>24337000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>28205000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>32038000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>34998000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>34966000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>25105000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>25033000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>23428000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>20143000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>16889000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>13697000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>14372000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>11313000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>14754000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>18770000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>19284000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>19027000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>17875000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>21296000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>23314000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>21211000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>20657000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>21853000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>14102000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>12183000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>13207000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>19203000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>15586000</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1090,103 +1102,107 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>148000</v>
+      </c>
+      <c r="E12" s="3">
         <v>139000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>338000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>133000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>141000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>348000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>218000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>286000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>173000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>524000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>190000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>176000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>164000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>595000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>188000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>214000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>288000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>357000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>299000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>333000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>280000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>555000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>292000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>332000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>287000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>703000</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>284000</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>514000</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>289000</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>340000</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>327000</v>
       </c>
     </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1280,8 +1296,11 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1297,8 +1316,8 @@
       <c r="G14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
+      <c r="H14" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="I14" s="3">
         <v>0</v>
@@ -1307,10 +1326,10 @@
         <v>0</v>
       </c>
       <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
         <v>4600000</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>24</v>
@@ -1321,26 +1340,26 @@
       <c r="O14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="P14" s="3">
+      <c r="P14" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q14" s="3">
         <v>24875000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>62000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>64000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>910000</v>
-      </c>
-      <c r="T14" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="U14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
+      <c r="V14" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="W14" s="3">
         <v>0</v>
@@ -1375,103 +1394,109 @@
       <c r="AG14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>4812000</v>
+      </c>
+      <c r="E15" s="3">
         <v>7740000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>4415000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>4242000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>4244000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>5064000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>5642000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>4451000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>4283000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>5661000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>4990000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>4952000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>5004000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>5416000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>4921000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>4852000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>4909000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>4923000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>4873000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>4631000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>4571000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>5028000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>4658000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>4589000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>4470000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>5842000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>4880000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>4652000</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>4519000</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>8117000</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>4605000</v>
       </c>
     </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1502,198 +1527,205 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>69663000</v>
+      </c>
+      <c r="E17" s="3">
         <v>71956000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>76159000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>70272000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>69063000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>74720000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>85513000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>89826000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>81528000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>73015000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>63966000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>61181000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>55297000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>72840000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>46292000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>33928000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>56167000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>60527000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>60061000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>64243000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>59155000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>63559000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>67325000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>66842000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>60767000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>48832000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>55406000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>53763000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>52607000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>42224000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>55345000</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>10748000</v>
+      </c>
+      <c r="E18" s="3">
         <v>9732000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>12411000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>10523000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>14581000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>18444000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>20999000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>21439000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>6206000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>8290000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>7926000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>4762000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>2255000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-27102000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-867000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-1651000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-1033000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>2497000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>3361000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>3248000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>2491000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>4694000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>6862000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>4614000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>4669000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>2000000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>3944000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>2263000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>3867000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-1828000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>1422000</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1727,483 +1759,499 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>1842000</v>
+      </c>
+      <c r="E20" s="3">
         <v>1165000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>1457000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>1382000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>2381000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>605000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>4632000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>3688000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>2538000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>3660000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>1894000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>1799000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>1595000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>802000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>774000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>328000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>1024000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>4149000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>1627000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>1600000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>1979000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>3642000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>2418000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>2045000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>2775000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>1203000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>1750000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>2051000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>2197000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>2640000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>1910000</v>
       </c>
     </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>17402000</v>
+      </c>
+      <c r="E21" s="3">
         <v>18637000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>18283000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>16147000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>21206000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>24113000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>31273000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>29578000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>13027000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>17611000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>14810000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>11513000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>8854000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>3991000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>4890000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>3593000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>5810000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>11569000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>9861000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>9479000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>9041000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>13364000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>13938000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>11248000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>11914000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>9045000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>10574000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>8966000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>10583000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>8929000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>7937000</v>
       </c>
     </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>221000</v>
+      </c>
+      <c r="E22" s="3">
         <v>272000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>169000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>249000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>159000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>207000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>209000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>194000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>188000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>221000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>214000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>254000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>258000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>313000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>279000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>317000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>249000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>232000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>267000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>216000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>181000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>215000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>200000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>147000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>204000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>186000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>111000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>158000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>146000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>195000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>106000</v>
       </c>
     </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>12369000</v>
+      </c>
+      <c r="E23" s="3">
         <v>10625000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>13699000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>11656000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>16803000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>18842000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>25422000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>24933000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>8556000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>11729000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>9606000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>6307000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>3592000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-26613000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-372000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-1640000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-258000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>6414000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>4721000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>4632000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>4289000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>8121000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>9080000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>6512000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>7240000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>3017000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>5583000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>4156000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>5918000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>617000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>3226000</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>3803000</v>
+      </c>
+      <c r="E24" s="3">
         <v>2637000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>4353000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>3503000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>4960000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>5817000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>5224000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>6359000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>2806000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>2703000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>2664000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1526000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>796000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-5985000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>337000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-471000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>512000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>1424000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>1474000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>1241000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>1883000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>1936000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>2634000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>2526000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>2457000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>550000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>1498000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>892000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>1828000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-1407000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>337000</v>
       </c>
     </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2297,198 +2345,207 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>8566000</v>
+      </c>
+      <c r="E26" s="3">
         <v>7988000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>9346000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>8153000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>11843000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>13025000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>20198000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>18574000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>5750000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>9026000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>6942000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>4781000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>2796000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-20628000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-709000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-1169000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-770000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>4990000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>3247000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>3391000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>2406000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>6185000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>6446000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>3986000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>4783000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>2467000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>4085000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>3264000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>4090000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>2024000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>2889000</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>8220000</v>
+      </c>
+      <c r="E27" s="3">
         <v>7606000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>9070000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>7880000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>11430000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>12720000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>19660000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>17850000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>5480000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>8817000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>6750000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>4690000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>2730000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-20095000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-680000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-1080000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-610000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>4950000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>3170000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>3130000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>2350000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>5979000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>6240000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>3950000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>4650000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>2438000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>3970000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>3350000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>4010000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>1680000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>2650000</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -2582,16 +2639,19 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D29" s="3">
+      <c r="D29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E29" s="3">
         <v>24000</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="F29" s="3" t="s">
         <v>24</v>
@@ -2599,11 +2659,11 @@
       <c r="G29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="H29" s="3">
+      <c r="H29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I29" s="3">
         <v>30000</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="J29" s="3" t="s">
         <v>24</v>
@@ -2611,11 +2671,11 @@
       <c r="K29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="L29" s="3">
+      <c r="L29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M29" s="3">
         <v>53000</v>
-      </c>
-      <c r="M29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="N29" s="3" t="s">
         <v>24</v>
@@ -2623,11 +2683,11 @@
       <c r="O29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="P29" s="3">
+      <c r="P29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q29" s="3">
         <v>25000</v>
-      </c>
-      <c r="Q29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="R29" s="3" t="s">
         <v>24</v>
@@ -2635,11 +2695,11 @@
       <c r="S29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="T29" s="3">
+      <c r="T29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="U29" s="3">
         <v>740000</v>
-      </c>
-      <c r="U29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="V29" s="3" t="s">
         <v>24</v>
@@ -2647,11 +2707,11 @@
       <c r="W29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="X29" s="3">
+      <c r="X29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Y29" s="3">
         <v>21000</v>
-      </c>
-      <c r="Y29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="Z29" s="3" t="s">
         <v>24</v>
@@ -2659,11 +2719,11 @@
       <c r="AA29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AB29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AC29" s="3">
         <v>5942000</v>
-      </c>
-      <c r="AC29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>24</v>
@@ -2677,8 +2737,11 @@
       <c r="AG29" s="3" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2772,8 +2835,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2867,198 +2933,207 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-1842000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-1165000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-1457000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-1382000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-2381000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-605000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-4632000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-3688000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-2538000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-3660000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-1894000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-1799000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-1595000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-802000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-774000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-328000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-1024000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-4149000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-1627000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-1600000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-1979000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-3642000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-2418000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-2045000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-2775000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-1203000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-1750000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-2051000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-2197000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-2640000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-1910000</v>
       </c>
     </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>8220000</v>
+      </c>
+      <c r="E33" s="3">
         <v>7630000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>9070000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>7880000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>11430000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>12750000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>19660000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>17850000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>5480000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>8870000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>6750000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>4690000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>2730000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-20070000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-680000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-1080000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-610000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>5690000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>3170000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>3130000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>2350000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>6000000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>6240000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>3950000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>4650000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>8380000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>3970000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>3350000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>4010000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>1680000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>2650000</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3152,203 +3227,212 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>8220000</v>
+      </c>
+      <c r="E35" s="3">
         <v>7630000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>9070000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>7880000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>11430000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>12750000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>19660000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>17850000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>5480000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>8870000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>6750000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>4690000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>2730000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-20070000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-680000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-1080000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-610000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>5690000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>3170000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>3130000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>2350000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>6000000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>6240000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>3950000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>4650000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>8380000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>3970000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>3350000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>4010000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>1680000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>2650000</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42916</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42825</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42735</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3382,8 +3466,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3417,103 +3502,107 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>33320000</v>
+      </c>
+      <c r="E41" s="3">
         <v>31539000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>32944000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>29528000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>32651000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>29640000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>30407000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>18861000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>11074000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>6802000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>4768000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>3465000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>3515000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>4364000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>8832000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>12576000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>11412000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>3089000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>5351000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>4213000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>4586000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>3042000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>5669000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>3430000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>4125000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>3177000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>4266000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>4042000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>4897000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>3657000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>5093000</v>
       </c>
     </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3607,8 +3696,11 @@
       <c r="AG42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3634,551 +3726,569 @@
         <v>0</v>
       </c>
       <c r="K43" s="3">
+        <v>0</v>
+      </c>
+      <c r="L43" s="3">
         <v>42142000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>32383000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>29516000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>28540000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>24755000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>20581000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>19974000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>19036000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>20871000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>26966000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>25308000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>27132000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>27105000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>24701000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>27880000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>26993000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>24686000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>25597000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>23263000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>21289000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>21842000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>21394000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>20388000</v>
       </c>
     </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>23491000</v>
+      </c>
+      <c r="E44" s="3">
         <v>25120000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>24450000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>24249000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>23642000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>24435000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>24096000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>23585000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>22177000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>18780000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>19607000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>19275000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>18357000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>18850000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>17885000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>19657000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>16501000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>18528000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>17590000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>18835000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>18332000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>18958000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>18761000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>18483000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>18048000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>16992000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>16743000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>15305000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>14873000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>15080000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>15342000</v>
       </c>
     </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>2200000</v>
+      </c>
+      <c r="E45" s="3">
         <v>1935000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1934000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2068000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>2123000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1807000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>2375000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2654000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1862000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1189000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1664000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1562000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1568000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1098000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>2002000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1747000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1465000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1469000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1759000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1563000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1553000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1272000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1665000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1649000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1456000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1368000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1480000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1544000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>1519000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>1285000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>2122000</v>
       </c>
     </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>99377000</v>
+      </c>
+      <c r="E46" s="3">
         <v>96609000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>101142000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>91760000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>97224000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>97631000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>99289000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>93163000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>77255000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>59154000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>55555000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>52842000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>48195000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>44893000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>48693000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>53016000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>50249000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>50052000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>50008000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>51743000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>51576000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>47973000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>53975000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>50555000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>48315000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>47134000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>45752000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>42180000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>43131000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>41416000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>42945000</v>
       </c>
     </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>47608000</v>
+      </c>
+      <c r="E47" s="3">
         <v>47630000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>48066000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>47273000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>49044000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>49793000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>50235000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>46820000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>46329000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>45195000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>45641000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>44774000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>44181000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>43515000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>43609000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>43192000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>42981000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>43164000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>42920000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>42533000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>42068000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>40790000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>40427000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>39691000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>40350000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>39160000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>37649000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>37719000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>38268000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>35102000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>35553000</v>
       </c>
     </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>213723000</v>
+      </c>
+      <c r="E48" s="3">
         <v>214940000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>205862000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>206736000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>206023000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>204692000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>203102000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>209159000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>212773000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>216552000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>218795000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>223012000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>224641000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>227553000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>250496000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>250524000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>248409000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>259651000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>257065000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>257118000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>253003000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>247101000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>249153000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>248209000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>250352000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>252630000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>255556000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>252987000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>253147000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>244224000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>251923000</v>
       </c>
     </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4272,8 +4382,11 @@
       <c r="AG49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4367,8 +4480,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4462,103 +4578,109 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>17210000</v>
+      </c>
+      <c r="E52" s="3">
         <v>17138000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>17189000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>17479000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>17080000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>16951000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>17526000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>18632000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>18414000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>18022000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>16697000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>16661000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>16753000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>16789000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>15245000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>14763000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>14165000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>9730000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>9368000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>9335000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>9542000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>10332000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>11073000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>10335000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>9809000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>9767000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>10470000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>10126000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>9663000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>9572000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>8965000</v>
       </c>
     </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4652,103 +4774,109 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>377918000</v>
+      </c>
+      <c r="E54" s="3">
         <v>376317000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>372259000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>363248000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>369371000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>369067000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>370152000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>367774000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>354771000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>338923000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>336688000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>337289000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>333770000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>332750000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>358043000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>361495000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>355804000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>362597000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>359361000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>360729000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>356189000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>346196000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>354628000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>348790000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>348826000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>348691000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>349427000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>343012000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>344209000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>330314000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>339386000</v>
       </c>
     </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4782,8 +4910,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4817,578 +4946,597 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>59531000</v>
+      </c>
+      <c r="E57" s="3">
         <v>58037000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>62257000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>54404000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>59935000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>63197000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>62550000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>67958000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>63501000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>50766000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>47257000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>45780000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>41017000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>35221000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>33340000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>33216000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>35815000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>40605000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>39336000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>40324000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>41190000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>37268000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>41714000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>38490000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>37207000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>36796000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>34698000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>31100000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>32069000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>31193000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>30027000</v>
       </c>
     </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>8227000</v>
+      </c>
+      <c r="E58" s="3">
         <v>4090000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>4743000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>3929000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2296000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>634000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>6182000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>7367000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>4886000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>4276000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>12966000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>15293000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>18185000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>20458000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>21911000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>22952000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>27755000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>20593000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>21219000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>26227000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>21828000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>17258000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>19413000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>20500000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>19836000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>17930000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>15741000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>17185000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>18483000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>13830000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>17239000</v>
       </c>
     </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>4163000</v>
+      </c>
+      <c r="E59" s="3">
         <v>3189000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>4186000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>3482000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>4435000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>5214000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>5325000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>4785000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>3672000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1601000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1633000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1165000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>948000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>684000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1217000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1102000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1203000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>2791000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>3640000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>3736000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>3614000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>2612000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>4161000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>3457000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>3263000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>3045000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>3338000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>2664000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>2822000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>2615000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>2755000</v>
       </c>
     </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>71921000</v>
+      </c>
+      <c r="E60" s="3">
         <v>65316000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>71186000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>61815000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>66666000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>69045000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>74057000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>80110000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>72059000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>56643000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>61856000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>62238000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>60150000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>56363000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>56468000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>57270000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>64773000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>63989000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>64195000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>70287000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>66632000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>57138000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>65288000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>62447000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>60306000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>57771000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>53777000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>50949000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>53374000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>47638000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>50021000</v>
       </c>
     </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>32213000</v>
+      </c>
+      <c r="E61" s="3">
         <v>37483000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>36510000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>37567000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>39150000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>40559000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>39246000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>39516000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>42651000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>43428000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>43639000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>45319000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>45137000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>47182000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>46888000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>46563000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>31857000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>26481000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>26089000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>19141000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>19177000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>20538000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>20624000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>20720000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>20781000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>24406000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>24869000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>24750000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>25124000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>28932000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>28916000</v>
       </c>
     </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>60732000</v>
+      </c>
+      <c r="E62" s="3">
         <v>60980000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>57030000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>56869000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>57141000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>56990000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>63806000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>63640000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>63535000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>63169000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>63687000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>64176000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>64382000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>65075000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>70075000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>70509000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>70431000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>73189000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>71968000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>72836000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>72359000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>69992000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>71885000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>72090000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>72828000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>72014000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>81583000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>81475000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>81940000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>79914000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>83439000</v>
       </c>
     </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5482,8 +5630,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -5577,8 +5728,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5672,103 +5826,109 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>172668000</v>
+      </c>
+      <c r="E66" s="3">
         <v>171515000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>172556000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>164202000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>170686000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>174018000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>184052000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>190458000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>185556000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>170346000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>176099000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>178718000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>176796000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>175600000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>180643000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>181312000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>173725000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>170947000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>169446000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>169352000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>164967000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>154402000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>164263000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>161568000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>160631000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>161003000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>167151000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>163834000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>167058000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>162989000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>168789000</v>
       </c>
     </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5802,8 +5962,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5897,8 +6058,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5992,8 +6156,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6087,8 +6254,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6182,103 +6352,109 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>458339000</v>
+      </c>
+      <c r="E72" s="3">
         <v>453927000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>450138000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>444731000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>440552000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>432860000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>423877000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>407902000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>393779000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>392059000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>386952000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>383922000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>382953000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>383943000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>407728000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>412124000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>416919000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>421341000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>419367000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>419913000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>420498000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>421653000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>419155000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>416418000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>415970000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>414540000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>409449000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>408768000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>408707000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>407831000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>409284000</v>
       </c>
     </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6372,8 +6548,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6467,8 +6646,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6562,103 +6744,109 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>205250000</v>
+      </c>
+      <c r="E76" s="3">
         <v>204802000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>199703000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>199046000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>198685000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>195049000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>186100000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>177316000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>169215000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>168577000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>160589000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>158571000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>156974000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>157150000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>177400000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>180183000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>182079000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>191650000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>189915000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>191377000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>191222000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>191794000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>190365000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>187222000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>188195000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>187688000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>182276000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>179178000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>177151000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>167325000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>170597000</v>
       </c>
     </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6752,203 +6940,212 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42916</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42825</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42735</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>8220000</v>
+      </c>
+      <c r="E81" s="3">
         <v>7630000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>9070000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>7880000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>11430000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>12750000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>19660000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>17850000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>5480000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>8870000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>6750000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>4690000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>2730000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-20070000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-680000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-1080000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-610000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>5690000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>3170000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>3130000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>2350000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>6000000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>6240000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>3950000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>4650000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>8380000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>3970000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>3350000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>4010000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>1680000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>2650000</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6982,103 +7179,107 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>4812000</v>
+      </c>
+      <c r="E83" s="3">
         <v>7740000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>4415000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>4242000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>4244000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>5064000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>5642000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>4451000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>4283000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>5661000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>4990000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>4952000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>5004000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>30291000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>4983000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>4916000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>5819000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>4923000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>4873000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>4631000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>4571000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>5028000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>4658000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>4589000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>4470000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>5842000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>4880000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>4652000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>4519000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>8117000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>4605000</v>
       </c>
     </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7172,8 +7373,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7267,8 +7471,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7362,8 +7569,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7457,8 +7667,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7552,103 +7765,109 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>14664000</v>
+      </c>
+      <c r="E89" s="3">
         <v>13682000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>15963000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>9383000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>16341000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>17621000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>24425000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>19963000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>14788000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>17124000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>12091000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>9650000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>9264000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>4005000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>4389000</v>
       </c>
-      <c r="R89" s="3">
-        <v>0</v>
-      </c>
       <c r="S89" s="3">
+        <v>0</v>
+      </c>
+      <c r="T89" s="3">
         <v>6274000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>6352000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>9079000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>5947000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>8338000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>8607000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>11108000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>7780000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>8519000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>7411000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>7535000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>6947000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>8173000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>7396000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>5355000</v>
       </c>
     </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7682,103 +7901,107 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-5074000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-6228000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-4920000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-5359000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-5412000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-5783000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-4876000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-3837000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-3911000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-4089000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-2840000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-2747000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-2400000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-3629000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-3291000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-4417000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-5945000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-6704000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-6285000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-6173000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-5199000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-6094000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-5204000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-4927000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-3349000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-4501000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-4913000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-3098000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-2890000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-3887000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-3404000</v>
       </c>
     </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7872,8 +8095,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7967,103 +8193,109 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-4577000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-5714000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-4279000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-4356000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-4925000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-5355000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-2378000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-3064000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-3945000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-2110000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-3054000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-2716000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-2355000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-3302000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-3709000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-5081000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-6367000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-4264000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-6150000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-6877000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-5793000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-5584000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-3907000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-5096000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-1859000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-6536000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-2555000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-2878000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-3761000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-1672000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-3235000</v>
       </c>
     </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8097,85 +8329,86 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-3808000</v>
+      </c>
+      <c r="E96" s="3">
         <v>-3839000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>-3663000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>-3701000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-3738000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-3767000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-3685000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-3727000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-3760000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-3763000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-3720000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-3721000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-3720000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-3715000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-3716000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-3715000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-3719000</v>
-      </c>
-      <c r="T96" s="3">
-        <v>-3716000</v>
       </c>
       <c r="U96" s="3">
         <v>-3716000</v>
       </c>
       <c r="V96" s="3">
+        <v>-3716000</v>
+      </c>
+      <c r="W96" s="3">
         <v>-3715000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-3505000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-3502000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-3503000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-3502000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-3291000</v>
-      </c>
-      <c r="AB96" s="3">
-        <v>-3289000</v>
       </c>
       <c r="AC96" s="3">
         <v>-3289000</v>
@@ -8184,16 +8417,19 @@
         <v>-3289000</v>
       </c>
       <c r="AE96" s="3">
+        <v>-3289000</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-3134000</v>
-      </c>
-      <c r="AF96" s="3">
-        <v>-3133000</v>
       </c>
       <c r="AG96" s="3">
         <v>-3133000</v>
       </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>-3133000</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8287,8 +8523,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8382,8 +8621,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8477,289 +8719,301 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-7982000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-9555000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-8059000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-8176000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-8507000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-13937000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-9793000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-8671000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-6713000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-12959000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-7657000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-7022000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-7785000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-5283000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-4494000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>6277000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>8785000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-4456000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-1666000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>548000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-1044000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-5501000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-4959000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-3244000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-5742000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-1837000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-4988000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-5059000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-3246000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-6746000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-1296000</v>
       </c>
     </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-324000</v>
+      </c>
+      <c r="E101" s="3">
         <v>182000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-209000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>30000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>102000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>872000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-651000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-441000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>142000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-21000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-77000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>38000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>27000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>112000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>70000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-32000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-369000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>106000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-125000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>9000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>43000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-149000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-3000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-135000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>30000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-127000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>232000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>135000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>74000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-414000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-89000</v>
       </c>
     </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1781000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1405000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>3416000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-3119000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>3011000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-799000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>11603000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>7787000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>4272000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>2034000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>1303000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-50000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-849000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-4468000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-3744000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>1164000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>8323000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-2262000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>1138000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-373000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>1544000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-2627000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>2239000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-695000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>948000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-1089000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>224000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-855000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>1240000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-1436000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>735000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/XOM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/XOM_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="92">
   <si>
     <t>XOM</t>
   </si>
@@ -656,419 +656,431 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="34" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="35" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42916</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42825</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42735</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>89986000</v>
+      </c>
+      <c r="E8" s="3">
         <v>80411000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>81688000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>88570000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>80795000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>83644000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>93164000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>106512000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>111265000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>87734000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>81305000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>71892000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>65943000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>57552000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>45738000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>45425000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>32277000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>55134000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>63024000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>63422000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>67491000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>61646000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>68253000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>74187000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>71456000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>65436000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>50832000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>59350000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>56026000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>56474000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>40396000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>56767000</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>64003000</v>
+      </c>
+      <c r="E9" s="3">
         <v>56692000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>56245000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>61772000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>56458000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>55439000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>61126000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>71514000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>76299000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>62629000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>56272000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>48464000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>45800000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>40663000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>32041000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>31053000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>20964000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>40380000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>44254000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>44138000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>48464000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>43771000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>46957000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>50873000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>50245000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>44779000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>28979000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>45248000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>43843000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>43267000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>21193000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>41181000</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>25983000</v>
+      </c>
+      <c r="E10" s="3">
         <v>23719000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>25443000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>26798000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>24337000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>28205000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>32038000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>34998000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>34966000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>25105000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>25033000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>23428000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>20143000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>16889000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>13697000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>14372000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>11313000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>14754000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>18770000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>19284000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>19027000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>17875000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>21296000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>23314000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>21211000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>20657000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>21853000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>14102000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>12183000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>13207000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>19203000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>15586000</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1103,106 +1115,110 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>153000</v>
+      </c>
+      <c r="E12" s="3">
         <v>148000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>139000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>338000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>133000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>141000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>348000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>218000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>286000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>173000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>524000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>190000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>176000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>164000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>595000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>188000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>214000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>288000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>357000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>299000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>333000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>280000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>555000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>292000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>332000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>287000</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>703000</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>284000</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>514000</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>289000</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>340000</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>327000</v>
       </c>
     </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1299,8 +1315,11 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1319,8 +1338,8 @@
       <c r="H14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
+      <c r="I14" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="J14" s="3">
         <v>0</v>
@@ -1329,10 +1348,10 @@
         <v>0</v>
       </c>
       <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
         <v>4600000</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>24</v>
@@ -1343,26 +1362,26 @@
       <c r="P14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="Q14" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="R14" s="3">
         <v>24875000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>62000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>64000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>910000</v>
-      </c>
-      <c r="U14" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="V14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
+      <c r="W14" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="X14" s="3">
         <v>0</v>
@@ -1397,106 +1416,112 @@
       <c r="AH14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>5787000</v>
+      </c>
+      <c r="E15" s="3">
         <v>4812000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>7740000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>4415000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>4242000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>4244000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>5064000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>5642000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>4451000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>4283000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>5661000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>4990000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>4952000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>5004000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>5416000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>4921000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>4852000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>4909000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>4923000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>4873000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>4631000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>4571000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>5028000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>4658000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>4589000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>4470000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>5842000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>4880000</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>4652000</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>4519000</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>8117000</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>4605000</v>
       </c>
     </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1528,204 +1553,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>77794000</v>
+      </c>
+      <c r="E17" s="3">
         <v>69663000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>71956000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>76159000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>70272000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>69063000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>74720000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>85513000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>89826000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>81528000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>73015000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>63966000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>61181000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>55297000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>72840000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>46292000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>33928000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>56167000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>60527000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>60061000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>64243000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>59155000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>63559000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>67325000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>66842000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>60767000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>48832000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>55406000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>53763000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>52607000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>42224000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>55345000</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>12192000</v>
+      </c>
+      <c r="E18" s="3">
         <v>10748000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>9732000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>12411000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>10523000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>14581000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>18444000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>20999000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>21439000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>6206000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>8290000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>7926000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>4762000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>2255000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-27102000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-867000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-1651000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-1033000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>2497000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>3361000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>3248000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>2491000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>4694000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>6862000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>4614000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>4669000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>2000000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>3944000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>2263000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>3867000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-1828000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>1422000</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1760,498 +1792,514 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>1744000</v>
+      </c>
+      <c r="E20" s="3">
         <v>1842000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>1165000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>1457000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>1382000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>2381000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>605000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>4632000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>3688000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>2538000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>3660000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>1894000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>1799000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>1595000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>802000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>774000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>328000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>1024000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>4149000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>1627000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>1600000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>1979000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>3642000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>2418000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>2045000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>2775000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>1203000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>1750000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>2051000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>2197000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>2640000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>1910000</v>
       </c>
     </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>19723000</v>
+      </c>
+      <c r="E21" s="3">
         <v>17402000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>18637000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>18283000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>16147000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>21206000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>24113000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>31273000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>29578000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>13027000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>17611000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>14810000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>11513000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>8854000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>3991000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>4890000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>3593000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>5810000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>11569000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>9861000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>9479000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>9041000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>13364000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>13938000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>11248000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>11914000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>9045000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>10574000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>8966000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>10583000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>8929000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>7937000</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>271000</v>
+      </c>
+      <c r="E22" s="3">
         <v>221000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>272000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>169000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>249000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>159000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>207000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>209000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>194000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>188000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>221000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>214000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>254000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>258000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>313000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>279000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>317000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>249000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>232000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>267000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>216000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>181000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>215000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>200000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>147000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>204000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>186000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>111000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>158000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>146000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>195000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>106000</v>
       </c>
     </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>13665000</v>
+      </c>
+      <c r="E23" s="3">
         <v>12369000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>10625000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>13699000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>11656000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>16803000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>18842000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>25422000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>24933000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>8556000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>11729000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>9606000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>6307000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>3592000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-26613000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-372000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-1640000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-258000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>6414000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>4721000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>4632000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>4289000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>8121000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>9080000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>6512000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>7240000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>3017000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>5583000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>4156000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>5918000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>617000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>3226000</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>4094000</v>
+      </c>
+      <c r="E24" s="3">
         <v>3803000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>2637000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>4353000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>3503000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>4960000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>5817000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>5224000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>6359000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>2806000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>2703000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>2664000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1526000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>796000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-5985000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>337000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-471000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>512000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>1424000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>1474000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>1241000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>1883000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>1936000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>2634000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>2526000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>2457000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>550000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>1498000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>892000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>1828000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-1407000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>337000</v>
       </c>
     </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2348,204 +2396,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>9571000</v>
+      </c>
+      <c r="E26" s="3">
         <v>8566000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>7988000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>9346000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>8153000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>11843000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>13025000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>20198000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>18574000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>5750000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>9026000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>6942000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>4781000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>2796000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-20628000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-709000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-1169000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-770000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>4990000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>3247000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>3391000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>2406000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>6185000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>6446000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>3986000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>4783000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>2467000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>4085000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>3264000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>4090000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>2024000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>2889000</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>9240000</v>
+      </c>
+      <c r="E27" s="3">
         <v>8220000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>7606000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>9070000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>7880000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>11430000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>12720000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>19660000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>17850000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>5480000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>8817000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>6750000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>4690000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>2730000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-20095000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-680000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-1080000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-610000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>4950000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>3170000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>3130000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>2350000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>5979000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>6240000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>3950000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>4650000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>2438000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>3970000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>3350000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>4010000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>1680000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>2650000</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -2642,19 +2699,22 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E29" s="3">
+      <c r="E29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F29" s="3">
         <v>24000</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>24</v>
@@ -2662,11 +2722,11 @@
       <c r="H29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="I29" s="3">
+      <c r="I29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J29" s="3">
         <v>30000</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>24</v>
@@ -2674,11 +2734,11 @@
       <c r="L29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="M29" s="3">
+      <c r="M29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="N29" s="3">
         <v>53000</v>
-      </c>
-      <c r="N29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="O29" s="3" t="s">
         <v>24</v>
@@ -2686,11 +2746,11 @@
       <c r="P29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="Q29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="R29" s="3">
         <v>25000</v>
-      </c>
-      <c r="R29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="S29" s="3" t="s">
         <v>24</v>
@@ -2698,11 +2758,11 @@
       <c r="T29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="U29" s="3">
+      <c r="U29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="V29" s="3">
         <v>740000</v>
-      </c>
-      <c r="V29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="W29" s="3" t="s">
         <v>24</v>
@@ -2710,11 +2770,11 @@
       <c r="X29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Y29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z29" s="3">
         <v>21000</v>
-      </c>
-      <c r="Z29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AA29" s="3" t="s">
         <v>24</v>
@@ -2722,11 +2782,11 @@
       <c r="AB29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AC29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AD29" s="3">
         <v>5942000</v>
-      </c>
-      <c r="AD29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>24</v>
@@ -2740,8 +2800,11 @@
       <c r="AH29" s="3" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2838,8 +2901,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2936,204 +3002,213 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-1744000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-1842000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-1165000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-1457000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-1382000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-2381000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-605000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-4632000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-3688000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-2538000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-3660000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-1894000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-1799000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-1595000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-802000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-774000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-328000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-1024000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-4149000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-1627000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-1600000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-1979000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-3642000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-2418000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-2045000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-2775000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-1203000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-1750000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-2051000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-2197000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-2640000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-1910000</v>
       </c>
     </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>9240000</v>
+      </c>
+      <c r="E33" s="3">
         <v>8220000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>7630000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>9070000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>7880000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>11430000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>12750000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>19660000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>17850000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>5480000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>8870000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>6750000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>4690000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>2730000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-20070000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-680000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-1080000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-610000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>5690000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>3170000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>3130000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>2350000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>6000000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>6240000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>3950000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>4650000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>8380000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>3970000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>3350000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>4010000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>1680000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>2650000</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3230,209 +3305,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>9240000</v>
+      </c>
+      <c r="E35" s="3">
         <v>8220000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>7630000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>9070000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>7880000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>11430000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>12750000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>19660000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>17850000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>5480000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>8870000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>6750000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>4690000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>2730000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-20070000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-680000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-1080000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-610000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>5690000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>3170000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>3130000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>2350000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>6000000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>6240000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>3950000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>4650000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>8380000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>3970000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>3350000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>4010000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>1680000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>2650000</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42916</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42825</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42735</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3467,8 +3551,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3503,106 +3588,110 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>26460000</v>
+      </c>
+      <c r="E41" s="3">
         <v>33320000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>31539000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>32944000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>29528000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>32651000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>29640000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>30407000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>18861000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>11074000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>6802000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>4768000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>3465000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>3515000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>4364000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>8832000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>12576000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>11412000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>3089000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>5351000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>4213000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>4586000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>3042000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>5669000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>3430000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>4125000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>3177000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>4266000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>4042000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>4897000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>3657000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>5093000</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3699,8 +3788,11 @@
       <c r="AH42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3729,566 +3821,584 @@
         <v>0</v>
       </c>
       <c r="L43" s="3">
+        <v>0</v>
+      </c>
+      <c r="M43" s="3">
         <v>42142000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>32383000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>29516000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>28540000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>24755000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>20581000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>19974000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>19036000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>20871000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>26966000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>25308000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>27132000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>27105000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>24701000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>27880000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>26993000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>24686000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>25597000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>23263000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>21289000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>21842000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>21394000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>20388000</v>
       </c>
     </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>24503000</v>
+      </c>
+      <c r="E44" s="3">
         <v>23491000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>25120000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>24450000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>24249000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>23642000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>24435000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>24096000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>23585000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>22177000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>18780000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>19607000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>19275000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>18357000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>18850000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>17885000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>19657000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>16501000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>18528000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>17590000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>18835000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>18332000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>18958000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>18761000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>18483000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>18048000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>16992000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>16743000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>15305000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>14873000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>15080000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>15342000</v>
       </c>
     </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>2204000</v>
+      </c>
+      <c r="E45" s="3">
         <v>2200000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1935000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1934000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>2068000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>2123000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1807000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2375000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2654000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1862000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1189000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1664000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1562000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1568000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1098000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>2002000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1747000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1465000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1469000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1759000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1563000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1553000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1272000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1665000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1649000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1456000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1368000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1480000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>1544000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>1519000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>1285000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>2122000</v>
       </c>
     </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>96238000</v>
+      </c>
+      <c r="E46" s="3">
         <v>99377000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>96609000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>101142000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>91760000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>97224000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>97631000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>99289000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>93163000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>77255000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>59154000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>55555000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>52842000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>48195000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>44893000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>48693000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>53016000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>50249000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>50052000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>50008000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>51743000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>51576000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>47973000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>53975000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>50555000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>48315000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>47134000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>45752000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>42180000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>43131000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>41416000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>42945000</v>
       </c>
     </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>47948000</v>
+      </c>
+      <c r="E47" s="3">
         <v>47608000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>47630000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>48066000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>47273000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>49044000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>49793000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>50235000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>46820000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>46329000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>45195000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>45641000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>44774000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>44181000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>43515000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>43609000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>43192000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>42981000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>43164000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>42920000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>42533000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>42068000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>40790000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>40427000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>39691000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>40350000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>39160000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>37649000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>37719000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>38268000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>35102000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>35553000</v>
       </c>
     </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>298283000</v>
+      </c>
+      <c r="E48" s="3">
         <v>213723000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>214940000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>205862000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>206736000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>206023000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>204692000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>203102000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>209159000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>212773000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>216552000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>218795000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>223012000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>224641000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>227553000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>250496000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>250524000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>248409000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>259651000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>257065000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>257118000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>253003000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>247101000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>249153000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>248209000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>250352000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>252630000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>255556000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>252987000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>253147000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>244224000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>251923000</v>
       </c>
     </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4385,8 +4495,11 @@
       <c r="AH49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4483,8 +4596,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4581,106 +4697,112 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>18238000</v>
+      </c>
+      <c r="E52" s="3">
         <v>17210000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>17138000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>17189000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>17479000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>17080000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>16951000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>17526000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>18632000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>18414000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>18022000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>16697000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>16661000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>16753000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>16789000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>15245000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>14763000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>14165000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>9730000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>9368000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>9335000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>9542000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>10332000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>11073000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>10335000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>9809000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>9767000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>10470000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>10126000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>9663000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>9572000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>8965000</v>
       </c>
     </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4777,106 +4899,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>460707000</v>
+      </c>
+      <c r="E54" s="3">
         <v>377918000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>376317000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>372259000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>363248000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>369371000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>369067000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>370152000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>367774000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>354771000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>338923000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>336688000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>337289000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>333770000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>332750000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>358043000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>361495000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>355804000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>362597000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>359361000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>360729000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>356189000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>346196000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>354628000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>348790000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>348826000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>348691000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>349427000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>343012000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>344209000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>330314000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>339386000</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4911,8 +5039,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4947,596 +5076,615 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>60107000</v>
+      </c>
+      <c r="E57" s="3">
         <v>59531000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>58037000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>62257000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>54404000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>59935000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>63197000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>62550000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>67958000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>63501000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>50766000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>47257000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>45780000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>41017000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>35221000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>33340000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>33216000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>35815000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>40605000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>39336000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>40324000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>41190000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>37268000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>41714000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>38490000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>37207000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>36796000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>34698000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>31100000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>32069000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>31193000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>30027000</v>
       </c>
     </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>6621000</v>
+      </c>
+      <c r="E58" s="3">
         <v>8227000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>4090000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>4743000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>3929000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>2296000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>634000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>6182000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>7367000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>4886000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>4276000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>12966000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>15293000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>18185000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>20458000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>21911000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>22952000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>27755000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>20593000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>21219000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>26227000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>21828000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>17258000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>19413000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>20500000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>19836000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>17930000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>15741000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>17185000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>18483000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>13830000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>17239000</v>
       </c>
     </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>4035000</v>
+      </c>
+      <c r="E59" s="3">
         <v>4163000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>3189000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>4186000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>3482000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>4435000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>5214000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>5325000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>4785000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>3672000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1601000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1633000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1165000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>948000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>684000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1217000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1102000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1203000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>2791000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>3640000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>3736000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>3614000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>2612000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>4161000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>3457000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>3263000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>3045000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>3338000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>2664000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>2822000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>2615000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>2755000</v>
       </c>
     </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>70763000</v>
+      </c>
+      <c r="E60" s="3">
         <v>71921000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>65316000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>71186000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>61815000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>66666000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>69045000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>74057000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>80110000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>72059000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>56643000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>61856000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>62238000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>60150000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>56363000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>56468000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>57270000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>64773000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>63989000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>64195000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>70287000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>66632000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>57138000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>65288000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>62447000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>60306000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>57771000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>53777000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>50949000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>53374000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>47638000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>50021000</v>
       </c>
     </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>36565000</v>
+      </c>
+      <c r="E61" s="3">
         <v>32213000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>37483000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>36510000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>37567000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>39150000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>40559000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>39246000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>39516000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>42651000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>43428000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>43639000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>45319000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>45137000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>47182000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>46888000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>46563000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>31857000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>26481000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>26089000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>19141000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>19177000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>20538000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>20624000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>20720000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>20781000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>24406000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>24869000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>24750000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>25124000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>28932000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>28916000</v>
       </c>
     </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>77113000</v>
+      </c>
+      <c r="E62" s="3">
         <v>60732000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>60980000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>57030000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>56869000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>57141000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>56990000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>63806000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>63640000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>63535000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>63169000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>63687000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>64176000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>64382000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>65075000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>70075000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>70509000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>70431000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>73189000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>71968000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>72836000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>72359000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>69992000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>71885000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>72090000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>72828000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>72014000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>81583000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>81475000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>81940000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>79914000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>83439000</v>
       </c>
     </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5633,8 +5781,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -5731,8 +5882,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5829,106 +5983,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>192302000</v>
+      </c>
+      <c r="E66" s="3">
         <v>172668000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>171515000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>172556000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>164202000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>170686000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>174018000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>184052000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>190458000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>185556000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>170346000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>176099000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>178718000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>176796000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>175600000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>180643000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>181312000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>173725000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>170947000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>169446000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>169352000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>164967000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>154402000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>164263000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>161568000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>160631000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>161003000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>167151000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>163834000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>167058000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>162989000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>168789000</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5963,8 +6123,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6061,8 +6222,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6159,8 +6323,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6257,8 +6424,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6355,106 +6525,112 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>463294000</v>
+      </c>
+      <c r="E72" s="3">
         <v>458339000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>453927000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>450138000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>444731000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>440552000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>432860000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>423877000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>407902000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>393779000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>392059000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>386952000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>383922000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>382953000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>383943000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>407728000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>412124000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>416919000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>421341000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>419367000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>419913000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>420498000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>421653000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>419155000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>416418000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>415970000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>414540000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>409449000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>408768000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>408707000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>407831000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>409284000</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6551,8 +6727,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6649,8 +6828,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6747,106 +6929,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>268405000</v>
+      </c>
+      <c r="E76" s="3">
         <v>205250000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>204802000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>199703000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>199046000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>198685000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>195049000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>186100000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>177316000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>169215000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>168577000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>160589000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>158571000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>156974000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>157150000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>177400000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>180183000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>182079000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>191650000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>189915000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>191377000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>191222000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>191794000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>190365000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>187222000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>188195000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>187688000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>182276000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>179178000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>177151000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>167325000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>170597000</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6943,209 +7131,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42916</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42825</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42735</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>9240000</v>
+      </c>
+      <c r="E81" s="3">
         <v>8220000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>7630000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>9070000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>7880000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>11430000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>12750000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>19660000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>17850000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>5480000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>8870000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>6750000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>4690000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>2730000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-20070000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-680000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-1080000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-610000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>5690000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>3170000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>3130000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>2350000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>6000000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>6240000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>3950000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>4650000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>8380000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>3970000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>3350000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>4010000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>1680000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>2650000</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7180,106 +7377,110 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>5787000</v>
+      </c>
+      <c r="E83" s="3">
         <v>4812000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>7740000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>4415000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>4242000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>4244000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>5064000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>5642000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>4451000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>4283000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>5661000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>4990000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>4952000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>5004000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>30291000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>4983000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>4916000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>5819000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>4923000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>4873000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>4631000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>4571000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>5028000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>4658000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>4589000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>4470000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>5842000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>4880000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>4652000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>4519000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>8117000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>4605000</v>
       </c>
     </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7376,8 +7577,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7474,8 +7678,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7572,8 +7779,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7670,8 +7880,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7768,106 +7981,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>10560000</v>
+      </c>
+      <c r="E89" s="3">
         <v>14664000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>13682000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>15963000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>9383000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>16341000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>17621000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>24425000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>19963000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>14788000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>17124000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>12091000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>9650000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>9264000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>4005000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>4389000</v>
       </c>
-      <c r="S89" s="3">
-        <v>0</v>
-      </c>
       <c r="T89" s="3">
+        <v>0</v>
+      </c>
+      <c r="U89" s="3">
         <v>6274000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>6352000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>9079000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>5947000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>8338000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>8607000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>11108000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>7780000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>8519000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>7411000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>7535000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>6947000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>8173000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>7396000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>5355000</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7902,106 +8121,110 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-6235000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-5074000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-6228000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-4920000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-5359000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-5412000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-5783000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-4876000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-3837000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-3911000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-4089000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-2840000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-2747000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-2400000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-3629000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-3291000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-4417000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-5945000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-6704000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-6285000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-6173000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-5199000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-6094000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-5204000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-4927000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-3349000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-4501000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-4913000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-3098000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-2890000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-3887000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-3404000</v>
       </c>
     </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8098,8 +8321,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8196,106 +8422,112 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-4869000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-4577000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-5714000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-4279000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-4356000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-4925000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-5355000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-2378000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-3064000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-3945000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-2110000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-3054000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-2716000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-2355000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-3302000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-3709000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-5081000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-6367000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-4264000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-6150000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-6877000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-5793000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-5584000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-3907000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-5096000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-1859000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-6536000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-2555000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-2878000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-3761000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-1672000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-3235000</v>
       </c>
     </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8330,88 +8562,89 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-4285000</v>
+      </c>
+      <c r="E96" s="3">
         <v>-3808000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>-3839000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>-3663000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-3701000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-3738000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-3767000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-3685000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-3727000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-3760000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-3763000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-3720000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-3721000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-3720000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-3715000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-3716000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-3715000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-3719000</v>
-      </c>
-      <c r="U96" s="3">
-        <v>-3716000</v>
       </c>
       <c r="V96" s="3">
         <v>-3716000</v>
       </c>
       <c r="W96" s="3">
+        <v>-3716000</v>
+      </c>
+      <c r="X96" s="3">
         <v>-3715000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-3505000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-3502000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-3503000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-3502000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-3291000</v>
-      </c>
-      <c r="AC96" s="3">
-        <v>-3289000</v>
       </c>
       <c r="AD96" s="3">
         <v>-3289000</v>
@@ -8420,16 +8653,19 @@
         <v>-3289000</v>
       </c>
       <c r="AF96" s="3">
+        <v>-3289000</v>
+      </c>
+      <c r="AG96" s="3">
         <v>-3134000</v>
-      </c>
-      <c r="AG96" s="3">
-        <v>-3133000</v>
       </c>
       <c r="AH96" s="3">
         <v>-3133000</v>
       </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>-3133000</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8526,8 +8762,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8624,8 +8863,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8722,298 +8964,310 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-12558000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-7982000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-9555000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-8059000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-8176000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-8507000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-13937000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-9793000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-8671000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-6713000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-12959000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-7657000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-7022000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-7785000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-5283000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-4494000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>6277000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>8785000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-4456000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-1666000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>548000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-1044000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-5501000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-4959000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-3244000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-5742000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-1837000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-4988000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-5059000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-3246000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-6746000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-1296000</v>
       </c>
     </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-324000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>182000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-209000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>30000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>102000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>872000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-651000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-441000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>142000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-21000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-77000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>38000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>27000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>112000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>70000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-32000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-369000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>106000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-125000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>9000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>43000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-149000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-3000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-135000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>30000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-127000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>232000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>135000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>74000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-414000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-89000</v>
       </c>
     </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-6861000</v>
+      </c>
+      <c r="E102" s="3">
         <v>1781000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1405000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>3416000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-3119000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>3011000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-799000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>11603000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>7787000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>4272000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>2034000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>1303000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-50000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-849000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-4468000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-3744000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>1164000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>8323000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-2262000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>1138000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-373000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>1544000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-2627000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>2239000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-695000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>948000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-1089000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>224000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-855000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>1240000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-1436000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>735000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/XOM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/XOM_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="92">
   <si>
     <t>XOM</t>
   </si>
@@ -656,431 +656,443 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="35" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="36" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43100</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43008</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42916</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42825</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42735</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>89986000</v>
+        <v>88535000</v>
       </c>
       <c r="E8" s="3">
-        <v>80411000</v>
+        <v>91316000</v>
       </c>
       <c r="F8" s="3">
-        <v>81688000</v>
+        <v>81241000</v>
       </c>
       <c r="G8" s="3">
-        <v>88570000</v>
+        <v>82726000</v>
       </c>
       <c r="H8" s="3">
-        <v>80795000</v>
+        <v>89852000</v>
       </c>
       <c r="I8" s="3">
-        <v>83644000</v>
+        <v>81532000</v>
       </c>
       <c r="J8" s="3">
+        <v>84183000</v>
+      </c>
+      <c r="K8" s="3">
         <v>93164000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>106512000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>111265000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>87734000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>81305000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>71892000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>65943000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>57552000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>45738000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>45425000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>32277000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>55134000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>63024000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>63422000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>67491000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>61646000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>68253000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>74187000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>71456000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>65436000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>50832000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>59350000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>56026000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>56474000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>40396000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>56767000</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>61142000</v>
+      </c>
+      <c r="E9" s="3">
         <v>64003000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>56692000</v>
       </c>
-      <c r="F9" s="3">
-        <v>56245000</v>
-      </c>
       <c r="G9" s="3">
+        <v>53558000</v>
+      </c>
+      <c r="H9" s="3">
         <v>61772000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>56458000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>55439000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>61126000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>71514000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>76299000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>62629000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>56272000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>48464000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>45800000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>40663000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>32041000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>31053000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>20964000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>40380000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>44254000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>44138000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>48464000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>43771000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>46957000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>50873000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>50245000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>44779000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>28979000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>45248000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>43843000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>43267000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>21193000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>41181000</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>25983000</v>
+        <v>27393000</v>
       </c>
       <c r="E10" s="3">
-        <v>23719000</v>
+        <v>27313000</v>
       </c>
       <c r="F10" s="3">
-        <v>25443000</v>
+        <v>24549000</v>
       </c>
       <c r="G10" s="3">
-        <v>26798000</v>
+        <v>29168000</v>
       </c>
       <c r="H10" s="3">
-        <v>24337000</v>
+        <v>28080000</v>
       </c>
       <c r="I10" s="3">
-        <v>28205000</v>
+        <v>25074000</v>
       </c>
       <c r="J10" s="3">
+        <v>28744000</v>
+      </c>
+      <c r="K10" s="3">
         <v>32038000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>34998000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>34966000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>25105000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>25033000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>23428000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>20143000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>16889000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>13697000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>14372000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>11313000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>14754000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>18770000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>19284000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>19027000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>17875000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>21296000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>23314000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>21211000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>20657000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>21853000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>14102000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>12183000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>13207000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>19203000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>15586000</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1116,109 +1128,113 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3">
-        <v>153000</v>
-      </c>
-      <c r="E12" s="3">
-        <v>148000</v>
-      </c>
-      <c r="F12" s="3">
-        <v>139000</v>
+      <c r="D12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="G12" s="3">
-        <v>338000</v>
-      </c>
-      <c r="H12" s="3">
-        <v>133000</v>
-      </c>
-      <c r="I12" s="3">
-        <v>141000</v>
-      </c>
-      <c r="J12" s="3">
+        <v>879000</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K12" s="3">
         <v>348000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>218000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>286000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>173000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>524000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>190000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>176000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>164000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>595000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>188000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>214000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>288000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>357000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>299000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>333000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>280000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>555000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>292000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>332000</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>287000</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>703000</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>284000</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>514000</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>289000</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>340000</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>327000</v>
       </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1318,8 +1334,11 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1332,8 +1351,8 @@
       <c r="F14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>24</v>
+      <c r="G14" s="3">
+        <v>2787000</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>24</v>
@@ -1341,8 +1360,8 @@
       <c r="I14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="J14" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1351,10 +1370,10 @@
         <v>0</v>
       </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>4600000</v>
-      </c>
-      <c r="N14" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>24</v>
@@ -1365,26 +1384,26 @@
       <c r="Q14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="R14" s="3">
+      <c r="R14" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="S14" s="3">
         <v>24875000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>62000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>64000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>910000</v>
-      </c>
-      <c r="V14" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="W14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
+      <c r="X14" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="Y14" s="3">
         <v>0</v>
@@ -1419,109 +1438,115 @@
       <c r="AI14" s="3">
         <v>0</v>
       </c>
+      <c r="AJ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>6258000</v>
+      </c>
+      <c r="E15" s="3">
         <v>5787000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>4812000</v>
       </c>
-      <c r="F15" s="3">
-        <v>7740000</v>
-      </c>
       <c r="G15" s="3">
+        <v>4440000</v>
+      </c>
+      <c r="H15" s="3">
         <v>4415000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>4242000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>4244000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>5064000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>5642000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>4451000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>4283000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>5661000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>4990000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>4952000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>5004000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>5416000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>4921000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>4852000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>4909000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>4923000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>4873000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>4631000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>4571000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>5028000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>4658000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>4589000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>4470000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>5842000</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>4880000</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>4652000</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>4519000</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>8117000</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>4605000</v>
       </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1554,210 +1579,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>77794000</v>
+        <v>76783000</v>
       </c>
       <c r="E17" s="3">
-        <v>69663000</v>
+        <v>79124000</v>
       </c>
       <c r="F17" s="3">
-        <v>71956000</v>
+        <v>70493000</v>
       </c>
       <c r="G17" s="3">
-        <v>76159000</v>
+        <v>70147000</v>
       </c>
       <c r="H17" s="3">
-        <v>70272000</v>
+        <v>76892000</v>
       </c>
       <c r="I17" s="3">
-        <v>69063000</v>
+        <v>71009000</v>
       </c>
       <c r="J17" s="3">
+        <v>69602000</v>
+      </c>
+      <c r="K17" s="3">
         <v>74720000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>85513000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>89826000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>81528000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>73015000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>63966000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>61181000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>55297000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>72840000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>46292000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>33928000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>56167000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>60527000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>60061000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>64243000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>59155000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>63559000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>67325000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>66842000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>60767000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>48832000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>55406000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>53763000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>52607000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>42224000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>55345000</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>11752000</v>
+      </c>
+      <c r="E18" s="3">
         <v>12192000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>10748000</v>
       </c>
-      <c r="F18" s="3">
-        <v>9732000</v>
-      </c>
       <c r="G18" s="3">
-        <v>12411000</v>
+        <v>12579000</v>
       </c>
       <c r="H18" s="3">
+        <v>12960000</v>
+      </c>
+      <c r="I18" s="3">
         <v>10523000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>14581000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>18444000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>20999000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>21439000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>6206000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>8290000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>7926000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>4762000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>2255000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-27102000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-867000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-1651000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-1033000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>2497000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>3361000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>3248000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>2491000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>4694000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>6862000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>4614000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>4669000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>2000000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>3944000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>2263000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>3867000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-1828000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>1422000</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1793,513 +1825,529 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>1744000</v>
+        <v>-1481000</v>
       </c>
       <c r="E20" s="3">
-        <v>1842000</v>
+        <v>-1744000</v>
       </c>
       <c r="F20" s="3">
-        <v>1165000</v>
+        <v>-1842000</v>
       </c>
       <c r="G20" s="3">
-        <v>1457000</v>
+        <v>-1105000</v>
       </c>
       <c r="H20" s="3">
-        <v>1382000</v>
+        <v>-908000</v>
       </c>
       <c r="I20" s="3">
-        <v>2381000</v>
+        <v>-1382000</v>
       </c>
       <c r="J20" s="3">
+        <v>-2381000</v>
+      </c>
+      <c r="K20" s="3">
         <v>605000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>4632000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>3688000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>2538000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>3660000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>1894000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>1799000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>1595000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>802000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>774000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>328000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>1024000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>4149000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>1627000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>1600000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>1979000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>3642000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>2418000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>2045000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>2775000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>1203000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>1750000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>2051000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>2197000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>2640000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>1910000</v>
       </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>19491000</v>
+      </c>
+      <c r="E21" s="3">
         <v>19723000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>17402000</v>
       </c>
-      <c r="F21" s="3">
-        <v>18637000</v>
-      </c>
       <c r="G21" s="3">
+        <v>18124000</v>
+      </c>
+      <c r="H21" s="3">
         <v>18283000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>16147000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>21206000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>24113000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>31273000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>29578000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>13027000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>17611000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>14810000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>11513000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>8854000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>3991000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>4890000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>3593000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>5810000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>11569000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>9861000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>9479000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>9041000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>13364000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>13938000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>11248000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>11914000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>9045000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>10574000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>8966000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>10583000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>8929000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>7937000</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>207000</v>
+      </c>
+      <c r="E22" s="3">
         <v>271000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>221000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>272000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>169000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>249000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>159000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>207000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>209000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>194000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>188000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>221000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>214000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>254000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>258000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>313000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>279000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>317000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>249000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>232000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>267000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>216000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>181000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>215000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>200000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>147000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>204000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>186000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>111000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>158000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>146000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>195000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>106000</v>
       </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>13026000</v>
+      </c>
+      <c r="E23" s="3">
         <v>13665000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>12369000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>10625000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>13699000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>11656000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>16803000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>18842000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>25422000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>24933000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>8556000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>11729000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>9606000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>6307000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>3592000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-26613000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-372000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-1640000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-258000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>6414000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>4721000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>4632000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>4289000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>8121000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>9080000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>6512000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>7240000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>3017000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>5583000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>4156000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>5918000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>617000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>3226000</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>4055000</v>
+      </c>
+      <c r="E24" s="3">
         <v>4094000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>3803000</v>
       </c>
-      <c r="F24" s="3">
-        <v>2637000</v>
-      </c>
       <c r="G24" s="3">
+        <v>2613000</v>
+      </c>
+      <c r="H24" s="3">
         <v>4353000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>3503000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>4960000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>5817000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>5224000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>6359000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>2806000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>2703000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>2664000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1526000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>796000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-5985000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>337000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-471000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>512000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>1424000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>1474000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>1241000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>1883000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>1936000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>2634000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>2526000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>2457000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>550000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>1498000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>892000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>1828000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>-1407000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>337000</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2399,210 +2447,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>8971000</v>
+      </c>
+      <c r="E26" s="3">
         <v>9571000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>8566000</v>
       </c>
-      <c r="F26" s="3">
-        <v>7988000</v>
-      </c>
       <c r="G26" s="3">
+        <v>8012000</v>
+      </c>
+      <c r="H26" s="3">
         <v>9346000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>8153000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>11843000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>13025000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>20198000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>18574000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>5750000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>9026000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>6942000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>4781000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>2796000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-20628000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-709000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-1169000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-770000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>4990000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>3247000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>3391000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>2406000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>6185000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>6446000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>3986000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>4783000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>2467000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>4085000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>3264000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>4090000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>2024000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>2889000</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>8610000</v>
+      </c>
+      <c r="E27" s="3">
         <v>9240000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>8220000</v>
       </c>
-      <c r="F27" s="3">
-        <v>7606000</v>
-      </c>
       <c r="G27" s="3">
+        <v>7630000</v>
+      </c>
+      <c r="H27" s="3">
         <v>9070000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>7880000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>11430000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>12720000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>19660000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>17850000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>5480000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>8817000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>6750000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>4690000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>2730000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-20095000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-680000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-1080000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-610000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>4950000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>3170000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>3130000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>2350000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>5979000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>6240000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>3950000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>4650000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>2438000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>3970000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>3350000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>4010000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>1680000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>2650000</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -2702,34 +2759,37 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>24</v>
+      <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
       </c>
       <c r="F29" s="3">
-        <v>24000</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>24</v>
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
+        <v>0</v>
       </c>
       <c r="J29" s="3">
+        <v>0</v>
+      </c>
+      <c r="K29" s="3">
         <v>30000</v>
-      </c>
-      <c r="K29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="L29" s="3" t="s">
         <v>24</v>
@@ -2737,11 +2797,11 @@
       <c r="M29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="N29" s="3">
+      <c r="N29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="O29" s="3">
         <v>53000</v>
-      </c>
-      <c r="O29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="P29" s="3" t="s">
         <v>24</v>
@@ -2749,11 +2809,11 @@
       <c r="Q29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="R29" s="3">
+      <c r="R29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="S29" s="3">
         <v>25000</v>
-      </c>
-      <c r="S29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="T29" s="3" t="s">
         <v>24</v>
@@ -2761,11 +2821,11 @@
       <c r="U29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="V29" s="3">
+      <c r="V29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="W29" s="3">
         <v>740000</v>
-      </c>
-      <c r="W29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="X29" s="3" t="s">
         <v>24</v>
@@ -2773,11 +2833,11 @@
       <c r="Y29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="Z29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AA29" s="3">
         <v>21000</v>
-      </c>
-      <c r="AA29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>24</v>
@@ -2785,11 +2845,11 @@
       <c r="AC29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AD29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AE29" s="3">
         <v>5942000</v>
-      </c>
-      <c r="AE29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AF29" s="3" t="s">
         <v>24</v>
@@ -2803,8 +2863,11 @@
       <c r="AI29" s="3" t="s">
         <v>24</v>
       </c>
+      <c r="AJ29" s="3" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2904,8 +2967,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3005,210 +3071,219 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-1744000</v>
+        <v>1481000</v>
       </c>
       <c r="E32" s="3">
-        <v>-1842000</v>
+        <v>1744000</v>
       </c>
       <c r="F32" s="3">
-        <v>-1165000</v>
+        <v>1842000</v>
       </c>
       <c r="G32" s="3">
-        <v>-1457000</v>
+        <v>1105000</v>
       </c>
       <c r="H32" s="3">
-        <v>-1382000</v>
+        <v>908000</v>
       </c>
       <c r="I32" s="3">
-        <v>-2381000</v>
+        <v>1382000</v>
       </c>
       <c r="J32" s="3">
+        <v>2381000</v>
+      </c>
+      <c r="K32" s="3">
         <v>-605000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-4632000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-3688000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-2538000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-3660000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-1894000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-1799000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-1595000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-802000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-774000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-328000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-1024000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-4149000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-1627000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-1600000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-1979000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-3642000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-2418000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-2045000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-2775000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-1203000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-1750000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-2051000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-2197000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-2640000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-1910000</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>8610000</v>
+      </c>
+      <c r="E33" s="3">
         <v>9240000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>8220000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>7630000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>9070000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>7880000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>11430000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>12750000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>19660000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>17850000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>5480000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>8870000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>6750000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>4690000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>2730000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-20070000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-680000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-1080000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-610000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>5690000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>3170000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>3130000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>2350000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>6000000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>6240000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>3950000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>4650000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>8380000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>3970000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>3350000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>4010000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>1680000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>2650000</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3308,215 +3383,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>8610000</v>
+      </c>
+      <c r="E35" s="3">
         <v>9240000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>8220000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>7630000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>9070000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>7880000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>11430000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>12750000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>19660000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>17850000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>5480000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>8870000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>6750000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>4690000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>2730000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-20070000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-680000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-1080000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-610000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>5690000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>3170000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>3130000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>2350000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>6000000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>6240000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>3950000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>4650000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>8380000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>3970000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>3350000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>4010000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>1680000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>2650000</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43100</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43008</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42916</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42825</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42735</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3552,8 +3636,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3589,109 +3674,113 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>26926000</v>
+      </c>
+      <c r="E41" s="3">
         <v>26460000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>33320000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>31539000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>32944000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>29528000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>32651000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>29640000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>30407000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>18861000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>11074000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>6802000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>4768000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>3465000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>3515000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>4364000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>8832000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>12576000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>11412000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>3089000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>5351000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>4213000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>4586000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>3042000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>5669000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>3430000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>4125000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>3177000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>4266000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>4042000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>4897000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>3657000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>5093000</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3791,31 +3880,34 @@
       <c r="AI42" s="3">
         <v>0</v>
       </c>
+      <c r="AJ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>0</v>
+        <v>41505000</v>
       </c>
       <c r="E43" s="3">
-        <v>0</v>
+        <v>43071000</v>
       </c>
       <c r="F43" s="3">
-        <v>0</v>
+        <v>40366000</v>
       </c>
       <c r="G43" s="3">
-        <v>0</v>
+        <v>38015000</v>
       </c>
       <c r="H43" s="3">
-        <v>0</v>
+        <v>41814000</v>
       </c>
       <c r="I43" s="3">
-        <v>0</v>
+        <v>35915000</v>
       </c>
       <c r="J43" s="3">
-        <v>0</v>
+        <v>38808000</v>
       </c>
       <c r="K43" s="3">
         <v>0</v>
@@ -3824,581 +3916,599 @@
         <v>0</v>
       </c>
       <c r="M43" s="3">
+        <v>0</v>
+      </c>
+      <c r="N43" s="3">
         <v>42142000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>32383000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>29516000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>28540000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>24755000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>20581000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>19974000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>19036000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>20871000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>26966000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>25308000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>27132000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>27105000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>24701000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>27880000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>26993000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>24686000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>25597000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>23263000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>21289000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>21842000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>21394000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>20388000</v>
       </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>23875000</v>
+      </c>
+      <c r="E44" s="3">
         <v>24503000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>23491000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>25120000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>24450000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>24249000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>23642000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>24435000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>24096000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>23585000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>22177000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>18780000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>19607000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>19275000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>18357000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>18850000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>17885000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>19657000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>16501000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>18528000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>17590000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>18835000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>18332000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>18958000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>18761000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>18483000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>18048000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>16992000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>16743000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>15305000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>14873000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>15080000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>15342000</v>
       </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>2204000</v>
+        <v>1997000</v>
       </c>
       <c r="E45" s="3">
-        <v>2200000</v>
+        <v>2176000</v>
       </c>
       <c r="F45" s="3">
-        <v>1935000</v>
+        <v>2171000</v>
       </c>
       <c r="G45" s="3">
-        <v>1934000</v>
+        <v>1906000</v>
       </c>
       <c r="H45" s="3">
-        <v>2068000</v>
+        <v>1905000</v>
       </c>
       <c r="I45" s="3">
-        <v>2123000</v>
+        <v>2039000</v>
       </c>
       <c r="J45" s="3">
+        <v>2098000</v>
+      </c>
+      <c r="K45" s="3">
         <v>1807000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2375000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2654000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1862000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1189000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1664000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1562000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1568000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1098000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>2002000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1747000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1465000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1469000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1759000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1563000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1553000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1272000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1665000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1649000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1456000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1368000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>1480000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>1544000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>1519000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>1285000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>2122000</v>
       </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>94349000</v>
+      </c>
+      <c r="E46" s="3">
         <v>96238000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>99377000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>96609000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>101142000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>91760000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>97224000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>97631000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>99289000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>93163000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>77255000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>59154000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>55555000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>52842000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>48195000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>44893000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>48693000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>53016000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>50249000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>50052000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>50008000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>51743000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>51576000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>47973000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>53975000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>50555000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>48315000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>47134000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>45752000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>42180000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>43131000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>41416000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>42945000</v>
       </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>47948000</v>
+        <v>41447000</v>
       </c>
       <c r="E47" s="3">
-        <v>47608000</v>
+        <v>40791000</v>
       </c>
       <c r="F47" s="3">
-        <v>47630000</v>
+        <v>39995000</v>
       </c>
       <c r="G47" s="3">
-        <v>48066000</v>
+        <v>34257000</v>
       </c>
       <c r="H47" s="3">
-        <v>47273000</v>
+        <v>40062000</v>
       </c>
       <c r="I47" s="3">
-        <v>49044000</v>
+        <v>39564000</v>
       </c>
       <c r="J47" s="3">
+        <v>40825000</v>
+      </c>
+      <c r="K47" s="3">
         <v>49793000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>50235000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>46820000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>46329000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>45195000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>45641000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>44774000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>44181000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>43515000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>43609000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>43192000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>42981000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>43164000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>42920000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>42533000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>42068000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>40790000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>40427000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>39691000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>40350000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>39160000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>37649000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>37719000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>38268000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>35102000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>35553000</v>
       </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>299543000</v>
+      </c>
+      <c r="E48" s="3">
         <v>298283000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>213723000</v>
       </c>
-      <c r="F48" s="3">
-        <v>214940000</v>
-      </c>
       <c r="G48" s="3">
+        <v>221789000</v>
+      </c>
+      <c r="H48" s="3">
         <v>205862000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>206736000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>206023000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>204692000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>203102000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>209159000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>212773000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>216552000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>218795000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>223012000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>224641000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>227553000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>250496000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>250524000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>248409000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>259651000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>257065000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>257118000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>253003000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>247101000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>249153000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>248209000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>250352000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>252630000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>255556000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>252987000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>253147000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>244224000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>251923000</v>
       </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4498,8 +4608,11 @@
       <c r="AI49" s="3">
         <v>0</v>
       </c>
+      <c r="AJ49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4599,8 +4712,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4700,109 +4816,115 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>18238000</v>
+        <v>26577000</v>
       </c>
       <c r="E52" s="3">
-        <v>17210000</v>
+        <v>25395000</v>
       </c>
       <c r="F52" s="3">
-        <v>17138000</v>
+        <v>24823000</v>
       </c>
       <c r="G52" s="3">
-        <v>17189000</v>
+        <v>20025000</v>
       </c>
       <c r="H52" s="3">
-        <v>17479000</v>
+        <v>25193000</v>
       </c>
       <c r="I52" s="3">
-        <v>17080000</v>
+        <v>25188000</v>
       </c>
       <c r="J52" s="3">
+        <v>25299000</v>
+      </c>
+      <c r="K52" s="3">
         <v>16951000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>17526000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>18632000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>18414000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>18022000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>16697000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>16661000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>16753000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>16789000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>15245000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>14763000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>14165000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>9730000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>9368000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>9335000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>9542000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>10332000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>11073000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>10335000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>9809000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>9767000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>10470000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>10126000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>9663000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>9572000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>8965000</v>
       </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4902,109 +5024,115 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>461916000</v>
+      </c>
+      <c r="E54" s="3">
         <v>460707000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>377918000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>376317000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>372259000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>363248000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>369371000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>369067000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>370152000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>367774000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>354771000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>338923000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>336688000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>337289000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>333770000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>332750000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>358043000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>361495000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>355804000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>362597000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>359361000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>360729000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>356189000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>346196000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>354628000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>348790000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>348826000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>348691000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>349427000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>343012000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>344209000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>330314000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>339386000</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5040,8 +5168,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5077,614 +5206,633 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>60518000</v>
+      </c>
+      <c r="E57" s="3">
         <v>60107000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>59531000</v>
       </c>
-      <c r="F57" s="3">
-        <v>58037000</v>
-      </c>
       <c r="G57" s="3">
+        <v>31249000</v>
+      </c>
+      <c r="H57" s="3">
         <v>62257000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>54404000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>59935000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>63197000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>62550000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>67958000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>63501000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>50766000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>47257000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>45780000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>41017000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>35221000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>33340000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>33216000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>35815000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>40605000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>39336000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>40324000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>41190000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>37268000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>41714000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>38490000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>37207000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>36796000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>34698000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>31100000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>32069000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>31193000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>30027000</v>
       </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>5632000</v>
+      </c>
+      <c r="E58" s="3">
         <v>6621000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>8227000</v>
       </c>
-      <c r="F58" s="3">
-        <v>4090000</v>
-      </c>
       <c r="G58" s="3">
+        <v>5712000</v>
+      </c>
+      <c r="H58" s="3">
         <v>4743000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>3929000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2296000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>634000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>6182000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>7367000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>4886000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>4276000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>12966000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>15293000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>18185000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>20458000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>21911000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>22952000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>27755000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>20593000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>21219000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>26227000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>21828000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>17258000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>19413000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>20500000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>19836000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>17930000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>15741000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>17185000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>18483000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>13830000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>17239000</v>
       </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>3843000</v>
+      </c>
+      <c r="E59" s="3">
         <v>4035000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>4163000</v>
       </c>
-      <c r="F59" s="3">
-        <v>3189000</v>
-      </c>
       <c r="G59" s="3">
+        <v>24538000</v>
+      </c>
+      <c r="H59" s="3">
         <v>4186000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>3482000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>4435000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>5214000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>5325000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>4785000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>3672000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1601000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1633000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1165000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>948000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>684000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1217000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1102000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1203000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>2791000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>3640000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>3736000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>3614000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>2612000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>4161000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>3457000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>3263000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>3045000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>3338000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>2664000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>2822000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>2615000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>2755000</v>
       </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>69993000</v>
+      </c>
+      <c r="E60" s="3">
         <v>70763000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>71921000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>65316000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>71186000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>61815000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>66666000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>69045000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>74057000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>80110000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>72059000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>56643000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>61856000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>62238000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>60150000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>56363000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>56468000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>57270000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>64773000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>63989000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>64195000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>70287000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>66632000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>57138000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>65288000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>62447000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>60306000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>57771000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>53777000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>50949000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>53374000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>47638000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>50021000</v>
       </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>36918000</v>
+      </c>
+      <c r="E61" s="3">
         <v>36565000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>32213000</v>
       </c>
-      <c r="F61" s="3">
-        <v>37483000</v>
-      </c>
       <c r="G61" s="3">
+        <v>41997000</v>
+      </c>
+      <c r="H61" s="3">
         <v>36510000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>37567000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>39150000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>40559000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>39246000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>39516000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>42651000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>43428000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>43639000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>45319000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>45137000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>47182000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>46888000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>46563000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>31857000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>26481000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>26089000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>19141000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>19177000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>20538000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>20624000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>20720000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>20781000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>24406000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>24869000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>24750000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>25124000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>28932000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>28916000</v>
       </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>77113000</v>
+        <v>27647000</v>
       </c>
       <c r="E62" s="3">
-        <v>60732000</v>
+        <v>26635000</v>
       </c>
       <c r="F62" s="3">
-        <v>60980000</v>
+        <v>26151000</v>
       </c>
       <c r="G62" s="3">
-        <v>57030000</v>
+        <v>21518000</v>
       </c>
       <c r="H62" s="3">
-        <v>56869000</v>
+        <v>22944000</v>
       </c>
       <c r="I62" s="3">
-        <v>57141000</v>
+        <v>23131000</v>
       </c>
       <c r="J62" s="3">
+        <v>23763000</v>
+      </c>
+      <c r="K62" s="3">
         <v>56990000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>63806000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>63640000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>63535000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>63169000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>63687000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>64176000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>64382000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>65075000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>70075000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>70509000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>70431000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>73189000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>71968000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>72836000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>72359000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>69992000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>71885000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>72090000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>72828000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>72014000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>81583000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>81475000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>81940000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>79914000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>83439000</v>
       </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5784,8 +5932,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -5885,8 +6036,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5986,109 +6140,115 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>192302000</v>
+        <v>185516000</v>
       </c>
       <c r="E66" s="3">
-        <v>172668000</v>
+        <v>184441000</v>
       </c>
       <c r="F66" s="3">
-        <v>171515000</v>
+        <v>164866000</v>
       </c>
       <c r="G66" s="3">
-        <v>172556000</v>
+        <v>163779000</v>
       </c>
       <c r="H66" s="3">
-        <v>164202000</v>
+        <v>164726000</v>
       </c>
       <c r="I66" s="3">
-        <v>170686000</v>
+        <v>156251000</v>
       </c>
       <c r="J66" s="3">
+        <v>162957000</v>
+      </c>
+      <c r="K66" s="3">
         <v>174018000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>184052000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>190458000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>185556000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>170346000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>176099000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>178718000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>176796000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>175600000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>180643000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>181312000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>173725000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>170947000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>169446000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>169352000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>164967000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>154402000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>164263000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>161568000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>160631000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>161003000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>167151000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>163834000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>167058000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>162989000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>168789000</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6124,8 +6284,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6225,8 +6386,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6326,8 +6490,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6427,8 +6594,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6528,109 +6698,115 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>467664000</v>
+      </c>
+      <c r="E72" s="3">
         <v>463294000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>458339000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>453927000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>450138000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>444731000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>440552000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>432860000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>423877000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>407902000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>393779000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>392059000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>386952000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>383922000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>382953000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>383943000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>407728000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>412124000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>416919000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>421341000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>419367000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>419913000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>420498000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>421653000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>419155000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>416418000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>415970000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>414540000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>409449000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>408768000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>408707000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>407831000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>409284000</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6730,8 +6906,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6831,8 +7010,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6932,109 +7114,115 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>268592000</v>
+      </c>
+      <c r="E76" s="3">
         <v>268405000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>205250000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>204802000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>199703000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>199046000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>198685000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>195049000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>186100000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>177316000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>169215000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>168577000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>160589000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>158571000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>156974000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>157150000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>177400000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>180183000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>182079000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>191650000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>189915000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>191377000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>191222000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>191794000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>190365000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>187222000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>188195000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>187688000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>182276000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>179178000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>177151000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>167325000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>170597000</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7134,215 +7322,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43100</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43008</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42916</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42825</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42735</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>8610000</v>
+      </c>
+      <c r="E81" s="3">
         <v>9240000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>8220000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>7630000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>9070000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>7880000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>11430000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>12750000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>19660000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>17850000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>5480000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>8870000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>6750000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>4690000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>2730000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-20070000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-680000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-1080000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-610000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>5690000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>3170000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>3130000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>2350000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>6000000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>6240000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>3950000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>4650000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>8380000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>3970000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>3350000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>4010000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>1680000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>2650000</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7378,109 +7575,113 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>5787000</v>
+        <v>4415000</v>
       </c>
       <c r="E83" s="3">
-        <v>4812000</v>
+        <v>4242000</v>
       </c>
       <c r="F83" s="3">
-        <v>7740000</v>
+        <v>4244000</v>
       </c>
       <c r="G83" s="3">
-        <v>4415000</v>
+        <v>-3108000</v>
       </c>
       <c r="H83" s="3">
-        <v>4242000</v>
+        <v>12289000</v>
       </c>
       <c r="I83" s="3">
-        <v>4244000</v>
+        <v>4451000</v>
       </c>
       <c r="J83" s="3">
+        <v>5908000</v>
+      </c>
+      <c r="K83" s="3">
         <v>5064000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>5642000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>4451000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>4283000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>5661000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>4990000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>4952000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>5004000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>30291000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>4983000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>4916000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>5819000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>4923000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>4873000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>4631000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>4571000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>5028000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>4658000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>4589000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>4470000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>5842000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>4880000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>4652000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>4519000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>8117000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>4605000</v>
       </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7580,8 +7781,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7681,8 +7885,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7782,8 +7989,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7883,8 +8093,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7984,109 +8197,115 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>17569000</v>
+      </c>
+      <c r="E89" s="3">
         <v>10560000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>14664000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>13682000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>15963000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>9383000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>16341000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>17621000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>24425000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>19963000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>14788000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>17124000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>12091000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>9650000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>9264000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>4005000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>4389000</v>
       </c>
-      <c r="T89" s="3">
-        <v>0</v>
-      </c>
       <c r="U89" s="3">
+        <v>0</v>
+      </c>
+      <c r="V89" s="3">
         <v>6274000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>6352000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>9079000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>5947000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>8338000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>8607000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>11108000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>7780000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>8519000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>7411000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>7535000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>6947000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>8173000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>7396000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>5355000</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8122,109 +8341,113 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-6160000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-6235000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-5074000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-6228000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-4920000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-5359000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-5412000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-5783000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-4876000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-3837000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-3911000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-4089000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-2840000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-2747000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-2400000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-3629000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-3291000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-4417000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-5945000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-6704000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-6285000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-6173000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-5199000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-6094000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-5204000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-4927000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-3349000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-4501000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-4913000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-3098000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-2890000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-3887000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-3404000</v>
       </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8324,8 +8547,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8425,109 +8651,115 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-6240000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-4869000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-4577000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-5714000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-4279000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-4356000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-4925000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-5355000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-2378000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-3064000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-3945000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-2110000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-3054000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-2716000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-2355000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-3302000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-3709000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-5081000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-6367000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-4264000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-6150000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-6877000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-5793000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-5584000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-3907000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-5096000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-1859000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-6536000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-2555000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-2878000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-3761000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-1672000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-3235000</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8563,91 +8795,92 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-4285000</v>
+        <v>4240000</v>
       </c>
       <c r="E96" s="3">
-        <v>-3808000</v>
+        <v>4285000</v>
       </c>
       <c r="F96" s="3">
-        <v>-3839000</v>
+        <v>3808000</v>
       </c>
       <c r="G96" s="3">
-        <v>-3663000</v>
+        <v>3839000</v>
       </c>
       <c r="H96" s="3">
-        <v>-3701000</v>
+        <v>3663000</v>
       </c>
       <c r="I96" s="3">
-        <v>-3738000</v>
+        <v>3701000</v>
       </c>
       <c r="J96" s="3">
+        <v>3738000</v>
+      </c>
+      <c r="K96" s="3">
         <v>-3767000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-3685000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-3727000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-3760000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-3763000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-3720000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-3721000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-3720000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-3715000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-3716000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-3715000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-3719000</v>
-      </c>
-      <c r="V96" s="3">
-        <v>-3716000</v>
       </c>
       <c r="W96" s="3">
         <v>-3716000</v>
       </c>
       <c r="X96" s="3">
+        <v>-3716000</v>
+      </c>
+      <c r="Y96" s="3">
         <v>-3715000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-3505000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-3502000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-3503000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-3502000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-3291000</v>
-      </c>
-      <c r="AD96" s="3">
-        <v>-3289000</v>
       </c>
       <c r="AE96" s="3">
         <v>-3289000</v>
@@ -8656,16 +8889,19 @@
         <v>-3289000</v>
       </c>
       <c r="AG96" s="3">
+        <v>-3289000</v>
+      </c>
+      <c r="AH96" s="3">
         <v>-3134000</v>
-      </c>
-      <c r="AH96" s="3">
-        <v>-3133000</v>
       </c>
       <c r="AI96" s="3">
         <v>-3133000</v>
       </c>
+      <c r="AJ96" s="3">
+        <v>-3133000</v>
+      </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8765,8 +9001,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8866,8 +9105,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8967,307 +9209,319 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-11106000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-12558000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-7982000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-9555000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-8059000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-8176000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-8507000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-13937000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-9793000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-8671000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-6713000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-12959000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-7657000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-7022000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-7785000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-5283000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-4494000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>6277000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>8785000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-4456000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-1666000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>548000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-1044000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-5501000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-4959000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-3244000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-5742000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-1837000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-4988000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-5059000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-3246000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-6746000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-1296000</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>6000</v>
+        <v>-209000</v>
       </c>
       <c r="E101" s="3">
-        <v>-324000</v>
+        <v>30000</v>
       </c>
       <c r="F101" s="3">
-        <v>182000</v>
+        <v>102000</v>
       </c>
       <c r="G101" s="3">
-        <v>-209000</v>
+        <v>872000</v>
       </c>
       <c r="H101" s="3">
+        <v>-651000</v>
+      </c>
+      <c r="I101" s="3">
+        <v>-441000</v>
+      </c>
+      <c r="J101" s="3">
+        <v>142000</v>
+      </c>
+      <c r="K101" s="3">
+        <v>872000</v>
+      </c>
+      <c r="L101" s="3">
+        <v>-651000</v>
+      </c>
+      <c r="M101" s="3">
+        <v>-441000</v>
+      </c>
+      <c r="N101" s="3">
+        <v>142000</v>
+      </c>
+      <c r="O101" s="3">
+        <v>-21000</v>
+      </c>
+      <c r="P101" s="3">
+        <v>-77000</v>
+      </c>
+      <c r="Q101" s="3">
+        <v>38000</v>
+      </c>
+      <c r="R101" s="3">
+        <v>27000</v>
+      </c>
+      <c r="S101" s="3">
+        <v>112000</v>
+      </c>
+      <c r="T101" s="3">
+        <v>70000</v>
+      </c>
+      <c r="U101" s="3">
+        <v>-32000</v>
+      </c>
+      <c r="V101" s="3">
+        <v>-369000</v>
+      </c>
+      <c r="W101" s="3">
+        <v>106000</v>
+      </c>
+      <c r="X101" s="3">
+        <v>-125000</v>
+      </c>
+      <c r="Y101" s="3">
+        <v>9000</v>
+      </c>
+      <c r="Z101" s="3">
+        <v>43000</v>
+      </c>
+      <c r="AA101" s="3">
+        <v>-149000</v>
+      </c>
+      <c r="AB101" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="AC101" s="3">
+        <v>-135000</v>
+      </c>
+      <c r="AD101" s="3">
         <v>30000</v>
       </c>
-      <c r="I101" s="3">
-        <v>102000</v>
-      </c>
-      <c r="J101" s="3">
-        <v>872000</v>
-      </c>
-      <c r="K101" s="3">
-        <v>-651000</v>
-      </c>
-      <c r="L101" s="3">
-        <v>-441000</v>
-      </c>
-      <c r="M101" s="3">
-        <v>142000</v>
-      </c>
-      <c r="N101" s="3">
-        <v>-21000</v>
-      </c>
-      <c r="O101" s="3">
-        <v>-77000</v>
-      </c>
-      <c r="P101" s="3">
-        <v>38000</v>
-      </c>
-      <c r="Q101" s="3">
-        <v>27000</v>
-      </c>
-      <c r="R101" s="3">
-        <v>112000</v>
-      </c>
-      <c r="S101" s="3">
-        <v>70000</v>
-      </c>
-      <c r="T101" s="3">
-        <v>-32000</v>
-      </c>
-      <c r="U101" s="3">
-        <v>-369000</v>
-      </c>
-      <c r="V101" s="3">
-        <v>106000</v>
-      </c>
-      <c r="W101" s="3">
-        <v>-125000</v>
-      </c>
-      <c r="X101" s="3">
-        <v>9000</v>
-      </c>
-      <c r="Y101" s="3">
-        <v>43000</v>
-      </c>
-      <c r="Z101" s="3">
-        <v>-149000</v>
-      </c>
-      <c r="AA101" s="3">
-        <v>-3000</v>
-      </c>
-      <c r="AB101" s="3">
-        <v>-135000</v>
-      </c>
-      <c r="AC101" s="3">
-        <v>30000</v>
-      </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-127000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>232000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>135000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>74000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-414000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-89000</v>
       </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>484000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-6861000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1781000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1405000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>3416000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-3119000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>3011000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-799000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>11603000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>7787000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>4272000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>2034000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>1303000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-50000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-849000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-4468000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-3744000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>1164000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>8323000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-2262000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>1138000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-373000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>1544000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-2627000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>2239000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-695000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>948000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-1089000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>224000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-855000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>1240000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-1436000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>735000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/XOM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/XOM_QTR_FIN.xlsx
@@ -656,443 +656,455 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="36" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="37" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43100</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43008</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42916</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42825</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>79476000</v>
+      </c>
+      <c r="E8" s="3">
         <v>88535000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>91316000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>81241000</v>
       </c>
-      <c r="G8" s="3">
-        <v>82726000</v>
-      </c>
       <c r="H8" s="3">
+        <v>81098000</v>
+      </c>
+      <c r="I8" s="3">
         <v>89852000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>81532000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>84183000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>93164000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>106512000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>111265000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>87734000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>81305000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>71892000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>65943000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>57552000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>45738000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>45425000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>32277000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>55134000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>63024000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>63422000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>67491000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>61646000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>68253000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>74187000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>71456000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>65436000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>50832000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>59350000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>56026000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>56474000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>40396000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>56767000</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>54064000</v>
+      </c>
+      <c r="E9" s="3">
         <v>61142000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>64003000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>56692000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>53558000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>61772000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>56458000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>55439000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>61126000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>71514000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>76299000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>62629000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>56272000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>48464000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>45800000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>40663000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>32041000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>31053000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>20964000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>40380000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>44254000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>44138000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>48464000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>43771000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>46957000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>50873000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>50245000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>44779000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>28979000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>45248000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>43843000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>43267000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>21193000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>41181000</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>25412000</v>
+      </c>
+      <c r="E10" s="3">
         <v>27393000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>27313000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>24549000</v>
       </c>
-      <c r="G10" s="3">
-        <v>29168000</v>
-      </c>
       <c r="H10" s="3">
+        <v>27540000</v>
+      </c>
+      <c r="I10" s="3">
         <v>28080000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>25074000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>28744000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>32038000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>34998000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>34966000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>25105000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>25033000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>23428000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>20143000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>16889000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>13697000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>14372000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>11313000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>14754000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>18770000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>19284000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>19027000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>17875000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>21296000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>23314000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>21211000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>20657000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>21853000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>14102000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>12183000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>13207000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>19203000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>15586000</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1129,13 +1141,14 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>24</v>
+      <c r="D12" s="3">
+        <v>987000</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>24</v>
@@ -1143,11 +1156,11 @@
       <c r="F12" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="G12" s="3">
+      <c r="G12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H12" s="3">
         <v>879000</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="I12" s="3" t="s">
         <v>24</v>
@@ -1155,86 +1168,89 @@
       <c r="J12" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="K12" s="3">
+      <c r="K12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L12" s="3">
         <v>348000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>218000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>286000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>173000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>524000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>190000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>176000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>164000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>595000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>188000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>214000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>288000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>357000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>299000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>333000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>280000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>555000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>292000</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>332000</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>287000</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>703000</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>284000</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>514000</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>289000</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>340000</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>327000</v>
       </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1337,13 +1353,16 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>24</v>
+      <c r="D14" s="3">
+        <v>-615000</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>24</v>
@@ -1351,11 +1370,11 @@
       <c r="F14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H14" s="3">
         <v>2787000</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>24</v>
@@ -1363,8 +1382,8 @@
       <c r="J14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
@@ -1373,10 +1392,10 @@
         <v>0</v>
       </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>4600000</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>24</v>
@@ -1387,26 +1406,26 @@
       <c r="R14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="S14" s="3">
+      <c r="S14" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="T14" s="3">
         <v>24875000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>62000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>64000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>910000</v>
-      </c>
-      <c r="W14" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="X14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
+      <c r="Y14" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="Z14" s="3">
         <v>0</v>
@@ -1441,112 +1460,118 @@
       <c r="AJ14" s="3">
         <v>0</v>
       </c>
+      <c r="AK14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>5977000</v>
+      </c>
+      <c r="E15" s="3">
         <v>6258000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>5787000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>4812000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>4440000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>4415000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>4242000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>4244000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>5064000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>5642000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>4451000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>4283000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>5661000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>4990000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>4952000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>5004000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>5416000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>4921000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>4852000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>4909000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>4923000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>4873000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>4631000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>4571000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>5028000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>4658000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>4589000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>4470000</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>5842000</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>4880000</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>4652000</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>4519000</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>8117000</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>4605000</v>
       </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1580,216 +1605,223 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>72708000</v>
+      </c>
+      <c r="E17" s="3">
         <v>76783000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>79124000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>70493000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>70147000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>76892000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>71009000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>69602000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>74720000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>85513000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>89826000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>81528000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>73015000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>63966000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>61181000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>55297000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>72840000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>46292000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>33928000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>56167000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>60527000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>60061000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>64243000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>59155000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>63559000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>67325000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>66842000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>60767000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>48832000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>55406000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>53763000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>52607000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>42224000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>55345000</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>6768000</v>
+      </c>
+      <c r="E18" s="3">
         <v>11752000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>12192000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>10748000</v>
       </c>
-      <c r="G18" s="3">
-        <v>12579000</v>
-      </c>
       <c r="H18" s="3">
+        <v>10951000</v>
+      </c>
+      <c r="I18" s="3">
         <v>12960000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>10523000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>14581000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>18444000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>20999000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>21439000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>6206000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>8290000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>7926000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>4762000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>2255000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-27102000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-867000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-1651000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-1033000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>2497000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>3361000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>3248000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>2491000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>4694000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>6862000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>4614000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>4669000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>2000000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>3944000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>2263000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>3867000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>-1828000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>1422000</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1826,528 +1858,544 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>-1127000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-1481000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-1744000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-1842000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-1105000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-908000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-1382000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-2381000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>605000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>4632000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>3688000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>2538000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>3660000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>1894000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>1799000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>1595000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>802000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>774000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>328000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>1024000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>4149000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>1627000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>1600000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>1979000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>3642000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>2418000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>2045000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>2775000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>1203000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>1750000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>2051000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>2197000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>2640000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>1910000</v>
       </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>13872000</v>
+      </c>
+      <c r="E21" s="3">
         <v>19491000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>19723000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>17402000</v>
       </c>
-      <c r="G21" s="3">
-        <v>18124000</v>
-      </c>
       <c r="H21" s="3">
+        <v>16496000</v>
+      </c>
+      <c r="I21" s="3">
         <v>18283000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>16147000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>21206000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>24113000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>31273000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>29578000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>13027000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>17611000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>14810000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>11513000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>8854000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>3991000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>4890000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>3593000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>5810000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>11569000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>9861000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>9479000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>9041000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>13364000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>13938000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>11248000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>11914000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>9045000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>10574000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>8966000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>10583000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>8929000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>7937000</v>
       </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>297000</v>
+      </c>
+      <c r="E22" s="3">
         <v>207000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>271000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>221000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>272000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>169000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>249000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>159000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>207000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>209000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>194000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>188000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>221000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>214000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>254000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>258000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>313000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>279000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>317000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>249000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>232000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>267000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>216000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>181000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>215000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>200000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>147000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>204000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>186000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>111000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>158000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>146000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>195000</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>106000</v>
       </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>9813000</v>
+      </c>
+      <c r="E23" s="3">
         <v>13026000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>13665000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>12369000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>10625000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>13699000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>11656000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>16803000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>18842000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>25422000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>24933000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>8556000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>11729000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>9606000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>6307000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>3592000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-26613000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-372000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-1640000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-258000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>6414000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>4721000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>4632000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>4289000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>8121000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>9080000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>6512000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>7240000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>3017000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>5583000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>4156000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>5918000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>617000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>3226000</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>1858000</v>
+      </c>
+      <c r="E24" s="3">
         <v>4055000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>4094000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>3803000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>2613000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>4353000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>3503000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>4960000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>5817000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>5224000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>6359000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>2806000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>2703000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>2664000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>1526000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>796000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-5985000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>337000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-471000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>512000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>1424000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>1474000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>1241000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>1883000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>1936000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>2634000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>2526000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>2457000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>550000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>1498000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>892000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>1828000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>-1407000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>337000</v>
       </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2450,216 +2498,225 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>7955000</v>
+      </c>
+      <c r="E26" s="3">
         <v>8971000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>9571000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>8566000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>8012000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>9346000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>8153000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>11843000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>13025000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>20198000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>18574000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>5750000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>9026000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>6942000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>4781000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>2796000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-20628000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-709000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-1169000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-770000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>4990000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>3247000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>3391000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>2406000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>6185000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>6446000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>3986000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>4783000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>2467000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>4085000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>3264000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>4090000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>2024000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>2889000</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>7610000</v>
+      </c>
+      <c r="E27" s="3">
         <v>8610000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>9240000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>8220000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>7630000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>9070000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>7880000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>11430000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>12720000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>19660000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>17850000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>5480000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>8817000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>6750000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>4690000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>2730000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-20095000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-680000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-1080000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-610000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>4950000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>3170000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>3130000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>2350000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>5979000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>6240000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>3950000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>4650000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>2438000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>3970000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>3350000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>4010000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>1680000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>2650000</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -2762,8 +2819,11 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -2789,10 +2849,10 @@
         <v>0</v>
       </c>
       <c r="K29" s="3">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3">
         <v>30000</v>
-      </c>
-      <c r="L29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="M29" s="3" t="s">
         <v>24</v>
@@ -2800,11 +2860,11 @@
       <c r="N29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="O29" s="3">
+      <c r="O29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="P29" s="3">
         <v>53000</v>
-      </c>
-      <c r="P29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="Q29" s="3" t="s">
         <v>24</v>
@@ -2812,11 +2872,11 @@
       <c r="R29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="S29" s="3">
+      <c r="S29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="T29" s="3">
         <v>25000</v>
-      </c>
-      <c r="T29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="U29" s="3" t="s">
         <v>24</v>
@@ -2824,11 +2884,11 @@
       <c r="V29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="W29" s="3">
+      <c r="W29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="X29" s="3">
         <v>740000</v>
-      </c>
-      <c r="X29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="Y29" s="3" t="s">
         <v>24</v>
@@ -2836,11 +2896,11 @@
       <c r="Z29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AA29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AB29" s="3">
         <v>21000</v>
-      </c>
-      <c r="AB29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AC29" s="3" t="s">
         <v>24</v>
@@ -2848,11 +2908,11 @@
       <c r="AD29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AE29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AF29" s="3">
         <v>5942000</v>
-      </c>
-      <c r="AF29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AG29" s="3" t="s">
         <v>24</v>
@@ -2866,8 +2926,11 @@
       <c r="AJ29" s="3" t="s">
         <v>24</v>
       </c>
+      <c r="AK29" s="3" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2970,8 +3033,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3074,216 +3140,225 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>1127000</v>
+      </c>
+      <c r="E32" s="3">
         <v>1481000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>1744000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>1842000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>1105000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>908000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>1382000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>2381000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-605000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-4632000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-3688000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-2538000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-3660000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-1894000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-1799000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-1595000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-802000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-774000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-328000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-1024000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-4149000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-1627000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-1600000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-1979000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-3642000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-2418000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-2045000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-2775000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-1203000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-1750000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-2051000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-2197000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-2640000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-1910000</v>
       </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>7610000</v>
+      </c>
+      <c r="E33" s="3">
         <v>8610000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>9240000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>8220000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>7630000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>9070000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>7880000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>11430000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>12750000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>19660000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>17850000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>5480000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>8870000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>6750000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>4690000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>2730000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-20070000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-680000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-1080000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-610000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>5690000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>3170000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>3130000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>2350000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>6000000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>6240000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>3950000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>4650000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>8380000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>3970000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>3350000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>4010000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>1680000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>2650000</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3386,221 +3461,230 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>7610000</v>
+      </c>
+      <c r="E35" s="3">
         <v>8610000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>9240000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>8220000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>7630000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>9070000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>7880000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>11430000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>12750000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>19660000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>17850000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>5480000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>8870000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>6750000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>4690000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>2730000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-20070000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-680000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-1080000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-610000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>5690000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>3170000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>3130000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>2350000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>6000000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>6240000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>3950000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>4650000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>8380000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>3970000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>3350000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>4010000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>1680000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>2650000</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43100</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43008</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42916</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42825</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3637,8 +3721,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3675,112 +3760,116 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>23029000</v>
+      </c>
+      <c r="E41" s="3">
         <v>26926000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>26460000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>33320000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>31539000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>32944000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>29528000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>32651000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>29640000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>30407000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>18861000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>11074000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>6802000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>4768000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>3465000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>3515000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>4364000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>8832000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>12576000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>11412000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>3089000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>5351000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>4213000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>4586000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>3042000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>5669000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>3430000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>4125000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>3177000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>4266000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>4042000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>4897000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>3657000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>5093000</v>
       </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3883,35 +3972,38 @@
       <c r="AJ42" s="3">
         <v>0</v>
       </c>
+      <c r="AK42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>43681000</v>
+      </c>
+      <c r="E43" s="3">
         <v>41505000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>43071000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>40366000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>38015000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>41814000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>35915000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>38808000</v>
       </c>
-      <c r="K43" s="3">
-        <v>0</v>
-      </c>
       <c r="L43" s="3">
         <v>0</v>
       </c>
@@ -3919,596 +4011,614 @@
         <v>0</v>
       </c>
       <c r="N43" s="3">
+        <v>0</v>
+      </c>
+      <c r="O43" s="3">
         <v>42142000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>32383000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>29516000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>28540000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>24755000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>20581000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>19974000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>19036000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>20871000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>26966000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>25308000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>27132000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>27105000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>24701000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>27880000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>26993000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>24686000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>25597000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>23263000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>21289000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>21842000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>21394000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>20388000</v>
       </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>23524000</v>
+      </c>
+      <c r="E44" s="3">
         <v>23875000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>24503000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>23491000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>25120000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>24450000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>24249000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>23642000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>24435000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>24096000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>23585000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>22177000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>18780000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>19607000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>19275000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>18357000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>18850000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>17885000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>19657000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>16501000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>18528000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>17590000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>18835000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>18332000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>18958000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>18761000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>18483000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>18048000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>16992000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>16743000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>15305000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>14873000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>15080000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>15342000</v>
       </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1598000</v>
+      </c>
+      <c r="E45" s="3">
         <v>1997000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>2176000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2171000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1906000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1905000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>2039000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2098000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1807000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2375000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2654000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1862000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1189000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1664000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1562000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1568000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1098000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>2002000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1747000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1465000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1469000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1759000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1563000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1553000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1272000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1665000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1649000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1456000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>1368000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>1480000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>1544000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>1519000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>1285000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>2122000</v>
       </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>91990000</v>
+      </c>
+      <c r="E46" s="3">
         <v>94349000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>96238000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>99377000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>96609000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>101142000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>91760000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>97224000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>97631000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>99289000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>93163000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>77255000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>59154000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>55555000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>52842000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>48195000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>44893000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>48693000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>53016000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>50249000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>50052000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>50008000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>51743000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>51576000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>47973000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>53975000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>50555000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>48315000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>47134000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>45752000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>42180000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>43131000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>41416000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>42945000</v>
       </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>34353000</v>
+      </c>
+      <c r="E47" s="3">
         <v>41447000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>40791000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>39995000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>34257000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>40062000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>39564000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>40825000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>49793000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>50235000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>46820000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>46329000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>45195000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>45641000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>44774000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>44181000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>43515000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>43609000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>43192000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>42981000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>43164000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>42920000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>42533000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>42068000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>40790000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>40427000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>39691000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>40350000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>39160000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>37649000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>37719000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>38268000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>35102000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>35553000</v>
       </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>301441000</v>
+      </c>
+      <c r="E48" s="3">
         <v>299543000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>298283000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>213723000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>221789000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>205862000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>206736000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>206023000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>204692000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>203102000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>209159000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>212773000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>216552000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>218795000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>223012000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>224641000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>227553000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>250496000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>250524000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>248409000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>259651000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>257065000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>257118000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>253003000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>247101000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>249153000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>248209000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>250352000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>252630000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>255556000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>252987000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>253147000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>244224000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>251923000</v>
       </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4611,8 +4721,11 @@
       <c r="AJ49" s="3">
         <v>0</v>
       </c>
+      <c r="AK49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4715,8 +4828,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4819,112 +4935,118 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>21755000</v>
+      </c>
+      <c r="E52" s="3">
         <v>26577000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>25395000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>24823000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>20025000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>25193000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>25188000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>25299000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>16951000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>17526000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>18632000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>18414000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>18022000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>16697000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>16661000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>16753000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>16789000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>15245000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>14763000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>14165000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>9730000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>9368000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>9335000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>9542000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>10332000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>11073000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>10335000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>9809000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>9767000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>10470000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>10126000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>9663000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>9572000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>8965000</v>
       </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5027,112 +5149,118 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>453475000</v>
+      </c>
+      <c r="E54" s="3">
         <v>461916000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>460707000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>377918000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>376317000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>372259000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>363248000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>369371000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>369067000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>370152000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>367774000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>354771000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>338923000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>336688000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>337289000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>333770000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>332750000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>358043000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>361495000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>355804000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>362597000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>359361000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>360729000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>356189000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>346196000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>354628000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>348790000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>348826000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>348691000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>349427000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>343012000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>344209000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>330314000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>339386000</v>
       </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5169,8 +5297,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5207,632 +5336,651 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>36145000</v>
+      </c>
+      <c r="E57" s="3">
         <v>60518000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>60107000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>59531000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>31249000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>62257000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>54404000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>59935000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>63197000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>62550000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>67958000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>63501000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>50766000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>47257000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>45780000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>41017000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>35221000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>33340000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>33216000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>35815000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>40605000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>39336000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>40324000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>41190000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>37268000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>41714000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>38490000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>37207000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>36796000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>34698000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>31100000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>32069000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>31193000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>30027000</v>
       </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>6813000</v>
+      </c>
+      <c r="E58" s="3">
         <v>5632000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>6621000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>8227000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>5712000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>4743000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>3929000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2296000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>634000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>6182000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>7367000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>4886000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>4276000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>12966000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>15293000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>18185000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>20458000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>21911000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>22952000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>27755000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>20593000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>21219000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>26227000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>21828000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>17258000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>19413000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>20500000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>19836000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>17930000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>15741000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>17185000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>18483000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>13830000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>17239000</v>
       </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>23772000</v>
+      </c>
+      <c r="E59" s="3">
         <v>3843000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>4035000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>4163000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>24538000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>4186000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>3482000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>4435000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>5214000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>5325000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>4785000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>3672000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1601000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1633000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1165000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>948000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>684000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1217000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1102000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1203000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>2791000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>3640000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>3736000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>3614000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>2612000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>4161000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>3457000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>3263000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>3045000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>3338000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>2664000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>2822000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>2615000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>2755000</v>
       </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>70307000</v>
+      </c>
+      <c r="E60" s="3">
         <v>69993000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>70763000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>71921000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>65316000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>71186000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>61815000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>66666000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>69045000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>74057000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>80110000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>72059000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>56643000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>61856000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>62238000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>60150000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>56363000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>56468000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>57270000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>64773000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>63989000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>64195000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>70287000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>66632000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>57138000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>65288000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>62447000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>60306000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>57771000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>53777000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>50949000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>53374000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>47638000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>50021000</v>
       </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>41496000</v>
+      </c>
+      <c r="E61" s="3">
         <v>36918000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>36565000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>32213000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>41997000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>36510000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>37567000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>39150000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>40559000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>39246000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>39516000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>42651000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>43428000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>43639000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>45319000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>45137000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>47182000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>46888000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>46563000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>31857000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>26481000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>26089000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>19141000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>19177000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>20538000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>20624000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>20720000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>20781000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>24406000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>24869000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>24750000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>25124000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>28932000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>28916000</v>
       </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>22324000</v>
+      </c>
+      <c r="E62" s="3">
         <v>27647000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>26635000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>26151000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>21518000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>22944000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>23131000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>23763000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>56990000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>63806000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>63640000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>63535000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>63169000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>63687000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>64176000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>64382000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>65075000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>70075000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>70509000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>70431000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>73189000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>71968000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>72836000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>72359000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>69992000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>71885000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>72090000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>72828000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>72014000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>81583000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>81475000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>81940000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>79914000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>83439000</v>
       </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5935,8 +6083,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -6039,8 +6190,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6143,112 +6297,118 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>182869000</v>
+      </c>
+      <c r="E66" s="3">
         <v>185516000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>184441000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>164866000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>163779000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>164726000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>156251000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>162957000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>174018000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>184052000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>190458000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>185556000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>170346000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>176099000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>178718000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>176796000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>175600000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>180643000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>181312000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>173725000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>170947000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>169446000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>169352000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>164967000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>154402000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>164263000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>161568000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>160631000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>161003000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>167151000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>163834000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>167058000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>162989000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>168789000</v>
       </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6285,8 +6445,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6389,8 +6550,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6493,8 +6657,11 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6597,8 +6764,11 @@
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6701,112 +6871,118 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>470903000</v>
+      </c>
+      <c r="E72" s="3">
         <v>467664000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>463294000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>458339000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>453927000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>450138000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>444731000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>440552000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>432860000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>423877000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>407902000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>393779000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>392059000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>386952000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>383922000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>382953000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>383943000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>407728000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>412124000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>416919000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>421341000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>419367000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>419913000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>420498000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>421653000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>419155000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>416418000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>415970000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>414540000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>409449000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>408768000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>408707000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>407831000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>409284000</v>
       </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6909,8 +7085,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7013,8 +7192,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7117,112 +7299,118 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>263705000</v>
+      </c>
+      <c r="E76" s="3">
         <v>268592000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>268405000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>205250000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>204802000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>199703000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>199046000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>198685000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>195049000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>186100000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>177316000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>169215000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>168577000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>160589000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>158571000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>156974000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>157150000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>177400000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>180183000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>182079000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>191650000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>189915000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>191377000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>191222000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>191794000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>190365000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>187222000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>188195000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>187688000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>182276000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>179178000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>177151000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>167325000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>170597000</v>
       </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7325,221 +7513,230 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43100</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43008</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42916</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42825</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>7610000</v>
+      </c>
+      <c r="E81" s="3">
         <v>8610000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>9240000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>8220000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>7630000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>9070000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>7880000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>11430000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>12750000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>19660000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>17850000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>5480000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>8870000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>6750000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>4690000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>2730000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-20070000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-680000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-1080000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-610000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>5690000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>3170000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>3130000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>2350000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>6000000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>6240000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>3950000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>4650000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>8380000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>3970000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>3350000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>4010000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>1680000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>2650000</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7576,112 +7773,116 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>4440000</v>
+      </c>
+      <c r="E83" s="3">
         <v>4415000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>4242000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>4244000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>-3108000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>12289000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>4451000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>5908000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>5064000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>5642000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>4451000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>4283000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>5661000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>4990000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>4952000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>5004000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>30291000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>4983000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>4916000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>5819000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>4923000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>4873000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>4631000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>4571000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>5028000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>4658000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>4589000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>4470000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>5842000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>4880000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>4652000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>4519000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>8117000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>4605000</v>
       </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7784,8 +7985,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7888,8 +8092,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7992,8 +8199,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8096,8 +8306,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8200,112 +8413,118 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>12229000</v>
+      </c>
+      <c r="E89" s="3">
         <v>17569000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>10560000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>14664000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>13682000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>15963000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>9383000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>16341000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>17621000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>24425000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>19963000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>14788000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>17124000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>12091000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>9650000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>9264000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>4005000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>4389000</v>
       </c>
-      <c r="U89" s="3">
-        <v>0</v>
-      </c>
       <c r="V89" s="3">
+        <v>0</v>
+      </c>
+      <c r="W89" s="3">
         <v>6274000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>6352000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>9079000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>5947000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>8338000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>8607000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>11108000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>7780000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>8519000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>7411000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>7535000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>6947000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>8173000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>7396000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>5355000</v>
       </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8342,112 +8561,116 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-6837000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-6160000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-6235000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-5074000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-6228000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-4920000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-5359000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-5412000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-5783000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-4876000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-3837000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-3911000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-4089000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-2840000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-2747000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-2400000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-3629000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-3291000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-4417000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-5945000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-6704000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-6285000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-6173000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-5199000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-6094000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-5204000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-4927000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-3349000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-4501000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-4913000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-3098000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-2890000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-3887000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-3404000</v>
       </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8550,8 +8773,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8654,112 +8880,118 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-4252000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-6240000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-4869000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-4577000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-5714000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-4279000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-4356000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-4925000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-5355000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-2378000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-3064000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-3945000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-2110000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-3054000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-2716000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-2355000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-3302000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-3709000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-5081000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-6367000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-4264000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-6150000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-6877000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-5793000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-5584000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-3907000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-5096000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-1859000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-6536000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-2555000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-2878000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-3761000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-1672000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-3235000</v>
       </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8796,94 +9028,95 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>4371000</v>
+      </c>
+      <c r="E96" s="3">
         <v>4240000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>4285000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>3808000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>3839000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>3663000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>3701000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>3738000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-3767000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-3685000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-3727000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-3760000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-3763000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-3720000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-3721000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-3720000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-3715000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-3716000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-3715000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-3719000</v>
-      </c>
-      <c r="W96" s="3">
-        <v>-3716000</v>
       </c>
       <c r="X96" s="3">
         <v>-3716000</v>
       </c>
       <c r="Y96" s="3">
+        <v>-3716000</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-3715000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-3505000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-3502000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-3503000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-3502000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-3291000</v>
-      </c>
-      <c r="AE96" s="3">
-        <v>-3289000</v>
       </c>
       <c r="AF96" s="3">
         <v>-3289000</v>
@@ -8892,16 +9125,19 @@
         <v>-3289000</v>
       </c>
       <c r="AH96" s="3">
+        <v>-3289000</v>
+      </c>
+      <c r="AI96" s="3">
         <v>-3134000</v>
-      </c>
-      <c r="AI96" s="3">
-        <v>-3133000</v>
       </c>
       <c r="AJ96" s="3">
         <v>-3133000</v>
       </c>
+      <c r="AK96" s="3">
+        <v>-3133000</v>
+      </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9004,8 +9240,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9108,8 +9347,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9212,316 +9454,328 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-11143000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-11106000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-12558000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-7982000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-9555000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-8059000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-8176000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-8507000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-13937000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-9793000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-8671000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-6713000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-12959000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-7657000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-7022000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-7785000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-5283000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-4494000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>6277000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>8785000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-4456000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-1666000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>548000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-1044000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-5501000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-4959000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-3244000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-5742000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-1837000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-4988000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-5059000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-3246000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-6746000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-1296000</v>
       </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>182000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-209000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>30000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>102000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>872000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-651000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-441000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>142000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>872000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-651000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-441000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>142000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-21000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-77000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>38000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>27000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>112000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>70000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-32000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-369000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>106000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-125000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>9000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>43000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-149000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-3000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-135000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>30000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-127000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>232000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>135000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>74000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-414000</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-89000</v>
       </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-3785000</v>
+      </c>
+      <c r="E102" s="3">
         <v>484000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-6861000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1781000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-1405000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>3416000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-3119000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>3011000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-799000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>11603000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>7787000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>4272000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>2034000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>1303000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-50000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-849000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-4468000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-3744000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>1164000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>8323000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-2262000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>1138000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-373000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>1544000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-2627000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>2239000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-695000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>948000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-1089000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>224000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-855000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>1240000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-1436000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>735000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/XOM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/XOM_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="92">
   <si>
     <t>XOM</t>
   </si>
@@ -656,455 +656,467 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="37" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="38" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43373</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43281</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43190</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43100</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43008</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42916</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42735</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>81761000</v>
+      </c>
+      <c r="E8" s="3">
         <v>79476000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>88535000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>91316000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>81241000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>81098000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>89852000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>81532000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>84183000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>93164000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>106512000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>111265000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>87734000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>81305000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>71892000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>65943000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>57552000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>45738000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>45425000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>32277000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>55134000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>63024000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>63422000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>67491000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>61646000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>68253000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>74187000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>71456000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>65436000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>50832000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>59350000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>56026000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>56474000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>40396000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>56767000</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>56871000</v>
+      </c>
+      <c r="E9" s="3">
         <v>54064000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>61142000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>64003000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>56692000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>53558000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>61772000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>56458000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>55439000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>61126000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>71514000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>76299000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>62629000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>56272000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>48464000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>45800000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>40663000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>32041000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>31053000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>20964000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>40380000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>44254000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>44138000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>48464000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>43771000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>46957000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>50873000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>50245000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>44779000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>28979000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>45248000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>43843000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>43267000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>21193000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>41181000</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>24890000</v>
+      </c>
+      <c r="E10" s="3">
         <v>25412000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>27393000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>27313000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>24549000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>27540000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>28080000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>25074000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>28744000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>32038000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>34998000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>34966000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>25105000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>25033000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>23428000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>20143000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>16889000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>13697000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>14372000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>11313000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>14754000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>18770000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>19284000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>19027000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>17875000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>21296000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>23314000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>21211000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>20657000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>21853000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>14102000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>12183000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>13207000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>19203000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>15586000</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1142,16 +1154,17 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E12" s="3">
         <v>987000</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>24</v>
@@ -1159,11 +1172,11 @@
       <c r="G12" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="H12" s="3">
+      <c r="H12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I12" s="3">
         <v>879000</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>24</v>
@@ -1171,86 +1184,89 @@
       <c r="K12" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="L12" s="3">
+      <c r="L12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M12" s="3">
         <v>348000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>218000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>286000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>173000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>524000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>190000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>176000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>164000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>595000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>188000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>214000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>288000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>357000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>299000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>333000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>280000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>555000</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>292000</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>332000</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>287000</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>703000</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>284000</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>514000</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>289000</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>340000</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>327000</v>
       </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1356,16 +1372,19 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E14" s="3">
         <v>-615000</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>24</v>
@@ -1373,11 +1392,11 @@
       <c r="G14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I14" s="3">
         <v>2787000</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>24</v>
@@ -1385,8 +1404,8 @@
       <c r="K14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -1395,10 +1414,10 @@
         <v>0</v>
       </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>4600000</v>
-      </c>
-      <c r="P14" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="Q14" s="3" t="s">
         <v>24</v>
@@ -1409,26 +1428,26 @@
       <c r="S14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="T14" s="3">
+      <c r="T14" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="U14" s="3">
         <v>24875000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>62000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>64000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>910000</v>
-      </c>
-      <c r="X14" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="Y14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
+      <c r="Z14" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="AA14" s="3">
         <v>0</v>
@@ -1463,115 +1482,121 @@
       <c r="AK14" s="3">
         <v>0</v>
       </c>
+      <c r="AL14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>5702000</v>
+      </c>
+      <c r="E15" s="3">
         <v>5977000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>6258000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>5787000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>4812000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>4440000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>4415000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>4242000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>4244000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>5064000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>5642000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>4451000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>4283000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>5661000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>4990000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>4952000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>5004000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>5416000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>4921000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>4852000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>4909000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>4923000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>4873000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>4631000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>4571000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>5028000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>4658000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>4589000</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>4470000</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>5842000</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>4880000</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>4652000</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>4519000</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>8117000</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>4605000</v>
       </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1606,222 +1631,229 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>71325000</v>
+      </c>
+      <c r="E17" s="3">
         <v>72708000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>76783000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>79124000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>70493000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>70147000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>76892000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>71009000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>69602000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>74720000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>85513000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>89826000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>81528000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>73015000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>63966000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>61181000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>55297000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>72840000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>46292000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>33928000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>56167000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>60527000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>60061000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>64243000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>59155000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>63559000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>67325000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>66842000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>60767000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>48832000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>55406000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>53763000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>52607000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>42224000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>55345000</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>10436000</v>
+      </c>
+      <c r="E18" s="3">
         <v>6768000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>11752000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>12192000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>10748000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>10951000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>12960000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>10523000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>14581000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>18444000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>20999000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>21439000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>6206000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>8290000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>7926000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>4762000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>2255000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-27102000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-867000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-1651000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-1033000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>2497000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>3361000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>3248000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>2491000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>4694000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>6862000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>4614000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>4669000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>2000000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>3944000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>2263000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>3867000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>-1828000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>1422000</v>
       </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1859,543 +1891,559 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>-1369000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-1127000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-1481000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-1744000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-1842000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-1105000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-908000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-1382000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-2381000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>605000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>4632000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>3688000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>2538000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>3660000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>1894000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>1799000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>1595000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>802000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>774000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>328000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>1024000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>4149000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>1627000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>1600000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>1979000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>3642000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>2418000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>2045000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>2775000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>1203000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>1750000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>2051000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>2197000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>2640000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>1910000</v>
       </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>17507000</v>
+      </c>
+      <c r="E21" s="3">
         <v>13872000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>19491000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>19723000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>17402000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>16496000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>18283000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>16147000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>21206000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>24113000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>31273000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>29578000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>13027000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>17611000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>14810000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>11513000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>8854000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>3991000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>4890000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>3593000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>5810000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>11569000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>9861000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>9479000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>9041000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>13364000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>13938000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>11248000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>11914000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>9045000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>10574000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>8966000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>10583000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>8929000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>7937000</v>
       </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>205000</v>
+      </c>
+      <c r="E22" s="3">
         <v>297000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>207000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>271000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>221000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>272000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>169000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>249000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>159000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>207000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>209000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>194000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>188000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>221000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>214000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>254000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>258000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>313000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>279000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>317000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>249000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>232000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>267000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>216000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>181000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>215000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>200000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>147000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>204000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>186000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>111000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>158000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>146000</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>195000</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>106000</v>
       </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>11600000</v>
+      </c>
+      <c r="E23" s="3">
         <v>9813000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>13026000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>13665000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>12369000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>10625000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>13699000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>11656000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>16803000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>18842000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>25422000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>24933000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>8556000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>11729000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>9606000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>6307000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>3592000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-26613000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-372000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-1640000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-258000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>6414000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>4721000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>4632000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>4289000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>8121000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>9080000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>6512000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>7240000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>3017000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>5583000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>4156000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>5918000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>617000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>3226000</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>3567000</v>
+      </c>
+      <c r="E24" s="3">
         <v>1858000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>4055000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>4094000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>3803000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>2613000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>4353000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>3503000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>4960000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>5817000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>5224000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>6359000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>2806000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>2703000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>2664000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>1526000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>796000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-5985000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>337000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-471000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>512000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>1424000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>1474000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>1241000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>1883000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>1936000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>2634000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>2526000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>2457000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>550000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>1498000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>892000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>1828000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>-1407000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>337000</v>
       </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2501,222 +2549,231 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>8033000</v>
+      </c>
+      <c r="E26" s="3">
         <v>7955000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>8971000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>9571000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>8566000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>8012000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>9346000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>8153000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>11843000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>13025000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>20198000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>18574000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>5750000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>9026000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>6942000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>4781000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>2796000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-20628000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-709000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-1169000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-770000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>4990000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>3247000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>3391000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>2406000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>6185000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>6446000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>3986000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>4783000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>2467000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>4085000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>3264000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>4090000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>2024000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>2889000</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>7713000</v>
+      </c>
+      <c r="E27" s="3">
         <v>7610000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>8610000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>9240000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>8220000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>7630000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>9070000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>7880000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>11430000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>12720000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>19660000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>17850000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>5480000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>8817000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>6750000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>4690000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>2730000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-20095000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-680000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-1080000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-610000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>4950000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>3170000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>3130000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>2350000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>5979000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>6240000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>3950000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>4650000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>2438000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>3970000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>3350000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>4010000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>1680000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>2650000</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -2822,8 +2879,11 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -2852,10 +2912,10 @@
         <v>0</v>
       </c>
       <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3">
         <v>30000</v>
-      </c>
-      <c r="M29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="N29" s="3" t="s">
         <v>24</v>
@@ -2863,11 +2923,11 @@
       <c r="O29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="P29" s="3">
+      <c r="P29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q29" s="3">
         <v>53000</v>
-      </c>
-      <c r="Q29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="R29" s="3" t="s">
         <v>24</v>
@@ -2875,11 +2935,11 @@
       <c r="S29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="T29" s="3">
+      <c r="T29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="U29" s="3">
         <v>25000</v>
-      </c>
-      <c r="U29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="V29" s="3" t="s">
         <v>24</v>
@@ -2887,11 +2947,11 @@
       <c r="W29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="X29" s="3">
+      <c r="X29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Y29" s="3">
         <v>740000</v>
-      </c>
-      <c r="Y29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="Z29" s="3" t="s">
         <v>24</v>
@@ -2899,11 +2959,11 @@
       <c r="AA29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AB29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AC29" s="3">
         <v>21000</v>
-      </c>
-      <c r="AC29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>24</v>
@@ -2911,11 +2971,11 @@
       <c r="AE29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AF29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AG29" s="3">
         <v>5942000</v>
-      </c>
-      <c r="AG29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AH29" s="3" t="s">
         <v>24</v>
@@ -2929,8 +2989,11 @@
       <c r="AK29" s="3" t="s">
         <v>24</v>
       </c>
+      <c r="AL29" s="3" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3036,8 +3099,11 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3143,222 +3209,231 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>1369000</v>
+      </c>
+      <c r="E32" s="3">
         <v>1127000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>1481000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>1744000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>1842000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>1105000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>908000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>1382000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>2381000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-605000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-4632000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-3688000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-2538000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-3660000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-1894000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-1799000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-1595000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-802000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-774000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-328000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-1024000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-4149000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-1627000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-1600000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-1979000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-3642000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-2418000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-2045000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-2775000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-1203000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-1750000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-2051000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-2197000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-2640000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-1910000</v>
       </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>7713000</v>
+      </c>
+      <c r="E33" s="3">
         <v>7610000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>8610000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>9240000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>8220000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>7630000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>9070000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>7880000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>11430000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>12750000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>19660000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>17850000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>5480000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>8870000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>6750000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>4690000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>2730000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-20070000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-680000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-1080000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-610000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>5690000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>3170000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>3130000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>2350000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>6000000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>6240000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>3950000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>4650000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>8380000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>3970000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>3350000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>4010000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>1680000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>2650000</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3464,227 +3539,236 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>7713000</v>
+      </c>
+      <c r="E35" s="3">
         <v>7610000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>8610000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>9240000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>8220000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>7630000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>9070000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>7880000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>11430000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>12750000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>19660000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>17850000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>5480000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>8870000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>6750000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>4690000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>2730000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-20070000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-680000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-1080000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-610000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>5690000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>3170000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>3130000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>2350000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>6000000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>6240000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>3950000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>4650000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>8380000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>3970000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>3350000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>4010000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>1680000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>2650000</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43373</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43281</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43190</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43100</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43008</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42916</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42735</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3722,8 +3806,9 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3761,115 +3846,119 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>17036000</v>
+      </c>
+      <c r="E41" s="3">
         <v>23029000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>26926000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>26460000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>33320000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>31539000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>32944000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>29528000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>32651000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>29640000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>30407000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>18861000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>11074000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>6802000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>4768000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>3465000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>3515000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>4364000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>8832000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>12576000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>11412000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>3089000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>5351000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>4213000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>4586000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>3042000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>5669000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>3430000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>4125000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>3177000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>4266000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>4042000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>4897000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>3657000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>5093000</v>
       </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3975,38 +4064,41 @@
       <c r="AK42" s="3">
         <v>0</v>
       </c>
+      <c r="AL42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>46303000</v>
+      </c>
+      <c r="E43" s="3">
         <v>43681000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>41505000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>43071000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>40366000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>38015000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>41814000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>35915000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>38808000</v>
       </c>
-      <c r="L43" s="3">
-        <v>0</v>
-      </c>
       <c r="M43" s="3">
         <v>0</v>
       </c>
@@ -4014,611 +4106,629 @@
         <v>0</v>
       </c>
       <c r="O43" s="3">
+        <v>0</v>
+      </c>
+      <c r="P43" s="3">
         <v>42142000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>32383000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>29516000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>28540000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>24755000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>20581000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>19974000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>19036000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>20871000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>26966000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>25308000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>27132000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>27105000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>24701000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>27880000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>26993000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>24686000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>25597000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>23263000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>21289000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>21842000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>21394000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>20388000</v>
       </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>24478000</v>
+      </c>
+      <c r="E44" s="3">
         <v>23524000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>23875000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>24503000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>23491000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>25120000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>24450000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>24249000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>23642000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>24435000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>24096000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>23585000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>22177000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>18780000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>19607000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>19275000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>18357000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>18850000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>17885000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>19657000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>16501000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>18528000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>17590000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>18835000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>18332000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>18958000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>18761000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>18483000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>18048000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>16992000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>16743000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>15305000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>14873000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>15080000</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>15342000</v>
       </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1940000</v>
+      </c>
+      <c r="E45" s="3">
         <v>1598000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1997000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2176000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>2171000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1906000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1905000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2039000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2098000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1807000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2375000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2654000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1862000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1189000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1664000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1562000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1568000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1098000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>2002000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1747000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1465000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1469000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1759000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1563000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1553000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1272000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1665000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1649000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>1456000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>1368000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>1480000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>1544000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>1519000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>1285000</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>2122000</v>
       </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>91233000</v>
+      </c>
+      <c r="E46" s="3">
         <v>91990000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>94349000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>96238000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>99377000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>96609000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>101142000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>91760000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>97224000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>97631000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>99289000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>93163000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>77255000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>59154000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>55555000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>52842000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>48195000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>44893000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>48693000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>53016000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>50249000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>50052000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>50008000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>51743000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>51576000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>47973000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>53975000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>50555000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>48315000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>47134000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>45752000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>42180000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>43131000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>41416000</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>42945000</v>
       </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>40356000</v>
+      </c>
+      <c r="E47" s="3">
         <v>34353000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>41447000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>40791000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>39995000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>34257000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>40062000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>39564000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>40825000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>49793000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>50235000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>46820000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>46329000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>45195000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>45641000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>44774000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>44181000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>43515000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>43609000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>43192000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>42981000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>43164000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>42920000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>42533000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>42068000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>40790000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>40427000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>39691000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>40350000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>39160000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>37649000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>37719000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>38268000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>35102000</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>35553000</v>
       </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>292646000</v>
+      </c>
+      <c r="E48" s="3">
         <v>301441000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>299543000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>298283000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>213723000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>221789000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>205862000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>206736000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>206023000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>204692000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>203102000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>209159000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>212773000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>216552000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>218795000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>223012000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>224641000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>227553000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>250496000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>250524000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>248409000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>259651000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>257065000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>257118000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>253003000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>247101000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>249153000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>248209000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>250352000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>252630000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>255556000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>252987000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>253147000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>244224000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>251923000</v>
       </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4724,8 +4834,11 @@
       <c r="AK49" s="3">
         <v>0</v>
       </c>
+      <c r="AL49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4831,8 +4944,11 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4938,115 +5054,121 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>27673000</v>
+      </c>
+      <c r="E52" s="3">
         <v>21755000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>26577000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>25395000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>24823000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>20025000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>25193000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>25188000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>25299000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>16951000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>17526000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>18632000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>18414000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>18022000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>16697000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>16661000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>16753000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>16789000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>15245000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>14763000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>14165000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>9730000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>9368000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>9335000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>9542000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>10332000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>11073000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>10335000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>9809000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>9767000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>10470000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>10126000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>9663000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>9572000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>8965000</v>
       </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5152,115 +5274,121 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>451908000</v>
+      </c>
+      <c r="E54" s="3">
         <v>453475000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>461916000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>460707000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>377918000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>376317000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>372259000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>363248000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>369371000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>369067000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>370152000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>367774000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>354771000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>338923000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>336688000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>337289000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>333770000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>332750000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>358043000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>361495000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>355804000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>362597000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>359361000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>360729000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>356189000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>346196000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>354628000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>348790000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>348826000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>348691000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>349427000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>343012000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>344209000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>330314000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>339386000</v>
       </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5298,8 +5426,9 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5337,650 +5466,669 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>63987000</v>
+      </c>
+      <c r="E57" s="3">
         <v>36145000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>60518000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>60107000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>59531000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>31249000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>62257000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>54404000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>59935000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>63197000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>62550000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>67958000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>63501000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>50766000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>47257000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>45780000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>41017000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>35221000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>33340000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>33216000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>35815000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>40605000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>39336000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>40324000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>41190000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>37268000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>41714000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>38490000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>37207000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>36796000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>34698000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>31100000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>32069000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>31193000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>30027000</v>
       </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>4728000</v>
+      </c>
+      <c r="E58" s="3">
         <v>6813000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>5632000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>6621000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>8227000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>5712000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>4743000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>3929000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2296000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>634000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>6182000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>7367000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>4886000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>4276000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>12966000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>15293000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>18185000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>20458000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>21911000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>22952000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>27755000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>20593000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>21219000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>26227000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>21828000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>17258000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>19413000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>20500000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>19836000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>17930000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>15741000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>17185000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>18483000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>13830000</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>17239000</v>
       </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>5114000</v>
+      </c>
+      <c r="E59" s="3">
         <v>23772000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>3843000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>4035000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>4163000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>24538000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>4186000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>3482000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>4435000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>5214000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>5325000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>4785000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>3672000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1601000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1633000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1165000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>948000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>684000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1217000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1102000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1203000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>2791000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>3640000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>3736000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>3614000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>2612000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>4161000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>3457000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>3263000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>3045000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>3338000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>2664000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>2822000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>2615000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>2755000</v>
       </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>73829000</v>
+      </c>
+      <c r="E60" s="3">
         <v>70307000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>69993000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>70763000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>71921000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>65316000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>71186000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>61815000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>66666000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>69045000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>74057000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>80110000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>72059000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>56643000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>61856000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>62238000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>60150000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>56363000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>56468000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>57270000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>64773000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>63989000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>64195000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>70287000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>66632000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>57138000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>65288000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>62447000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>60306000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>57771000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>53777000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>50949000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>53374000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>47638000</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>50021000</v>
       </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>32823000</v>
+      </c>
+      <c r="E61" s="3">
         <v>41496000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>36918000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>36565000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>32213000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>41997000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>36510000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>37567000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>39150000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>40559000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>39246000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>39516000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>42651000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>43428000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>43639000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>45319000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>45137000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>47182000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>46888000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>46563000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>31857000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>26481000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>26089000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>19141000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>19177000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>20538000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>20624000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>20720000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>20781000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>24406000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>24869000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>24750000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>25124000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>28932000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>28916000</v>
       </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>26344000</v>
+      </c>
+      <c r="E62" s="3">
         <v>22324000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>27647000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>26635000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>26151000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>21518000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>22944000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>23131000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>23763000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>56990000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>63806000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>63640000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>63535000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>63169000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>63687000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>64176000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>64382000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>65075000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>70075000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>70509000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>70431000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>73189000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>71968000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>72836000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>72359000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>69992000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>71885000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>72090000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>72828000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>72014000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>81583000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>81475000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>81940000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>79914000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>83439000</v>
       </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6086,8 +6234,11 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -6193,8 +6344,11 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6300,115 +6454,121 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>182102000</v>
+      </c>
+      <c r="E66" s="3">
         <v>182869000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>185516000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>184441000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>164866000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>163779000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>164726000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>156251000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>162957000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>174018000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>184052000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>190458000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>185556000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>170346000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>176099000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>178718000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>176796000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>175600000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>180643000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>181312000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>173725000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>170947000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>169446000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>169352000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>164967000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>154402000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>164263000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>161568000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>160631000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>161003000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>167151000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>163834000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>167058000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>162989000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>168789000</v>
       </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6446,8 +6606,9 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6553,8 +6714,11 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6660,8 +6824,11 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6767,8 +6934,11 @@
       <c r="AK70" s="3">
         <v>0</v>
       </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6874,115 +7044,121 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>474290000</v>
+      </c>
+      <c r="E72" s="3">
         <v>470903000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>467664000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>463294000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>458339000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>453927000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>450138000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>444731000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>440552000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>432860000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>423877000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>407902000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>393779000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>392059000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>386952000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>383922000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>382953000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>383943000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>407728000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>412124000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>416919000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>421341000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>419367000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>419913000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>420498000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>421653000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>419155000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>416418000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>415970000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>414540000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>409449000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>408768000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>408707000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>407831000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>409284000</v>
       </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7088,8 +7264,11 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7195,8 +7374,11 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7302,115 +7484,121 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>262720000</v>
+      </c>
+      <c r="E76" s="3">
         <v>263705000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>268592000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>268405000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>205250000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>204802000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>199703000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>199046000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>198685000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>195049000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>186100000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>177316000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>169215000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>168577000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>160589000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>158571000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>156974000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>157150000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>177400000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>180183000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>182079000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>191650000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>189915000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>191377000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>191222000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>191794000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>190365000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>187222000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>188195000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>187688000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>182276000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>179178000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>177151000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>167325000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>170597000</v>
       </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7516,227 +7704,236 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43373</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43281</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43190</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43100</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43008</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42916</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42735</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>7713000</v>
+      </c>
+      <c r="E81" s="3">
         <v>7610000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>8610000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>9240000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>8220000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>7630000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>9070000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>7880000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>11430000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>12750000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>19660000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>17850000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>5480000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>8870000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>6750000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>4690000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>2730000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-20070000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-680000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-1080000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-610000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>5690000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>3170000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>3130000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>2350000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>6000000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>6240000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>3950000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>4650000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>8380000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>3970000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>3350000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>4010000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>1680000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>2650000</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7774,115 +7971,119 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>4812000</v>
+      </c>
+      <c r="E83" s="3">
         <v>4440000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>4415000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>4242000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>4244000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>-3108000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>12289000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>4451000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>5908000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>5064000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>5642000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>4451000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>4283000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>5661000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>4990000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>4952000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>5004000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>30291000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>4983000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>4916000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>5819000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>4923000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>4873000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>4631000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>4571000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>5028000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>4658000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>4589000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>4470000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>5842000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>4880000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>4652000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>4519000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>8117000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>4605000</v>
       </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7988,8 +8189,11 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8095,8 +8299,11 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8202,8 +8409,11 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8309,8 +8519,11 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8416,115 +8629,121 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>12953000</v>
+      </c>
+      <c r="E89" s="3">
         <v>12229000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>17569000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>10560000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>14664000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>13682000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>15963000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>9383000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>16341000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>17621000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>24425000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>19963000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>14788000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>17124000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>12091000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>9650000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>9264000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>4005000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>4389000</v>
       </c>
-      <c r="V89" s="3">
-        <v>0</v>
-      </c>
       <c r="W89" s="3">
+        <v>0</v>
+      </c>
+      <c r="X89" s="3">
         <v>6274000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>6352000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>9079000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>5947000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>8338000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>8607000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>11108000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>7780000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>8519000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>7411000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>7535000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>6947000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>8173000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>7396000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>5355000</v>
       </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8562,115 +8781,119 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-5898000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-6837000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-6160000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-6235000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-5074000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-6228000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-4920000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-5359000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-5412000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-5783000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-4876000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-3837000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-3911000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-4089000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-2840000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-2747000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-2400000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-3629000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-3291000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-4417000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-5945000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-6704000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-6285000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-6173000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-5199000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-6094000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-5204000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-4927000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-3349000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-4501000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-4913000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-3098000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-2890000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-3887000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-3404000</v>
       </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8776,8 +8999,11 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8883,115 +9109,121 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-4135000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-4252000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-6240000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-4869000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-4577000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-5714000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-4279000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-4356000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-4925000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-5355000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-2378000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-3064000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-3945000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-2110000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-3054000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-2716000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-2355000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-3302000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-3709000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-5081000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-6367000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-4264000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-6150000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-6877000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-5793000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-5584000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-3907000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-5096000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-1859000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-6536000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-2555000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-2878000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-3761000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-1672000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-3235000</v>
       </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9029,97 +9261,98 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>4335000</v>
+      </c>
+      <c r="E96" s="3">
         <v>4371000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>4240000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>4285000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>3808000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>3839000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>3663000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>3701000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>3738000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-3767000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-3685000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-3727000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-3760000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-3763000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-3720000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-3721000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-3720000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-3715000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-3716000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-3715000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-3719000</v>
-      </c>
-      <c r="X96" s="3">
-        <v>-3716000</v>
       </c>
       <c r="Y96" s="3">
         <v>-3716000</v>
       </c>
       <c r="Z96" s="3">
+        <v>-3716000</v>
+      </c>
+      <c r="AA96" s="3">
         <v>-3715000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-3505000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-3502000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-3503000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-3502000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-3291000</v>
-      </c>
-      <c r="AF96" s="3">
-        <v>-3289000</v>
       </c>
       <c r="AG96" s="3">
         <v>-3289000</v>
@@ -9128,16 +9361,19 @@
         <v>-3289000</v>
       </c>
       <c r="AI96" s="3">
+        <v>-3289000</v>
+      </c>
+      <c r="AJ96" s="3">
         <v>-3134000</v>
-      </c>
-      <c r="AJ96" s="3">
-        <v>-3133000</v>
       </c>
       <c r="AK96" s="3">
         <v>-3133000</v>
       </c>
+      <c r="AL96" s="3">
+        <v>-3133000</v>
+      </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9243,8 +9479,11 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9350,8 +9589,11 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9457,325 +9699,337 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-13579000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-11143000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-11106000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-12558000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-7982000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-9555000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-8059000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-8176000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-8507000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-13937000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-9793000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-8671000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-6713000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-12959000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-7657000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-7022000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-7785000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-5283000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-4494000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>6277000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>8785000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-4456000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-1666000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>548000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-1044000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-5501000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-4959000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-3244000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-5742000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-1837000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-4988000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-5059000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-3246000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-6746000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-1296000</v>
       </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-324000</v>
+      </c>
+      <c r="E101" s="3">
         <v>182000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-209000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>30000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>102000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>872000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-651000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-441000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>142000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>872000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-651000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-441000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>142000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-21000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-77000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>38000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>27000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>112000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>70000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-32000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-369000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>106000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-125000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>9000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>43000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-149000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-3000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-135000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>30000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-127000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>232000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>135000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>74000</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-414000</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-89000</v>
       </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-4675000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-3785000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>484000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-6861000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>1781000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-1405000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>3416000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-3119000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>3011000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-799000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>11603000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>7787000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>4272000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>2034000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>1303000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-50000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-849000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-4468000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-3744000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>1164000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>8323000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-2262000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>1138000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-373000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>1544000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-2627000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>2239000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-695000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>948000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-1089000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>224000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-855000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>1240000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-1436000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>735000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/XOM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/XOM_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="92">
   <si>
     <t>XOM</t>
   </si>
@@ -656,467 +656,479 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AL102"/>
+  <dimension ref="A5:AM102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="38" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="39" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43465</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43373</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43281</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43190</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43100</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43008</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42825</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42735</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>80044000</v>
+      </c>
+      <c r="E8" s="3">
         <v>81761000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>79476000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>88535000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>91316000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>81241000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>81098000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>89852000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>81532000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>84183000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>93164000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>106512000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>111265000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>87734000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>81305000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>71892000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>65943000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>57552000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>45738000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>45425000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>32277000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>55134000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>63024000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>63422000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>67491000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>61646000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>68253000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>74187000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>71456000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>65436000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>50832000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>59350000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>56026000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>56474000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>40396000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>56767000</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>55429000</v>
+      </c>
+      <c r="E9" s="3">
         <v>56871000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>54064000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>61142000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>64003000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>56692000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>53558000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>61772000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>56458000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>55439000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>61126000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>71514000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>76299000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>62629000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>56272000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>48464000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>45800000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>40663000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>32041000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>31053000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>20964000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>40380000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>44254000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>44138000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>48464000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>43771000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>46957000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>50873000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>50245000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>44779000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>28979000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>45248000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>43843000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>43267000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>21193000</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>41181000</v>
       </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>24615000</v>
+      </c>
+      <c r="E10" s="3">
         <v>24890000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>25412000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>27393000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>27313000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>24549000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>27540000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>28080000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>25074000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>28744000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>32038000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>34998000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>34966000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>25105000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>25033000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>23428000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>20143000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>16889000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>13697000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>14372000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>11313000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>14754000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>18770000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>19284000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>19027000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>17875000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>21296000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>23314000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>21211000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>20657000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>21853000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>14102000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>12183000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>13207000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>19203000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>15586000</v>
       </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1155,19 +1167,20 @@
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F12" s="3">
         <v>987000</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>24</v>
@@ -1175,11 +1188,11 @@
       <c r="H12" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="I12" s="3">
+      <c r="I12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J12" s="3">
         <v>879000</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>24</v>
@@ -1187,86 +1200,89 @@
       <c r="L12" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="M12" s="3">
+      <c r="M12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="N12" s="3">
         <v>348000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>218000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>286000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>173000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>524000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>190000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>176000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>164000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>595000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>188000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>214000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>288000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>357000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>299000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>333000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>280000</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>555000</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>292000</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>332000</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>287000</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>703000</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>284000</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>514000</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>289000</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>340000</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>327000</v>
       </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1375,19 +1391,22 @@
       <c r="AL13" s="3">
         <v>0</v>
       </c>
+      <c r="AM13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F14" s="3">
         <v>-615000</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>24</v>
@@ -1395,11 +1414,11 @@
       <c r="H14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J14" s="3">
         <v>2787000</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>24</v>
@@ -1407,8 +1426,8 @@
       <c r="L14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
@@ -1417,10 +1436,10 @@
         <v>0</v>
       </c>
       <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>4600000</v>
-      </c>
-      <c r="Q14" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="R14" s="3" t="s">
         <v>24</v>
@@ -1431,26 +1450,26 @@
       <c r="T14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="U14" s="3">
+      <c r="U14" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="V14" s="3">
         <v>24875000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>62000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>64000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>910000</v>
-      </c>
-      <c r="Y14" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="Z14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
+      <c r="AA14" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="AB14" s="3">
         <v>0</v>
@@ -1485,118 +1504,124 @@
       <c r="AL14" s="3">
         <v>0</v>
       </c>
+      <c r="AM14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>6101000</v>
+      </c>
+      <c r="E15" s="3">
         <v>5702000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>5977000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>6258000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>5787000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>4812000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>4440000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>4415000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>4242000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>4244000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>5064000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>5642000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>4451000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>4283000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>5661000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>4990000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>4952000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>5004000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>5416000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>4921000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>4852000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>4909000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>4923000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>4873000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>4631000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>4571000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>5028000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>4658000</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>4589000</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>4470000</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>5842000</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>4880000</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>4652000</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>4519000</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>8117000</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>4605000</v>
       </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1632,228 +1657,235 @@
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
     </row>
-    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>70656000</v>
+      </c>
+      <c r="E17" s="3">
         <v>71325000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>72708000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>76783000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>79124000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>70493000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>70147000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>76892000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>71009000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>69602000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>74720000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>85513000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>89826000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>81528000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>73015000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>63966000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>61181000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>55297000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>72840000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>46292000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>33928000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>56167000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>60527000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>60061000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>64243000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>59155000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>63559000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>67325000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>66842000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>60767000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>48832000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>55406000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>53763000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>52607000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>42224000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>55345000</v>
       </c>
     </row>
-    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>9388000</v>
+      </c>
+      <c r="E18" s="3">
         <v>10436000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>6768000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>11752000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>12192000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>10748000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>10951000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>12960000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>10523000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>14581000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>18444000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>20999000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>21439000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>6206000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>8290000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>7926000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>4762000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>2255000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-27102000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-867000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-1651000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-1033000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>2497000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>3361000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>3248000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>2491000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>4694000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>6862000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>4614000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>4669000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>2000000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>3944000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>2263000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>3867000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>-1828000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>1422000</v>
       </c>
     </row>
-    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1892,558 +1924,574 @@
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
     </row>
-    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>-1462000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-1369000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-1127000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-1481000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-1744000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-1842000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-1105000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-908000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-1382000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-2381000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>605000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>4632000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>3688000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>2538000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>3660000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>1894000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>1799000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>1595000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>802000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>774000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>328000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>1024000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>4149000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>1627000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>1600000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>1979000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>3642000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>2418000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>2045000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>2775000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>1203000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>1750000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>2051000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>2197000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>2640000</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>1910000</v>
       </c>
     </row>
-    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>16951000</v>
+      </c>
+      <c r="E21" s="3">
         <v>17507000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>13872000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>19491000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>19723000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>17402000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>16496000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>18283000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>16147000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>21206000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>24113000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>31273000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>29578000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>13027000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>17611000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>14810000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>11513000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>8854000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>3991000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>4890000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>3593000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>5810000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>11569000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>9861000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>9479000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>9041000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>13364000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>13938000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>11248000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>11914000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>9045000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>10574000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>8966000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>10583000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>8929000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>7937000</v>
       </c>
     </row>
-    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>145000</v>
+      </c>
+      <c r="E22" s="3">
         <v>205000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>297000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>207000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>271000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>221000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>272000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>169000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>249000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>159000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>207000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>209000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>194000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>188000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>221000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>214000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>254000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>258000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>313000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>279000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>317000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>249000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>232000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>267000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>216000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>181000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>215000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>200000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>147000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>204000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>186000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>111000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>158000</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>146000</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>195000</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>106000</v>
       </c>
     </row>
-    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>10705000</v>
+      </c>
+      <c r="E23" s="3">
         <v>11600000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>9813000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>13026000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>13665000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>12369000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>10625000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>13699000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>11656000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>16803000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>18842000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>25422000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>24933000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>8556000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>11729000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>9606000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>6307000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>3592000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-26613000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-372000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-1640000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-258000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>6414000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>4721000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>4632000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>4289000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>8121000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>9080000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>6512000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>7240000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>3017000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>5583000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>4156000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>5918000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>617000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>3226000</v>
       </c>
     </row>
-    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>3351000</v>
+      </c>
+      <c r="E24" s="3">
         <v>3567000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1858000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>4055000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>4094000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>3803000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>2613000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>4353000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>3503000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>4960000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>5817000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>5224000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>6359000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>2806000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>2703000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>2664000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>1526000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>796000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-5985000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>337000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-471000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>512000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>1424000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>1474000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>1241000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>1883000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>1936000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>2634000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>2526000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>2457000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>550000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>1498000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>892000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>1828000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>-1407000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>337000</v>
       </c>
     </row>
-    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2552,228 +2600,237 @@
       <c r="AL25" s="3">
         <v>0</v>
       </c>
+      <c r="AM25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>7354000</v>
+      </c>
+      <c r="E26" s="3">
         <v>8033000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>7955000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>8971000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>9571000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>8566000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>8012000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>9346000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>8153000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>11843000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>13025000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>20198000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>18574000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>5750000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>9026000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>6942000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>4781000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>2796000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-20628000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-709000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-1169000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-770000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>4990000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>3247000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>3391000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>2406000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>6185000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>6446000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>3986000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>4783000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>2467000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>4085000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>3264000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>4090000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>2024000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>2889000</v>
       </c>
     </row>
-    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>7082000</v>
+      </c>
+      <c r="E27" s="3">
         <v>7713000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>7610000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>8610000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>9240000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>8220000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>7630000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>9070000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>7880000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>11430000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>12720000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>19660000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>17850000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>5480000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>8817000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>6750000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>4690000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>2730000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-20095000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-680000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-1080000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-610000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>4950000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>3170000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>3130000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>2350000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>5979000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>6240000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>3950000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>4650000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>2438000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>3970000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>3350000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>4010000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>1680000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>2650000</v>
       </c>
     </row>
-    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -2882,8 +2939,11 @@
       <c r="AL28" s="3">
         <v>0</v>
       </c>
+      <c r="AM28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -2915,10 +2975,10 @@
         <v>0</v>
       </c>
       <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3">
         <v>30000</v>
-      </c>
-      <c r="N29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="O29" s="3" t="s">
         <v>24</v>
@@ -2926,11 +2986,11 @@
       <c r="P29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="Q29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="R29" s="3">
         <v>53000</v>
-      </c>
-      <c r="R29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="S29" s="3" t="s">
         <v>24</v>
@@ -2938,11 +2998,11 @@
       <c r="T29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="U29" s="3">
+      <c r="U29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="V29" s="3">
         <v>25000</v>
-      </c>
-      <c r="V29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="W29" s="3" t="s">
         <v>24</v>
@@ -2950,11 +3010,11 @@
       <c r="X29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Y29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z29" s="3">
         <v>740000</v>
-      </c>
-      <c r="Z29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AA29" s="3" t="s">
         <v>24</v>
@@ -2962,11 +3022,11 @@
       <c r="AB29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AC29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AD29" s="3">
         <v>21000</v>
-      </c>
-      <c r="AD29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>24</v>
@@ -2974,11 +3034,11 @@
       <c r="AF29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AG29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AH29" s="3">
         <v>5942000</v>
-      </c>
-      <c r="AH29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AI29" s="3" t="s">
         <v>24</v>
@@ -2992,8 +3052,11 @@
       <c r="AL29" s="3" t="s">
         <v>24</v>
       </c>
+      <c r="AM29" s="3" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3102,8 +3165,11 @@
       <c r="AL30" s="3">
         <v>0</v>
       </c>
+      <c r="AM30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3212,228 +3278,237 @@
       <c r="AL31" s="3">
         <v>0</v>
       </c>
+      <c r="AM31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>1462000</v>
+      </c>
+      <c r="E32" s="3">
         <v>1369000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>1127000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>1481000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>1744000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>1842000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>1105000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>908000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>1382000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>2381000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-605000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-4632000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-3688000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-2538000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-3660000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-1894000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-1799000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-1595000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-802000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-774000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-328000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-1024000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-4149000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-1627000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-1600000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-1979000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-3642000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-2418000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-2045000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-2775000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-1203000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-1750000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-2051000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-2197000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-2640000</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-1910000</v>
       </c>
     </row>
-    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>7082000</v>
+      </c>
+      <c r="E33" s="3">
         <v>7713000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>7610000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>8610000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>9240000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>8220000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>7630000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>9070000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>7880000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>11430000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>12750000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>19660000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>17850000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>5480000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>8870000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>6750000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>4690000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>2730000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-20070000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-680000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-1080000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-610000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>5690000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>3170000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>3130000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>2350000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>6000000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>6240000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>3950000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>4650000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>8380000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>3970000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>3350000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>4010000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>1680000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>2650000</v>
       </c>
     </row>
-    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3542,233 +3617,242 @@
       <c r="AL34" s="3">
         <v>0</v>
       </c>
+      <c r="AM34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>7082000</v>
+      </c>
+      <c r="E35" s="3">
         <v>7713000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>7610000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>8610000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>9240000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>8220000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>7630000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>9070000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>7880000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>11430000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>12750000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>19660000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>17850000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>5480000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>8870000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>6750000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>4690000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>2730000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-20070000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-680000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-1080000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-610000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>5690000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>3170000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>3130000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>2350000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>6000000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>6240000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>3950000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>4650000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>8380000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>3970000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>3350000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>4010000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>1680000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>2650000</v>
       </c>
     </row>
-    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43465</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43373</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43281</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43190</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43100</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43008</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42825</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42735</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3807,8 +3891,9 @@
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
+      <c r="AM39" s="3"/>
     </row>
-    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3847,118 +3932,122 @@
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
+      <c r="AM40" s="3"/>
     </row>
-    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>14352000</v>
+      </c>
+      <c r="E41" s="3">
         <v>17036000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>23029000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>26926000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>26460000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>33320000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>31539000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>32944000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>29528000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>32651000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>29640000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>30407000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>18861000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>11074000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>6802000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>4768000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>3465000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>3515000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>4364000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>8832000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>12576000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>11412000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>3089000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>5351000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>4213000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>4586000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>3042000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>5669000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>3430000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>4125000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>3177000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>4266000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>4042000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>4897000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>3657000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>5093000</v>
       </c>
     </row>
-    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4067,41 +4156,44 @@
       <c r="AL42" s="3">
         <v>0</v>
       </c>
+      <c r="AM42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>41792000</v>
+      </c>
+      <c r="E43" s="3">
         <v>46303000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>43681000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>41505000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>43071000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>40366000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>38015000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>41814000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>35915000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>38808000</v>
       </c>
-      <c r="M43" s="3">
-        <v>0</v>
-      </c>
       <c r="N43" s="3">
         <v>0</v>
       </c>
@@ -4109,626 +4201,644 @@
         <v>0</v>
       </c>
       <c r="P43" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="3">
         <v>42142000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>32383000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>29516000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>28540000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>24755000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>20581000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>19974000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>19036000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>20871000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>26966000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>25308000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>27132000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>27105000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>24701000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>27880000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>26993000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>24686000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>25597000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>23263000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>21289000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>21842000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>21394000</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>20388000</v>
       </c>
     </row>
-    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>25371000</v>
+      </c>
+      <c r="E44" s="3">
         <v>24478000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>23524000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>23875000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>24503000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>23491000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>25120000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>24450000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>24249000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>23642000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>24435000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>24096000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>23585000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>22177000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>18780000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>19607000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>19275000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>18357000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>18850000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>17885000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>19657000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>16501000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>18528000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>17590000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>18835000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>18332000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>18958000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>18761000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>18483000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>18048000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>16992000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>16743000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>15305000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>14873000</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>15080000</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>15342000</v>
       </c>
     </row>
-    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>2234000</v>
+      </c>
+      <c r="E45" s="3">
         <v>1940000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1598000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1997000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>2176000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>2171000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1906000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1905000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2039000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2098000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1807000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2375000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2654000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1862000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1189000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1664000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1562000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1568000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1098000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>2002000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1747000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1465000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1469000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1759000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1563000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1553000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1272000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1665000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>1649000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>1456000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>1368000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>1480000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>1544000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>1519000</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>1285000</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>2122000</v>
       </c>
     </row>
-    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>85108000</v>
+      </c>
+      <c r="E46" s="3">
         <v>91233000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>91990000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>94349000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>96238000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>99377000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>96609000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>101142000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>91760000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>97224000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>97631000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>99289000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>93163000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>77255000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>59154000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>55555000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>52842000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>48195000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>44893000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>48693000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>53016000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>50249000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>50052000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>50008000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>51743000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>51576000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>47973000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>53975000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>50555000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>48315000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>47134000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>45752000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>42180000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>43131000</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>41416000</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>42945000</v>
       </c>
     </row>
-    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>39019000</v>
+      </c>
+      <c r="E47" s="3">
         <v>40356000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>34353000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>41447000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>40791000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>39995000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>34257000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>40062000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>39564000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>40825000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>49793000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>50235000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>46820000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>46329000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>45195000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>45641000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>44774000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>44181000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>43515000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>43609000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>43192000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>42981000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>43164000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>42920000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>42533000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>42068000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>40790000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>40427000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>39691000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>40350000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>39160000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>37649000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>37719000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>38268000</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>35102000</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>35553000</v>
       </c>
     </row>
-    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>295356000</v>
+      </c>
+      <c r="E48" s="3">
         <v>292646000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>301441000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>299543000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>298283000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>213723000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>221789000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>205862000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>206736000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>206023000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>204692000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>203102000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>209159000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>212773000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>216552000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>218795000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>223012000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>224641000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>227553000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>250496000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>250524000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>248409000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>259651000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>257065000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>257118000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>253003000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>247101000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>249153000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>248209000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>250352000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>252630000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>255556000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>252987000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>253147000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>244224000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>251923000</v>
       </c>
     </row>
-    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4837,8 +4947,11 @@
       <c r="AL49" s="3">
         <v>0</v>
       </c>
+      <c r="AM49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4947,8 +5060,11 @@
       <c r="AL50" s="3">
         <v>0</v>
       </c>
+      <c r="AM50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5057,118 +5173,124 @@
       <c r="AL51" s="3">
         <v>0</v>
       </c>
+      <c r="AM51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>28114000</v>
+      </c>
+      <c r="E52" s="3">
         <v>27673000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>21755000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>26577000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>25395000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>24823000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>20025000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>25193000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>25188000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>25299000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>16951000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>17526000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>18632000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>18414000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>18022000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>16697000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>16661000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>16753000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>16789000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>15245000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>14763000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>14165000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>9730000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>9368000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>9335000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>9542000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>10332000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>11073000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>10335000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>9809000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>9767000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>10470000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>10126000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>9663000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>9572000</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>8965000</v>
       </c>
     </row>
-    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5277,118 +5399,124 @@
       <c r="AL53" s="3">
         <v>0</v>
       </c>
+      <c r="AM53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>447597000</v>
+      </c>
+      <c r="E54" s="3">
         <v>451908000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>453475000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>461916000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>460707000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>377918000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>376317000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>372259000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>363248000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>369371000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>369067000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>370152000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>367774000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>354771000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>338923000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>336688000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>337289000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>333770000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>332750000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>358043000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>361495000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>355804000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>362597000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>359361000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>360729000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>356189000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>346196000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>354628000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>348790000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>348826000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>348691000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>349427000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>343012000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>344209000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>330314000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>339386000</v>
       </c>
     </row>
-    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5427,8 +5555,9 @@
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
+      <c r="AM55" s="3"/>
     </row>
-    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5467,668 +5596,687 @@
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
     </row>
-    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>59725000</v>
+      </c>
+      <c r="E57" s="3">
         <v>63987000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>36145000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>60518000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>60107000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>59531000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>31249000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>62257000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>54404000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>59935000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>63197000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>62550000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>67958000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>63501000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>50766000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>47257000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>45780000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>41017000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>35221000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>33340000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>33216000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>35815000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>40605000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>39336000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>40324000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>41190000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>37268000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>41714000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>38490000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>37207000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>36796000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>34698000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>31100000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>32069000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>31193000</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>30027000</v>
       </c>
     </row>
-    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>5419000</v>
+      </c>
+      <c r="E58" s="3">
         <v>4728000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>6813000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>5632000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>6621000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>8227000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>5712000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>4743000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>3929000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>2296000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>634000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>6182000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>7367000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>4886000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>4276000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>12966000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>15293000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>18185000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>20458000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>21911000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>22952000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>27755000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>20593000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>21219000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>26227000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>21828000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>17258000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>19413000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>20500000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>19836000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>17930000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>15741000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>17185000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>18483000</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>13830000</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>17239000</v>
       </c>
     </row>
-    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>3017000</v>
+      </c>
+      <c r="E59" s="3">
         <v>5114000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>23772000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>3843000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>4035000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>4163000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>24538000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>4186000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>3482000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>4435000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>5214000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>5325000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>4785000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>3672000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1601000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1633000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1165000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>948000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>684000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1217000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1102000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1203000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>2791000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>3640000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>3736000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>3614000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>2612000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>4161000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>3457000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>3263000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>3045000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>3338000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>2664000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>2822000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>2615000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>2755000</v>
       </c>
     </row>
-    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>68161000</v>
+      </c>
+      <c r="E60" s="3">
         <v>73829000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>70307000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>69993000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>70763000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>71921000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>65316000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>71186000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>61815000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>66666000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>69045000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>74057000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>80110000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>72059000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>56643000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>61856000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>62238000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>60150000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>56363000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>56468000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>57270000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>64773000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>63989000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>64195000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>70287000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>66632000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>57138000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>65288000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>62447000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>60306000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>57771000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>53777000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>50949000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>53374000</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>47638000</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>50021000</v>
       </c>
     </row>
-    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>33570000</v>
+      </c>
+      <c r="E61" s="3">
         <v>32823000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>41496000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>36918000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>36565000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>32213000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>41997000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>36510000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>37567000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>39150000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>40559000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>39246000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>39516000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>42651000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>43428000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>43639000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>45319000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>45137000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>47182000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>46888000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>46563000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>31857000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>26481000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>26089000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>19141000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>19177000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>20538000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>20624000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>20720000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>20781000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>24406000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>24869000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>24750000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>25124000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>28932000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>28916000</v>
       </c>
     </row>
-    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>26184000</v>
+      </c>
+      <c r="E62" s="3">
         <v>26344000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>22324000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>27647000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>26635000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>26151000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>21518000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>22944000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>23131000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>23763000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>56990000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>63806000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>63640000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>63535000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>63169000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>63687000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>64176000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>64382000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>65075000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>70075000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>70509000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>70431000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>73189000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>71968000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>72836000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>72359000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>69992000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>71885000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>72090000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>72828000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>72014000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>81583000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>81475000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>81940000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>79914000</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>83439000</v>
       </c>
     </row>
-    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6237,8 +6385,11 @@
       <c r="AL63" s="3">
         <v>0</v>
       </c>
+      <c r="AM63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -6347,8 +6498,11 @@
       <c r="AL64" s="3">
         <v>0</v>
       </c>
+      <c r="AM64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6457,118 +6611,124 @@
       <c r="AL65" s="3">
         <v>0</v>
       </c>
+      <c r="AM65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>177635000</v>
+      </c>
+      <c r="E66" s="3">
         <v>182102000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>182869000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>185516000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>184441000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>164866000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>163779000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>164726000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>156251000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>162957000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>174018000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>184052000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>190458000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>185556000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>170346000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>176099000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>178718000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>176796000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>175600000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>180643000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>181312000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>173725000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>170947000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>169446000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>169352000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>164967000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>154402000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>164263000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>161568000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>160631000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>161003000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>167151000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>163834000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>167058000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>162989000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>168789000</v>
       </c>
     </row>
-    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6607,8 +6767,9 @@
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
+      <c r="AM67" s="3"/>
     </row>
-    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6717,8 +6878,11 @@
       <c r="AL68" s="3">
         <v>0</v>
       </c>
+      <c r="AM68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6827,8 +6991,11 @@
       <c r="AL69" s="3">
         <v>0</v>
       </c>
+      <c r="AM69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6937,8 +7104,11 @@
       <c r="AL70" s="3">
         <v>0</v>
       </c>
+      <c r="AM70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7047,118 +7217,124 @@
       <c r="AL71" s="3">
         <v>0</v>
       </c>
+      <c r="AM71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>477061000</v>
+      </c>
+      <c r="E72" s="3">
         <v>474290000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>470903000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>467664000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>463294000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>458339000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>453927000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>450138000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>444731000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>440552000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>432860000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>423877000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>407902000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>393779000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>392059000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>386952000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>383922000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>382953000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>383943000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>407728000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>412124000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>416919000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>421341000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>419367000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>419913000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>420498000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>421653000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>419155000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>416418000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>415970000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>414540000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>409449000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>408768000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>408707000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>407831000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>409284000</v>
       </c>
     </row>
-    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7267,8 +7443,11 @@
       <c r="AL73" s="3">
         <v>0</v>
       </c>
+      <c r="AM73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7377,8 +7556,11 @@
       <c r="AL74" s="3">
         <v>0</v>
       </c>
+      <c r="AM74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7487,118 +7669,124 @@
       <c r="AL75" s="3">
         <v>0</v>
       </c>
+      <c r="AM75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>262593000</v>
+      </c>
+      <c r="E76" s="3">
         <v>262720000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>263705000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>268592000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>268405000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>205250000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>204802000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>199703000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>199046000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>198685000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>195049000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>186100000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>177316000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>169215000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>168577000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>160589000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>158571000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>156974000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>157150000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>177400000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>180183000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>182079000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>191650000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>189915000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>191377000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>191222000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>191794000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>190365000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>187222000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>188195000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>187688000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>182276000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>179178000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>177151000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>167325000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>170597000</v>
       </c>
     </row>
-    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7707,233 +7895,242 @@
       <c r="AL77" s="3">
         <v>0</v>
       </c>
+      <c r="AM77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43465</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43373</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43281</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43190</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43100</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43008</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42825</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42735</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>7082000</v>
+      </c>
+      <c r="E81" s="3">
         <v>7713000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>7610000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>8610000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>9240000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>8220000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>7630000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>9070000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>7880000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>11430000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>12750000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>19660000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>17850000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>5480000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>8870000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>6750000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>4690000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>2730000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-20070000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-680000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-1080000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-610000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>5690000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>3170000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>3130000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>2350000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>6000000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>6240000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>3950000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>4650000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>8380000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>3970000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>3350000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>4010000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>1680000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>2650000</v>
       </c>
     </row>
-    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7972,118 +8169,122 @@
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
+      <c r="AM82" s="3"/>
     </row>
-    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>5787000</v>
+      </c>
+      <c r="E83" s="3">
         <v>4812000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>4440000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>4415000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>4242000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>4244000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>-3108000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>12289000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>4451000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>5908000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>5064000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>5642000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>4451000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>4283000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>5661000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>4990000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>4952000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>5004000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>30291000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>4983000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>4916000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>5819000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>4923000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>4873000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>4631000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>4571000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>5028000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>4658000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>4589000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>4470000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>5842000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>4880000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>4652000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>4519000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>8117000</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>4605000</v>
       </c>
     </row>
-    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8192,8 +8393,11 @@
       <c r="AL84" s="3">
         <v>0</v>
       </c>
+      <c r="AM84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8302,8 +8506,11 @@
       <c r="AL85" s="3">
         <v>0</v>
       </c>
+      <c r="AM85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8412,8 +8619,11 @@
       <c r="AL86" s="3">
         <v>0</v>
       </c>
+      <c r="AM86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8522,8 +8732,11 @@
       <c r="AL87" s="3">
         <v>0</v>
       </c>
+      <c r="AM87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8632,118 +8845,124 @@
       <c r="AL88" s="3">
         <v>0</v>
       </c>
+      <c r="AM88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>11550000</v>
+      </c>
+      <c r="E89" s="3">
         <v>12953000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>12229000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>17569000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>10560000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>14664000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>13682000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>15963000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>9383000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>16341000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>17621000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>24425000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>19963000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>14788000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>17124000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>12091000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>9650000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>9264000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>4005000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>4389000</v>
       </c>
-      <c r="W89" s="3">
-        <v>0</v>
-      </c>
       <c r="X89" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y89" s="3">
         <v>6274000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>6352000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>9079000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>5947000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>8338000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>8607000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>11108000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>7780000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>8519000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>7411000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>7535000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>6947000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>8173000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>7396000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>5355000</v>
       </c>
     </row>
-    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8782,118 +9001,122 @@
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
     </row>
-    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-6283000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-5898000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-6837000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-6160000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-6235000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-5074000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-6228000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-4920000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-5359000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-5412000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-5783000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-4876000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-3837000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-3911000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-4089000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-2840000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-2747000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-2400000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-3629000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-3291000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-4417000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-5945000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-6704000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-6285000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-6173000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-5199000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-6094000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-5204000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-4927000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-3349000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-4501000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-4913000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-3098000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-2890000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-3887000</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-3404000</v>
       </c>
     </row>
-    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9002,8 +9225,11 @@
       <c r="AL92" s="3">
         <v>0</v>
       </c>
+      <c r="AM92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9112,118 +9338,124 @@
       <c r="AL93" s="3">
         <v>0</v>
       </c>
+      <c r="AM93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-6180000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-4135000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-4252000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-6240000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-4869000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-4577000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-5714000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-4279000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-4356000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-4925000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-5355000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-2378000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-3064000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-3945000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-2110000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-3054000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-2716000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-2355000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-3302000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-3709000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-5081000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-6367000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-4264000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-6150000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-6877000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-5793000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-5584000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-3907000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-5096000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-1859000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-6536000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-2555000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-2878000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-3761000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-1672000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-3235000</v>
       </c>
     </row>
-    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9262,100 +9494,101 @@
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
+      <c r="AM95" s="3"/>
     </row>
-    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>4288000</v>
+      </c>
+      <c r="E96" s="3">
         <v>4335000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>4371000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>4240000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>4285000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>3808000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>3839000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>3663000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>3701000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>3738000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-3767000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-3685000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-3727000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-3760000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-3763000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-3720000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-3721000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-3720000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-3715000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-3716000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-3715000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-3719000</v>
-      </c>
-      <c r="Y96" s="3">
-        <v>-3716000</v>
       </c>
       <c r="Z96" s="3">
         <v>-3716000</v>
       </c>
       <c r="AA96" s="3">
+        <v>-3716000</v>
+      </c>
+      <c r="AB96" s="3">
         <v>-3715000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-3505000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-3502000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-3503000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-3502000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-3291000</v>
-      </c>
-      <c r="AG96" s="3">
-        <v>-3289000</v>
       </c>
       <c r="AH96" s="3">
         <v>-3289000</v>
@@ -9364,16 +9597,19 @@
         <v>-3289000</v>
       </c>
       <c r="AJ96" s="3">
+        <v>-3289000</v>
+      </c>
+      <c r="AK96" s="3">
         <v>-3134000</v>
-      </c>
-      <c r="AK96" s="3">
-        <v>-3133000</v>
       </c>
       <c r="AL96" s="3">
         <v>-3133000</v>
       </c>
+      <c r="AM96" s="3">
+        <v>-3133000</v>
+      </c>
     </row>
-    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9482,8 +9718,11 @@
       <c r="AL97" s="3">
         <v>0</v>
       </c>
+      <c r="AM97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9592,8 +9831,11 @@
       <c r="AL98" s="3">
         <v>0</v>
       </c>
+      <c r="AM98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9702,334 +9944,346 @@
       <c r="AL99" s="3">
         <v>0</v>
       </c>
+      <c r="AM99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-8685000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-13579000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-11143000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-11106000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-12558000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-7982000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-9555000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-8059000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-8176000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-8507000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-13937000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-9793000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-8671000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-6713000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-12959000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-7657000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-7022000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-7785000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-5283000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-4494000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>6277000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>8785000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-4456000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-1666000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>548000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-1044000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-5501000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-4959000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-3244000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-5742000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-1837000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-4988000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-5059000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-3246000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-6746000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-1296000</v>
       </c>
     </row>
-    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-324000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>182000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-209000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>30000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>102000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>872000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-651000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-441000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>142000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>872000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-651000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-441000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>142000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-21000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-77000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>38000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>27000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>112000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>70000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-32000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-369000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>106000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-125000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>9000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>43000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-149000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-3000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-135000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>30000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-127000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>232000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>135000</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>74000</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-414000</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>-89000</v>
       </c>
     </row>
-    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-2801000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-4675000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-3785000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>484000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-6861000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>1781000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1405000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>3416000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-3119000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>3011000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-799000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>11603000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>7787000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>4272000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>2034000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>1303000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-50000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-849000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-4468000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-3744000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>1164000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>8323000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-2262000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>1138000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-373000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>1544000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-2627000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>2239000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-695000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>948000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-1089000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>224000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-855000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>1240000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-1436000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>735000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/XOM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/XOM_QTR_FIN.xlsx
@@ -656,491 +656,503 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AN102"/>
+  <dimension ref="A5:AO102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="40" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="41" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43830</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43738</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43646</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43555</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43465</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43373</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43281</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43190</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43008</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42916</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42825</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42735</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>80039000</v>
+      </c>
+      <c r="E8" s="3">
         <v>83331000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>79477000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>81058000</v>
       </c>
-      <c r="G8" s="3">
-        <v>82379000</v>
-      </c>
       <c r="H8" s="3">
+        <v>81058000</v>
+      </c>
+      <c r="I8" s="3">
         <v>87792000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>89986000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>80411000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>81098000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>89852000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>81532000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>84183000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>93164000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>106512000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>111265000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>87734000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>81305000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>71892000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>65943000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>57552000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>45738000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>45425000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>32277000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>55134000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>63024000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>63422000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>67491000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>61646000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>68253000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>74187000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>71456000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>65436000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>50832000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>59350000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>56026000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>56474000</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>40396000</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>56767000</v>
       </c>
     </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>53015000</v>
+      </c>
+      <c r="E9" s="3">
         <v>58022000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>55429000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>56871000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>54064000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>61142000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>64003000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>56692000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>53558000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>61772000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>56458000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>55439000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>61126000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>71514000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>76299000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>62629000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>56272000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>48464000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>45800000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>40663000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>32041000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>31053000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>20964000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>40380000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>44254000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>44138000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>48464000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>43771000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>46957000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>50873000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>50245000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>44779000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>28979000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>45248000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>43843000</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>43267000</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>21193000</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>41181000</v>
       </c>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>27024000</v>
+      </c>
+      <c r="E10" s="3">
         <v>25309000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>24048000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>24187000</v>
       </c>
-      <c r="G10" s="3">
-        <v>28315000</v>
-      </c>
       <c r="H10" s="3">
+        <v>26994000</v>
+      </c>
+      <c r="I10" s="3">
         <v>26650000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>25983000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>23719000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>27540000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>28080000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>25074000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>28744000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>32038000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>34998000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>34966000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>25105000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>25033000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>23428000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>20143000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>16889000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>13697000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>14372000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>11313000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>14754000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>18770000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>19284000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>19027000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>17875000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>21296000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>23314000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>21211000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>20657000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>21853000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>14102000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>12183000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>13207000</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>19203000</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>15586000</v>
       </c>
     </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1181,13 +1193,14 @@
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>24</v>
+      <c r="D12" s="3">
+        <v>1228000</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>24</v>
@@ -1195,11 +1208,11 @@
       <c r="F12" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="G12" s="3">
+      <c r="G12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H12" s="3">
         <v>987000</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="I12" s="3" t="s">
         <v>24</v>
@@ -1207,11 +1220,11 @@
       <c r="J12" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="K12" s="3">
+      <c r="K12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L12" s="3">
         <v>879000</v>
-      </c>
-      <c r="L12" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="M12" s="3" t="s">
         <v>24</v>
@@ -1219,86 +1232,89 @@
       <c r="N12" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="O12" s="3">
+      <c r="O12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="P12" s="3">
         <v>348000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>218000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>286000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>173000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>524000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>190000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>176000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>164000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>595000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>188000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>214000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>288000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>357000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>299000</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>333000</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>280000</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>555000</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>292000</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>332000</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>287000</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>703000</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>284000</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>514000</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>289000</v>
       </c>
-      <c r="AM12" s="3">
+      <c r="AN12" s="3">
         <v>340000</v>
       </c>
-      <c r="AN12" s="3">
+      <c r="AO12" s="3">
         <v>327000</v>
       </c>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1413,25 +1429,28 @@
       <c r="AN13" s="3">
         <v>0</v>
       </c>
+      <c r="AO13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>587000</v>
+      </c>
+      <c r="E14" s="3">
         <v>155000</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H14" s="3">
         <v>-615000</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>24</v>
@@ -1439,11 +1458,11 @@
       <c r="J14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L14" s="3">
         <v>2787000</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>24</v>
@@ -1451,8 +1470,8 @@
       <c r="N14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
@@ -1461,10 +1480,10 @@
         <v>0</v>
       </c>
       <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>4600000</v>
-      </c>
-      <c r="S14" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="T14" s="3" t="s">
         <v>24</v>
@@ -1475,26 +1494,26 @@
       <c r="V14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="W14" s="3">
+      <c r="W14" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="X14" s="3">
         <v>24875000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>62000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>64000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>910000</v>
-      </c>
-      <c r="AA14" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AB14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AC14" s="3">
-        <v>0</v>
+      <c r="AC14" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="AD14" s="3">
         <v>0</v>
@@ -1529,124 +1548,130 @@
       <c r="AN14" s="3">
         <v>0</v>
       </c>
+      <c r="AO14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>5975000</v>
+      </c>
+      <c r="E15" s="3">
         <v>6320000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>6101000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>5702000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>5977000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>6258000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>5787000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>4812000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>4440000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>4415000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>4242000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>4244000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>5064000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>5642000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>4451000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>4283000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>5661000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>4990000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>4952000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>5004000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>5416000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>4921000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>4852000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>4909000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>4923000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>4873000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>4631000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>4571000</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>5028000</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>4658000</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>4589000</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>4470000</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>5842000</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>4880000</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>4652000</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>4519000</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>8117000</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>4605000</v>
       </c>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1684,240 +1709,247 @@
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
+      <c r="AO16" s="3"/>
     </row>
-    <row r="17" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>72414000</v>
+      </c>
+      <c r="E17" s="3">
         <v>74117000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>70656000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>71325000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>72708000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>76783000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>79124000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>70493000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>70147000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>76892000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>71009000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>69602000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>74720000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>85513000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>89826000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>81528000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>73015000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>63966000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>61181000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>55297000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>72840000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>46292000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>33928000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>56167000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>60527000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>60061000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>64243000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>59155000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>63559000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>67325000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>66842000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>60767000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>48832000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>55406000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>53763000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>52607000</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>42224000</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>55345000</v>
       </c>
     </row>
-    <row r="18" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>7625000</v>
+      </c>
+      <c r="E18" s="3">
         <v>9214000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>8821000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>9733000</v>
       </c>
-      <c r="G18" s="3">
-        <v>9671000</v>
-      </c>
       <c r="H18" s="3">
+        <v>8350000</v>
+      </c>
+      <c r="I18" s="3">
         <v>11009000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>10862000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>9918000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>10951000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>12960000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>10523000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>14581000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>18444000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>20999000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>21439000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>6206000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>8290000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>7926000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>4762000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>2255000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-27102000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-867000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-1651000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-1033000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>2497000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>3361000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>3248000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>2491000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>4694000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>6862000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>4614000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>4669000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>2000000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>3944000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>2263000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>3867000</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>-1828000</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>1422000</v>
       </c>
     </row>
-    <row r="19" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1958,588 +1990,604 @@
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
     </row>
-    <row r="20" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>56000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-1963000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-2029000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-2072000</v>
       </c>
-      <c r="G20" s="3">
-        <v>1776000</v>
-      </c>
       <c r="H20" s="3">
+        <v>455000</v>
+      </c>
+      <c r="I20" s="3">
         <v>-2224000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-3074000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-2672000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-1105000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-908000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-1382000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-2381000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>605000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>4632000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>3688000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>2538000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>3660000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>1894000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>1799000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>1595000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>802000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>774000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>328000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>1024000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>4149000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>1627000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>1600000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>1979000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>3642000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>2418000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>2045000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>2775000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>1203000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>1750000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>2051000</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>2197000</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>2640000</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>1910000</v>
       </c>
     </row>
-    <row r="21" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>13544000</v>
+      </c>
+      <c r="E21" s="3">
         <v>17497000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>16951000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>17507000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>13872000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>19491000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>19723000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>17402000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>16496000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>18283000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>16147000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>21206000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>24113000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>31273000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>29578000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>13027000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>17611000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>14810000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>11513000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>8854000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>3991000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>4890000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>3593000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>5810000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>11569000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>9861000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>9479000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>9041000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>13364000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>13938000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>11248000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>11914000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>9045000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>10574000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>8966000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>10583000</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>8929000</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>7937000</v>
       </c>
     </row>
-    <row r="22" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>163000</v>
+      </c>
+      <c r="E22" s="3">
         <v>90000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>145000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>205000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>297000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>207000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>271000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>221000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>272000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>169000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>249000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>159000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>207000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>209000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>194000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>188000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>221000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>214000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>254000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>258000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>313000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>279000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>317000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>249000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>232000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>267000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>216000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>181000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>215000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>200000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>147000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>204000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>186000</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>111000</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>158000</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>146000</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>195000</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>106000</v>
       </c>
     </row>
-    <row r="23" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>8031000</v>
+      </c>
+      <c r="E23" s="3">
         <v>10932000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>10705000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>11600000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>9813000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>13026000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>13665000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>12369000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>10625000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>13699000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>11656000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>16803000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>18842000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>25422000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>24933000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>8556000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>11729000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>9606000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>6307000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>3592000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-26613000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-372000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-1640000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-258000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>6414000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>4721000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>4632000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>4289000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>8121000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>9080000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>6512000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>7240000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>3017000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>5583000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>4156000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>5918000</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>617000</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>3226000</v>
       </c>
     </row>
-    <row r="24" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>1422000</v>
+      </c>
+      <c r="E24" s="3">
         <v>3164000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>3351000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>3567000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1858000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>4055000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>4094000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>3803000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>2613000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>4353000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>3503000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>4960000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>5817000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>5224000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>6359000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>2806000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>2703000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>2664000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>1526000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>796000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-5985000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>337000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-471000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>512000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>1424000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>1474000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>1241000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>1883000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>1936000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>2634000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>2526000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>2457000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>550000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>1498000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>892000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>1828000</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>-1407000</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>337000</v>
       </c>
     </row>
-    <row r="25" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2654,240 +2702,249 @@
       <c r="AN25" s="3">
         <v>0</v>
       </c>
+      <c r="AO25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>6609000</v>
+      </c>
+      <c r="E26" s="3">
         <v>7768000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>7354000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>8033000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>7955000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>8971000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>9571000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>8566000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>8012000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>9346000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>8153000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>11843000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>13025000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>20198000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>18574000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>5750000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>9026000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>6942000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>4781000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>2796000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-20628000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-709000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-1169000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-770000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>4990000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>3247000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>3391000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>2406000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>6185000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>6446000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>3986000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>4783000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>2467000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>4085000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>3264000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>4090000</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>2024000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>2889000</v>
       </c>
     </row>
-    <row r="27" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>6501000</v>
+      </c>
+      <c r="E27" s="3">
         <v>7548000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>7082000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>7713000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>7610000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>8610000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>9240000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>8220000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>7630000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>9070000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>7880000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>11430000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>12720000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>19660000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>17850000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>5480000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>8817000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>6750000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>4690000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>2730000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-20095000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-680000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-1080000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-610000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>4950000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>3170000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>3130000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>2350000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>5979000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>6240000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>3950000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>4650000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>2438000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>3970000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>3350000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>4010000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>1680000</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>2650000</v>
       </c>
     </row>
-    <row r="28" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -3002,8 +3059,11 @@
       <c r="AN28" s="3">
         <v>0</v>
       </c>
+      <c r="AO28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -3041,10 +3101,10 @@
         <v>0</v>
       </c>
       <c r="O29" s="3">
+        <v>0</v>
+      </c>
+      <c r="P29" s="3">
         <v>30000</v>
-      </c>
-      <c r="P29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="Q29" s="3" t="s">
         <v>24</v>
@@ -3052,11 +3112,11 @@
       <c r="R29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="S29" s="3">
+      <c r="S29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="T29" s="3">
         <v>53000</v>
-      </c>
-      <c r="T29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="U29" s="3" t="s">
         <v>24</v>
@@ -3064,11 +3124,11 @@
       <c r="V29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="W29" s="3">
+      <c r="W29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="X29" s="3">
         <v>25000</v>
-      </c>
-      <c r="X29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="Y29" s="3" t="s">
         <v>24</v>
@@ -3076,11 +3136,11 @@
       <c r="Z29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AA29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AB29" s="3">
         <v>740000</v>
-      </c>
-      <c r="AB29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AC29" s="3" t="s">
         <v>24</v>
@@ -3088,11 +3148,11 @@
       <c r="AD29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AE29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AF29" s="3">
         <v>21000</v>
-      </c>
-      <c r="AF29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AG29" s="3" t="s">
         <v>24</v>
@@ -3100,11 +3160,11 @@
       <c r="AH29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AI29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AJ29" s="3">
         <v>5942000</v>
-      </c>
-      <c r="AJ29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AK29" s="3" t="s">
         <v>24</v>
@@ -3118,8 +3178,11 @@
       <c r="AN29" s="3" t="s">
         <v>24</v>
       </c>
+      <c r="AO29" s="3" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="30" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3234,8 +3297,11 @@
       <c r="AN30" s="3">
         <v>0</v>
       </c>
+      <c r="AO30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3350,240 +3416,249 @@
       <c r="AN31" s="3">
         <v>0</v>
       </c>
+      <c r="AO31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-56000</v>
+      </c>
+      <c r="E32" s="3">
         <v>1963000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>2029000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>2072000</v>
       </c>
-      <c r="G32" s="3">
-        <v>-1776000</v>
-      </c>
       <c r="H32" s="3">
+        <v>-455000</v>
+      </c>
+      <c r="I32" s="3">
         <v>2224000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>3074000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>2672000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>1105000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>908000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>1382000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>2381000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-605000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-4632000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-3688000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-2538000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-3660000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-1894000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-1799000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-1595000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-802000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-774000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-328000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-1024000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-4149000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-1627000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-1600000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-1979000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-3642000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-2418000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-2045000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-2775000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-1203000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-1750000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-2051000</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-2197000</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-2640000</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-1910000</v>
       </c>
     </row>
-    <row r="33" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>6501000</v>
+      </c>
+      <c r="E33" s="3">
         <v>7548000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>7082000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>7713000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>7610000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>8610000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>9240000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>8220000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>7630000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>9070000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>7880000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>11430000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>12750000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>19660000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>17850000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>5480000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>8870000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>6750000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>4690000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>2730000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-20070000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-680000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-1080000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-610000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>5690000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>3170000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>3130000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>2350000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>6000000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>6240000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>3950000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>4650000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>8380000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>3970000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>3350000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>4010000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>1680000</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>2650000</v>
       </c>
     </row>
-    <row r="34" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3698,245 +3773,254 @@
       <c r="AN34" s="3">
         <v>0</v>
       </c>
+      <c r="AO34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>6501000</v>
+      </c>
+      <c r="E35" s="3">
         <v>7548000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>7082000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>7713000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>7610000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>8610000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>9240000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>8220000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>7630000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>9070000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>7880000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>11430000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>12750000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>19660000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>17850000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>5480000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>8870000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>6750000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>4690000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>2730000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-20070000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-680000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-1080000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-610000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>5690000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>3170000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>3130000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>2350000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>6000000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>6240000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>3950000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>4650000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>8380000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>3970000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>3350000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>4010000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>1680000</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>2650000</v>
       </c>
     </row>
-    <row r="37" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43830</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43738</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43646</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43555</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43465</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43373</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43281</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43190</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43008</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42916</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42825</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42735</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3977,8 +4061,9 @@
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
+      <c r="AO39" s="3"/>
     </row>
-    <row r="40" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4019,124 +4104,128 @@
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
+      <c r="AO40" s="3"/>
     </row>
-    <row r="41" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>10681000</v>
+      </c>
+      <c r="E41" s="3">
         <v>13814000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>14352000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>17036000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>23029000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>26926000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>26460000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>33320000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>31539000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>32944000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>29528000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>32651000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>29640000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>30407000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>18861000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>11074000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>6802000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>4768000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>3465000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>3515000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>4364000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>8832000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>12576000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>11412000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>3089000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>5351000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>4213000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>4586000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>3042000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>5669000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>3430000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>4125000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>3177000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>4266000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>4042000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>4897000</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>3657000</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>5093000</v>
       </c>
     </row>
-    <row r="42" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4251,47 +4340,50 @@
       <c r="AN42" s="3">
         <v>0</v>
       </c>
+      <c r="AO42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>44562000</v>
+      </c>
+      <c r="E43" s="3">
         <v>45285000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>41792000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>46303000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>43681000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>41505000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>43071000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>40366000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>38015000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>41814000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>35915000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>38808000</v>
       </c>
-      <c r="O43" s="3">
-        <v>0</v>
-      </c>
       <c r="P43" s="3">
         <v>0</v>
       </c>
@@ -4299,656 +4391,674 @@
         <v>0</v>
       </c>
       <c r="R43" s="3">
+        <v>0</v>
+      </c>
+      <c r="S43" s="3">
         <v>42142000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>32383000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>29516000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>28540000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>24755000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>20581000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>19974000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>19036000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>20871000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>26966000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>25308000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>27132000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>27105000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>24701000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>27880000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>26993000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>24686000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>25597000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>23263000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>21289000</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>21842000</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>21394000</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>20388000</v>
       </c>
     </row>
-    <row r="44" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>26302000</v>
+      </c>
+      <c r="E44" s="3">
         <v>27238000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>25371000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>24478000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>23524000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>23875000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>24503000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>23491000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>25120000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>24450000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>24249000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>23642000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>24435000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>24096000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>23585000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>22177000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>18780000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>19607000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>19275000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>18357000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>18850000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>17885000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>19657000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>16501000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>18528000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>17590000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>18835000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>18332000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>18958000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>18761000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>18483000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>18048000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>16992000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>16743000</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>15305000</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>14873000</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>15080000</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>15342000</v>
       </c>
     </row>
-    <row r="45" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1837000</v>
+      </c>
+      <c r="E45" s="3">
         <v>2113000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>2234000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1940000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1598000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1997000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>2176000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2171000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1906000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1905000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2039000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2098000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1807000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>2375000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>2654000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1862000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1189000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1664000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1562000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1568000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1098000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>2002000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1747000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1465000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1469000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1759000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1563000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1553000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>1272000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>1665000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>1649000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>1456000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>1368000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>1480000</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>1544000</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>1519000</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>1285000</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>2122000</v>
       </c>
     </row>
-    <row r="46" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>83382000</v>
+      </c>
+      <c r="E46" s="3">
         <v>88505000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>85108000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>91233000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>91990000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>94349000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>96238000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>99377000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>96609000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>101142000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>91760000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>97224000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>97631000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>99289000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>93163000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>77255000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>59154000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>55555000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>52842000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>48195000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>44893000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>48693000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>53016000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>50249000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>50052000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>50008000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>51743000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>51576000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>47973000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>53975000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>50555000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>48315000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>47134000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>45752000</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>42180000</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>43131000</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>41416000</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>42945000</v>
       </c>
     </row>
-    <row r="47" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>32924000</v>
+      </c>
+      <c r="E47" s="3">
         <v>39102000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>39019000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>40356000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>34353000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>41447000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>40791000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>39995000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>34257000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>40062000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>39564000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>40825000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>49793000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>50235000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>46820000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>46329000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>45195000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>45641000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>44774000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>44181000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>43515000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>43609000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>43192000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>42981000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>43164000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>42920000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>42533000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>42068000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>40790000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>40427000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>39691000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>40350000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>39160000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>37649000</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>37719000</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>38268000</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>35102000</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>35553000</v>
       </c>
     </row>
-    <row r="48" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>306597000</v>
+      </c>
+      <c r="E48" s="3">
         <v>298388000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>295356000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>292646000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>301441000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>299543000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>298283000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>213723000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>221789000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>205862000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>206736000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>206023000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>204692000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>203102000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>209159000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>212773000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>216552000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>218795000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>223012000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>224641000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>227553000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>250496000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>250524000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>248409000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>259651000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>257065000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>257118000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>253003000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>247101000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>249153000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>248209000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>250352000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>252630000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>255556000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>252987000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>253147000</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>244224000</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>251923000</v>
       </c>
     </row>
-    <row r="49" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -5063,8 +5173,11 @@
       <c r="AN49" s="3">
         <v>0</v>
       </c>
+      <c r="AO49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5179,8 +5292,11 @@
       <c r="AN50" s="3">
         <v>0</v>
       </c>
+      <c r="AO50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5295,124 +5411,130 @@
       <c r="AN51" s="3">
         <v>0</v>
       </c>
+      <c r="AO51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>22318000</v>
+      </c>
+      <c r="E52" s="3">
         <v>28345000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>28114000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>27673000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>21755000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>26577000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>25395000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>24823000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>20025000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>25193000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>25188000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>25299000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>16951000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>17526000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>18632000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>18414000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>18022000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>16697000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>16661000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>16753000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>16789000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>15245000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>14763000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>14165000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>9730000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>9368000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>9335000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>9542000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>10332000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>11073000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>10335000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>9809000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>9767000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>10470000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>10126000</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>9663000</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>9572000</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>8965000</v>
       </c>
     </row>
-    <row r="53" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5527,124 +5649,130 @@
       <c r="AN53" s="3">
         <v>0</v>
       </c>
+      <c r="AO53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>448980000</v>
+      </c>
+      <c r="E54" s="3">
         <v>454340000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>447597000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>451908000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>453475000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>461916000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>460707000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>377918000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>376317000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>372259000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>363248000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>369371000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>369067000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>370152000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>367774000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>354771000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>338923000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>336688000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>337289000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>333770000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>332750000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>358043000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>361495000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>355804000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>362597000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>359361000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>360729000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>356189000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>346196000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>354628000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>348790000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>348826000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>348691000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>349427000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>343012000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>344209000</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>330314000</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>339386000</v>
       </c>
     </row>
-    <row r="55" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5685,8 +5813,9 @@
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
+      <c r="AO55" s="3"/>
     </row>
-    <row r="56" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5727,704 +5856,723 @@
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
+      <c r="AO56" s="3"/>
     </row>
-    <row r="57" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>36049000</v>
+      </c>
+      <c r="E57" s="3">
         <v>65382000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>59725000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>63987000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>36145000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>60518000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>60107000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>59531000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>31249000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>62257000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>54404000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>59935000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>63197000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>62550000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>67958000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>63501000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>50766000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>47257000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>45780000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>41017000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>35221000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>33340000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>33216000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>35815000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>40605000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>39336000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>40324000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>41190000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>37268000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>41714000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>38490000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>37207000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>36796000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>34698000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>31100000</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>32069000</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>31193000</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>30027000</v>
       </c>
     </row>
-    <row r="58" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>11245000</v>
+      </c>
+      <c r="E58" s="3">
         <v>9212000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>5419000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>4728000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>6813000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>5632000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>6621000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>8227000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>5712000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>4743000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>3929000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>2296000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>634000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>6182000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>7367000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>4886000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>4276000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>12966000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>15293000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>18185000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>20458000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>21911000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>22952000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>27755000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>20593000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>21219000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>26227000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>21828000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>17258000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>19413000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>20500000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>19836000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>17930000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>15741000</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>17185000</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>18483000</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>13830000</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>17239000</v>
       </c>
     </row>
-    <row r="59" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>21487000</v>
+      </c>
+      <c r="E59" s="3">
         <v>3256000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>3017000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>5114000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>23772000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>3843000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>4035000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>4163000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>24538000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>4186000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>3482000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>4435000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>5214000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>5325000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>4785000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>3672000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1601000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1633000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1165000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>948000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>684000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1217000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1102000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1203000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>2791000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>3640000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>3736000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>3614000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>2612000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>4161000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>3457000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>3263000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>3045000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>3338000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>2664000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>2822000</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>2615000</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>2755000</v>
       </c>
     </row>
-    <row r="60" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>72330000</v>
+      </c>
+      <c r="E60" s="3">
         <v>77850000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>68161000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>73829000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>70307000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>69993000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>70763000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>71921000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>65316000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>71186000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>61815000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>66666000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>69045000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>74057000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>80110000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>72059000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>56643000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>61856000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>62238000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>60150000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>56363000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>56468000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>57270000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>64773000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>63989000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>64195000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>70287000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>66632000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>57138000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>65288000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>62447000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>60306000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>57771000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>53777000</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>50949000</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>53374000</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>47638000</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>50021000</v>
       </c>
     </row>
-    <row r="61" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>39242000</v>
+      </c>
+      <c r="E61" s="3">
         <v>32824000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>33570000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>32823000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>41496000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>36918000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>36565000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>32213000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>41997000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>36510000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>37567000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>39150000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>40559000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>39246000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>39516000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>42651000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>43428000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>43639000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>45319000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>45137000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>47182000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>46888000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>46563000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>31857000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>26481000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>26089000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>19141000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>19177000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>20538000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>20624000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>20720000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>20781000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>24406000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>24869000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>24750000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>25124000</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>28932000</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>28916000</v>
       </c>
     </row>
-    <row r="62" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>21719000</v>
+      </c>
+      <c r="E62" s="3">
         <v>25107000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>26184000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>26344000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>22324000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>27647000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>26635000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>26151000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>21518000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>22944000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>23131000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>23763000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>56990000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>63806000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>63640000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>63535000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>63169000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>63687000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>64176000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>64382000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>65075000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>70075000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>70509000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>70431000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>73189000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>71968000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>72836000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>72359000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>69992000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>71885000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>72090000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>72828000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>72014000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>81583000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>81475000</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>81940000</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>79914000</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>83439000</v>
       </c>
     </row>
-    <row r="63" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6539,8 +6687,11 @@
       <c r="AN63" s="3">
         <v>0</v>
       </c>
+      <c r="AO63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -6655,8 +6806,11 @@
       <c r="AN64" s="3">
         <v>0</v>
       </c>
+      <c r="AO64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6771,124 +6925,130 @@
       <c r="AN65" s="3">
         <v>0</v>
       </c>
+      <c r="AO65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>182354000</v>
+      </c>
+      <c r="E66" s="3">
         <v>186117000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>177635000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>182102000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>182869000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>185516000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>184441000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>164866000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>163779000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>164726000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>156251000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>162957000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>174018000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>184052000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>190458000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>185556000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>170346000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>176099000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>178718000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>176796000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>175600000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>180643000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>181312000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>173725000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>170947000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>169446000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>169352000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>164967000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>154402000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>164263000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>161568000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>160631000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>161003000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>167151000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>163834000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>167058000</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>162989000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>168789000</v>
       </c>
     </row>
-    <row r="67" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6929,8 +7089,9 @@
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
+      <c r="AO67" s="3"/>
     </row>
-    <row r="68" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7045,8 +7206,11 @@
       <c r="AN68" s="3">
         <v>0</v>
       </c>
+      <c r="AO68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7161,8 +7325,11 @@
       <c r="AN69" s="3">
         <v>0</v>
       </c>
+      <c r="AO69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7277,8 +7444,11 @@
       <c r="AN70" s="3">
         <v>0</v>
       </c>
+      <c r="AO70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7393,124 +7563,130 @@
       <c r="AN71" s="3">
         <v>0</v>
       </c>
+      <c r="AO71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>482494000</v>
+      </c>
+      <c r="E72" s="3">
         <v>480367000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>477061000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>474290000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>470903000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>467664000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>463294000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>458339000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>453927000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>450138000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>444731000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>440552000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>432860000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>423877000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>407902000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>393779000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>392059000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>386952000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>383922000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>382953000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>383943000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>407728000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>412124000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>416919000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>421341000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>419367000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>419913000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>420498000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>421653000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>419155000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>416418000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>415970000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>414540000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>409449000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>408768000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>408707000</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>407831000</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>409284000</v>
       </c>
     </row>
-    <row r="73" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7625,8 +7801,11 @@
       <c r="AN73" s="3">
         <v>0</v>
       </c>
+      <c r="AO73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7741,8 +7920,11 @@
       <c r="AN74" s="3">
         <v>0</v>
       </c>
+      <c r="AO74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7857,124 +8039,130 @@
       <c r="AN75" s="3">
         <v>0</v>
       </c>
+      <c r="AO75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>259386000</v>
+      </c>
+      <c r="E76" s="3">
         <v>260561000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>262593000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>262720000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>263705000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>268592000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>268405000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>205250000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>204802000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>199703000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>199046000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>198685000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>195049000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>186100000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>177316000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>169215000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>168577000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>160589000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>158571000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>156974000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>157150000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>177400000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>180183000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>182079000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>191650000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>189915000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>191377000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>191222000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>191794000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>190365000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>187222000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>188195000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>187688000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>182276000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>179178000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>177151000</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>167325000</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>170597000</v>
       </c>
     </row>
-    <row r="77" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8089,245 +8277,254 @@
       <c r="AN77" s="3">
         <v>0</v>
       </c>
+      <c r="AO77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43830</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43738</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43646</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43555</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43465</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43373</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43281</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43190</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43008</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42916</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42825</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42735</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>6501000</v>
+      </c>
+      <c r="E81" s="3">
         <v>7548000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>7082000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>7713000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>7610000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>8610000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>9240000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>8220000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>7630000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>9070000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>7880000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>11430000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>12750000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>19660000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>17850000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>5480000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>8870000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>6750000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>4690000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>2730000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-20070000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-680000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-1080000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-610000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>5690000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>3170000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>3130000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>2350000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>6000000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>6240000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>3950000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>4650000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>8380000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>3970000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>3350000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>4010000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>1680000</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>2650000</v>
       </c>
     </row>
-    <row r="82" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8368,124 +8565,128 @@
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
+      <c r="AO82" s="3"/>
     </row>
-    <row r="83" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>6585000</v>
+      </c>
+      <c r="E83" s="3">
         <v>6258000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>5787000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>4812000</v>
       </c>
-      <c r="G83" s="3">
-        <v>4440000</v>
-      </c>
       <c r="H83" s="3">
+        <v>3740000</v>
+      </c>
+      <c r="I83" s="3">
         <v>4415000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>4242000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>4244000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>-3108000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>12289000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>4451000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>5908000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>5064000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>5642000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>4451000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>4283000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>5661000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>4990000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>4952000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>5004000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>30291000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>4983000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>4916000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>5819000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>4923000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>4873000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>4631000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>4571000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>5028000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>4658000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>4589000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>4470000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>5842000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>4880000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>4652000</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>4519000</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>8117000</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>4605000</v>
       </c>
     </row>
-    <row r="84" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8600,8 +8801,11 @@
       <c r="AN84" s="3">
         <v>0</v>
       </c>
+      <c r="AO84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8716,8 +8920,11 @@
       <c r="AN85" s="3">
         <v>0</v>
       </c>
+      <c r="AO85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8832,8 +9039,11 @@
       <c r="AN86" s="3">
         <v>0</v>
       </c>
+      <c r="AO86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8948,8 +9158,11 @@
       <c r="AN87" s="3">
         <v>0</v>
       </c>
+      <c r="AO87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9064,124 +9277,130 @@
       <c r="AN88" s="3">
         <v>0</v>
       </c>
+      <c r="AO88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>12679000</v>
+      </c>
+      <c r="E89" s="3">
         <v>14788000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>11550000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>12953000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>12229000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>17569000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>10560000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>14664000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>13682000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>15963000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>9383000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>16341000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>17621000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>24425000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>19963000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>14788000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>17124000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>12091000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>9650000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>9264000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>4005000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>4389000</v>
       </c>
-      <c r="Y89" s="3">
-        <v>0</v>
-      </c>
       <c r="Z89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA89" s="3">
         <v>6274000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>6352000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>9079000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>5947000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>8338000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>8607000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>11108000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>7780000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>8519000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>7411000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>7535000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>6947000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>8173000</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>7396000</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>5355000</v>
       </c>
     </row>
-    <row r="90" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9222,124 +9441,128 @@
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
+      <c r="AO90" s="3"/>
     </row>
-    <row r="91" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-7450000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-8727000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-6283000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-5898000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-6837000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-6160000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-6235000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-5074000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-6228000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-4920000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-5359000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-5412000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-5783000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-4876000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-3837000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-3911000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-4089000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-2840000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-2747000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-2400000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-3629000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-3291000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-4417000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-5945000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-6704000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-6285000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-6173000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-5199000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-6094000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-5204000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-4927000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-3349000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-4501000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-4913000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-3098000</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-2890000</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-3887000</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-3404000</v>
       </c>
     </row>
-    <row r="92" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9454,8 +9677,11 @@
       <c r="AN92" s="3">
         <v>0</v>
       </c>
+      <c r="AO92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9570,124 +9796,130 @@
       <c r="AN93" s="3">
         <v>0</v>
       </c>
+      <c r="AO93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-7133000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-8479000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-6180000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-4135000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-4252000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-6240000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-4869000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-4577000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-5714000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-4279000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-4356000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-4925000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-5355000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-2378000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-3064000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-3945000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-2110000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-3054000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-2716000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-2355000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-3302000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-3709000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-5081000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-6367000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-4264000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-6150000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-6877000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-5793000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-5584000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-3907000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-5096000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-1859000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-6536000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-2555000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-2878000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-3761000</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-1672000</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-3235000</v>
       </c>
     </row>
-    <row r="95" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9728,106 +9960,107 @@
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
+      <c r="AO95" s="3"/>
     </row>
-    <row r="96" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>4366000</v>
+      </c>
+      <c r="E96" s="3">
         <v>4242000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>4288000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>4335000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>4371000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>4240000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>4285000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>3808000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>3839000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>3663000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>3701000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>3738000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-3767000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-3685000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-3727000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-3760000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-3763000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-3720000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-3721000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-3720000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-3715000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-3716000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-3715000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-3719000</v>
-      </c>
-      <c r="AA96" s="3">
-        <v>-3716000</v>
       </c>
       <c r="AB96" s="3">
         <v>-3716000</v>
       </c>
       <c r="AC96" s="3">
+        <v>-3716000</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-3715000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-3505000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-3502000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-3503000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-3502000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-3291000</v>
-      </c>
-      <c r="AI96" s="3">
-        <v>-3289000</v>
       </c>
       <c r="AJ96" s="3">
         <v>-3289000</v>
@@ -9836,16 +10069,19 @@
         <v>-3289000</v>
       </c>
       <c r="AL96" s="3">
+        <v>-3289000</v>
+      </c>
+      <c r="AM96" s="3">
         <v>-3134000</v>
-      </c>
-      <c r="AM96" s="3">
-        <v>-3133000</v>
       </c>
       <c r="AN96" s="3">
         <v>-3133000</v>
       </c>
+      <c r="AO96" s="3">
+        <v>-3133000</v>
+      </c>
     </row>
-    <row r="97" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9960,8 +10196,11 @@
       <c r="AN97" s="3">
         <v>0</v>
       </c>
+      <c r="AO97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10076,8 +10315,11 @@
       <c r="AN98" s="3">
         <v>0</v>
       </c>
+      <c r="AO98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10192,352 +10434,364 @@
       <c r="AN99" s="3">
         <v>0</v>
       </c>
+      <c r="AO99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-8734000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-8083000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-8685000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-13579000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-11143000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-11106000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-12558000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-7982000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-9555000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-8059000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-8176000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-8507000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-13937000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-9793000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-8671000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-6713000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-12959000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-7657000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-7022000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-7785000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-5283000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-4494000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>6277000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>8785000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-4456000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-1666000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>548000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-1044000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-5501000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-4959000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-3244000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-5742000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-1837000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-4988000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-5059000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-3246000</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-6746000</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-1296000</v>
       </c>
     </row>
-    <row r="101" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-619000</v>
+      </c>
+      <c r="E101" s="3">
         <v>261000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>6000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-324000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>182000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-209000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>30000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>102000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>872000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-651000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-441000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>142000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>872000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-651000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-441000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>142000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-21000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-77000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>38000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>27000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>112000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>70000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-32000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-369000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>106000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-125000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>9000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>43000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-149000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-3000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-135000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>30000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-127000</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>232000</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>135000</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>74000</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>-414000</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>-89000</v>
       </c>
     </row>
-    <row r="102" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-3188000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1842000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-2801000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-4675000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-3785000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>484000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-6861000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>1781000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1405000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>3416000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-3119000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>3011000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-799000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>11603000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>7787000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>4272000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>2034000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>1303000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-50000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-849000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-4468000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-3744000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>1164000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>8323000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-2262000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>1138000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-373000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>1544000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-2627000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>2239000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-695000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>948000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-1089000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>224000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-855000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>1240000</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-1436000</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>735000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/XOM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/XOM_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="92">
   <si>
     <t>XOM</t>
   </si>
@@ -656,503 +656,515 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AO102"/>
+  <dimension ref="A5:AP102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="41" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="42" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43921</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43830</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43738</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43646</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43555</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43465</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43373</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43281</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43100</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43008</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42916</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42825</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42735</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>83161000</v>
+      </c>
+      <c r="E8" s="3">
         <v>80039000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>83331000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>79477000</v>
-      </c>
-      <c r="G8" s="3">
-        <v>81058000</v>
       </c>
       <c r="H8" s="3">
         <v>81058000</v>
       </c>
       <c r="I8" s="3">
+        <v>81058000</v>
+      </c>
+      <c r="J8" s="3">
         <v>87792000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>89986000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>80411000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>81098000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>89852000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>81532000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>84183000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>93164000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>106512000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>111265000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>87734000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>81305000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>71892000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>65943000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>57552000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>45738000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>45425000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>32277000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>55134000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>63024000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>63422000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>67491000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>61646000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>68253000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>74187000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>71456000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>65436000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>50832000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>59350000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>56026000</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>56474000</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>40396000</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>56767000</v>
       </c>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>62497000</v>
+      </c>
+      <c r="E9" s="3">
         <v>53015000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>58022000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>55429000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>56871000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>54064000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>61142000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>64003000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>56692000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>53558000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>61772000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>56458000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>55439000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>61126000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>71514000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>76299000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>62629000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>56272000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>48464000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>45800000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>40663000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>32041000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>31053000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>20964000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>40380000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>44254000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>44138000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>48464000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>43771000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>46957000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>50873000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>50245000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>44779000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>28979000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>45248000</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>43843000</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>43267000</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>21193000</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>41181000</v>
       </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>20664000</v>
+      </c>
+      <c r="E10" s="3">
         <v>27024000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>25309000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>24048000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>24187000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>26994000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>26650000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>25983000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>23719000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>27540000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>28080000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>25074000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>28744000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>32038000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>34998000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>34966000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>25105000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>25033000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>23428000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>20143000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>16889000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>13697000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>14372000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>11313000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>14754000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>18770000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>19284000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>19027000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>17875000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>21296000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>23314000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>21211000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>20657000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>21853000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>14102000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>12183000</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>13207000</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>19203000</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>15586000</v>
       </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1194,16 +1206,17 @@
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
+      <c r="AP11" s="3"/>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E12" s="3">
         <v>1228000</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>24</v>
@@ -1211,11 +1224,11 @@
       <c r="G12" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="H12" s="3">
+      <c r="H12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I12" s="3">
         <v>987000</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>24</v>
@@ -1223,11 +1236,11 @@
       <c r="K12" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="L12" s="3">
+      <c r="L12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M12" s="3">
         <v>879000</v>
-      </c>
-      <c r="M12" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="N12" s="3" t="s">
         <v>24</v>
@@ -1235,86 +1248,89 @@
       <c r="O12" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="P12" s="3">
+      <c r="P12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q12" s="3">
         <v>348000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>218000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>286000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>173000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>524000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>190000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>176000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>164000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>595000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>188000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>214000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>288000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>357000</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>299000</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>333000</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>280000</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>555000</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>292000</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>332000</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>287000</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>703000</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>284000</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>514000</v>
       </c>
-      <c r="AM12" s="3">
+      <c r="AN12" s="3">
         <v>289000</v>
       </c>
-      <c r="AN12" s="3">
+      <c r="AO12" s="3">
         <v>340000</v>
       </c>
-      <c r="AO12" s="3">
+      <c r="AP12" s="3">
         <v>327000</v>
       </c>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1432,28 +1448,31 @@
       <c r="AO13" s="3">
         <v>0</v>
       </c>
+      <c r="AP13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E14" s="3">
         <v>587000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>155000</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I14" s="3">
         <v>-615000</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>24</v>
@@ -1461,11 +1480,11 @@
       <c r="K14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M14" s="3">
         <v>2787000</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>24</v>
@@ -1473,8 +1492,8 @@
       <c r="O14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="P14" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
@@ -1483,10 +1502,10 @@
         <v>0</v>
       </c>
       <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
         <v>4600000</v>
-      </c>
-      <c r="T14" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="U14" s="3" t="s">
         <v>24</v>
@@ -1497,26 +1516,26 @@
       <c r="W14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="X14" s="3">
+      <c r="X14" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Y14" s="3">
         <v>24875000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>62000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>64000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>910000</v>
-      </c>
-      <c r="AB14" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AC14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AD14" s="3">
-        <v>0</v>
+      <c r="AD14" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="AE14" s="3">
         <v>0</v>
@@ -1551,127 +1570,133 @@
       <c r="AO14" s="3">
         <v>0</v>
       </c>
+      <c r="AP14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>6771000</v>
+      </c>
+      <c r="E15" s="3">
         <v>5975000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>6320000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>6101000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>5702000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>5977000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>6258000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>5787000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>4812000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>4440000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>4415000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>4242000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>4244000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>5064000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>5642000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>4451000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>4283000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>5661000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>4990000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>4952000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>5004000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>5416000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>4921000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>4852000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>4909000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>4923000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>4873000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>4631000</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>4571000</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>5028000</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>4658000</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>4589000</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>4470000</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>5842000</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>4880000</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>4652000</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>4519000</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>8117000</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AP15" s="3">
         <v>4605000</v>
       </c>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1710,246 +1735,253 @@
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
+      <c r="AP16" s="3"/>
     </row>
-    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>77876000</v>
+      </c>
+      <c r="E17" s="3">
         <v>72414000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>74117000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>70656000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>71325000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>72708000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>76783000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>79124000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>70493000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>70147000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>76892000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>71009000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>69602000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>74720000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>85513000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>89826000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>81528000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>73015000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>63966000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>61181000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>55297000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>72840000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>46292000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>33928000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>56167000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>60527000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>60061000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>64243000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>59155000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>63559000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>67325000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>66842000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>60767000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>48832000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>55406000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>53763000</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>52607000</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>42224000</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>55345000</v>
       </c>
     </row>
-    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>5285000</v>
+      </c>
+      <c r="E18" s="3">
         <v>7625000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>9214000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>8821000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>9733000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>8350000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>11009000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>10862000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>9918000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>10951000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>12960000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>10523000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>14581000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>18444000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>20999000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>21439000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>6206000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>8290000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>7926000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>4762000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>2255000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-27102000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-867000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-1651000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-1033000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>2497000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>3361000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>3248000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>2491000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>4694000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>6862000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>4614000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>4669000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>2000000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>3944000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>2263000</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>3867000</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>-1828000</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>1422000</v>
       </c>
     </row>
-    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1991,603 +2023,619 @@
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
+      <c r="AP19" s="3"/>
     </row>
-    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>-1977000</v>
+      </c>
+      <c r="E20" s="3">
         <v>56000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-1963000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-2029000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-2072000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>455000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-2224000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-3074000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-2672000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-1105000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-908000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-1382000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-2381000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>605000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>4632000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>3688000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>2538000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>3660000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>1894000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>1799000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>1595000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>802000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>774000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>328000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>1024000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>4149000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>1627000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>1600000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>1979000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>3642000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>2418000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>2045000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>2775000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>1203000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>1750000</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>2051000</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>2197000</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>2640000</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>1910000</v>
       </c>
     </row>
-    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>14033000</v>
+      </c>
+      <c r="E21" s="3">
         <v>13544000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>17497000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>16951000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>17507000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>13872000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>19491000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>19723000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>17402000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>16496000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>18283000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>16147000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>21206000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>24113000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>31273000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>29578000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>13027000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>17611000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>14810000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>11513000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>8854000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>3991000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>4890000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>3593000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>5810000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>11569000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>9861000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>9479000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>9041000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>13364000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>13938000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>11248000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>11914000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>9045000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>10574000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>8966000</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>10583000</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>8929000</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>7937000</v>
       </c>
     </row>
-    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>295000</v>
+      </c>
+      <c r="E22" s="3">
         <v>163000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>90000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>145000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>205000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>297000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>207000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>271000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>221000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>272000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>169000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>249000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>159000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>207000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>209000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>194000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>188000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>221000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>214000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>254000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>258000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>313000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>279000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>317000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>249000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>232000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>267000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>216000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>181000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>215000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>200000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>147000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>204000</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>186000</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>111000</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>158000</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>146000</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>195000</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>106000</v>
       </c>
     </row>
-    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>6967000</v>
+      </c>
+      <c r="E23" s="3">
         <v>8031000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>10932000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>10705000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>11600000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>9813000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>13026000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>13665000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>12369000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>10625000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>13699000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>11656000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>16803000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>18842000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>25422000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>24933000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>8556000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>11729000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>9606000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>6307000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>3592000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-26613000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-372000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-1640000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-258000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>6414000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>4721000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>4632000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>4289000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>8121000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>9080000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>6512000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>7240000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>3017000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>5583000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>4156000</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>5918000</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>617000</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>3226000</v>
       </c>
     </row>
-    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>2495000</v>
+      </c>
+      <c r="E24" s="3">
         <v>1422000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>3164000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>3351000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>3567000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1858000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>4055000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>4094000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>3803000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>2613000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>4353000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>3503000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>4960000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>5817000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>5224000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>6359000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>2806000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>2703000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>2664000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>1526000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>796000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-5985000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>337000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-471000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>512000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>1424000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>1474000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>1241000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>1883000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>1936000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>2634000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>2526000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>2457000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>550000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>1498000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>892000</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>1828000</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>-1407000</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>337000</v>
       </c>
     </row>
-    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2705,246 +2753,255 @@
       <c r="AO25" s="3">
         <v>0</v>
       </c>
+      <c r="AP25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>4472000</v>
+      </c>
+      <c r="E26" s="3">
         <v>6609000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>7768000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>7354000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>8033000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>7955000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>8971000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>9571000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>8566000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>8012000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>9346000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>8153000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>11843000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>13025000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>20198000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>18574000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>5750000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>9026000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>6942000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>4781000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>2796000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-20628000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-709000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-1169000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-770000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>4990000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>3247000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>3391000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>2406000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>6185000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>6446000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>3986000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>4783000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>2467000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>4085000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>3264000</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>4090000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>2024000</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>2889000</v>
       </c>
     </row>
-    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>4183000</v>
+      </c>
+      <c r="E27" s="3">
         <v>6501000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>7548000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>7082000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>7713000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>7610000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>8610000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>9240000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>8220000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>7630000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>9070000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>7880000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>11430000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>12720000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>19660000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>17850000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>5480000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>8817000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>6750000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>4690000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>2730000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-20095000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-680000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-1080000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-610000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>4950000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>3170000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>3130000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>2350000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>5979000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>6240000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>3950000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>4650000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>2438000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>3970000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>3350000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>4010000</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>1680000</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>2650000</v>
       </c>
     </row>
-    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -3062,8 +3119,11 @@
       <c r="AO28" s="3">
         <v>0</v>
       </c>
+      <c r="AP28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -3104,10 +3164,10 @@
         <v>0</v>
       </c>
       <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3">
         <v>30000</v>
-      </c>
-      <c r="Q29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="R29" s="3" t="s">
         <v>24</v>
@@ -3115,11 +3175,11 @@
       <c r="S29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="T29" s="3">
+      <c r="T29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="U29" s="3">
         <v>53000</v>
-      </c>
-      <c r="U29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="V29" s="3" t="s">
         <v>24</v>
@@ -3127,11 +3187,11 @@
       <c r="W29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="X29" s="3">
+      <c r="X29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Y29" s="3">
         <v>25000</v>
-      </c>
-      <c r="Y29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="Z29" s="3" t="s">
         <v>24</v>
@@ -3139,11 +3199,11 @@
       <c r="AA29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AB29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AC29" s="3">
         <v>740000</v>
-      </c>
-      <c r="AC29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>24</v>
@@ -3151,11 +3211,11 @@
       <c r="AE29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AF29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AG29" s="3">
         <v>21000</v>
-      </c>
-      <c r="AG29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AH29" s="3" t="s">
         <v>24</v>
@@ -3163,11 +3223,11 @@
       <c r="AI29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AJ29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AK29" s="3">
         <v>5942000</v>
-      </c>
-      <c r="AK29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AL29" s="3" t="s">
         <v>24</v>
@@ -3181,8 +3241,11 @@
       <c r="AO29" s="3" t="s">
         <v>24</v>
       </c>
+      <c r="AP29" s="3" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3300,8 +3363,11 @@
       <c r="AO30" s="3">
         <v>0</v>
       </c>
+      <c r="AP30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3419,246 +3485,255 @@
       <c r="AO31" s="3">
         <v>0</v>
       </c>
+      <c r="AP31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>1977000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-56000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>1963000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>2029000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>2072000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-455000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>2224000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>3074000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>2672000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>1105000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>908000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>1382000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>2381000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-605000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-4632000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-3688000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-2538000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-3660000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-1894000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-1799000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-1595000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-802000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-774000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-328000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-1024000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-4149000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-1627000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-1600000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-1979000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-3642000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-2418000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-2045000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-2775000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-1203000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-1750000</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-2051000</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-2197000</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-2640000</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>-1910000</v>
       </c>
     </row>
-    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>4183000</v>
+      </c>
+      <c r="E33" s="3">
         <v>6501000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>7548000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>7082000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>7713000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>7610000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>8610000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>9240000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>8220000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>7630000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>9070000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>7880000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>11430000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>12750000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>19660000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>17850000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>5480000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>8870000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>6750000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>4690000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>2730000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-20070000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-680000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-1080000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-610000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>5690000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>3170000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>3130000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>2350000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>6000000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>6240000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>3950000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>4650000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>8380000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>3970000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>3350000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>4010000</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>1680000</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>2650000</v>
       </c>
     </row>
-    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3776,251 +3851,260 @@
       <c r="AO34" s="3">
         <v>0</v>
       </c>
+      <c r="AP34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>4183000</v>
+      </c>
+      <c r="E35" s="3">
         <v>6501000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>7548000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>7082000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>7713000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>7610000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>8610000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>9240000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>8220000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>7630000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>9070000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>7880000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>11430000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>12750000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>19660000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>17850000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>5480000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>8870000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>6750000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>4690000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>2730000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-20070000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-680000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-1080000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-610000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>5690000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>3170000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>3130000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>2350000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>6000000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>6240000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>3950000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>4650000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>8380000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>3970000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>3350000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>4010000</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>1680000</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>2650000</v>
       </c>
     </row>
-    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43921</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43830</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43738</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43646</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43555</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43465</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43373</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43281</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43100</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43008</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42916</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42825</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42735</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4062,8 +4146,9 @@
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
+      <c r="AP39" s="3"/>
     </row>
-    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4105,127 +4190,131 @@
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
+      <c r="AP40" s="3"/>
     </row>
-    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>8435000</v>
+      </c>
+      <c r="E41" s="3">
         <v>10681000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>13814000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>14352000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>17036000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>23029000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>26926000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>26460000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>33320000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>31539000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>32944000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>29528000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>32651000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>29640000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>30407000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>18861000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>11074000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>6802000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>4768000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>3465000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>3515000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>4364000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>8832000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>12576000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>11412000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>3089000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>5351000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>4213000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>4586000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>3042000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>5669000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>3430000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>4125000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>3177000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>4266000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>4042000</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>4897000</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>3657000</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>5093000</v>
       </c>
     </row>
-    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4343,50 +4432,53 @@
       <c r="AO42" s="3">
         <v>0</v>
       </c>
+      <c r="AP42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>61783000</v>
+      </c>
+      <c r="E43" s="3">
         <v>44562000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>45285000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>41792000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>46303000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>43681000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>41505000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>43071000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>40366000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>38015000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>41814000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>35915000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>38808000</v>
       </c>
-      <c r="P43" s="3">
-        <v>0</v>
-      </c>
       <c r="Q43" s="3">
         <v>0</v>
       </c>
@@ -4394,671 +4486,689 @@
         <v>0</v>
       </c>
       <c r="S43" s="3">
+        <v>0</v>
+      </c>
+      <c r="T43" s="3">
         <v>42142000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>32383000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>29516000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>28540000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>24755000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>20581000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>19974000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>19036000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>20871000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>26966000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>25308000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>27132000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>27105000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>24701000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>27880000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>26993000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>24686000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>25597000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>23263000</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>21289000</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>21842000</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>21394000</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>20388000</v>
       </c>
     </row>
-    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>24975000</v>
+      </c>
+      <c r="E44" s="3">
         <v>26302000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>27238000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>25371000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>24478000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>23524000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>23875000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>24503000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>23491000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>25120000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>24450000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>24249000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>23642000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>24435000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>24096000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>23585000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>22177000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>18780000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>19607000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>19275000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>18357000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>18850000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>17885000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>19657000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>16501000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>18528000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>17590000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>18835000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>18332000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>18958000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>18761000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>18483000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>18048000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>16992000</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>16743000</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>15305000</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>14873000</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>15080000</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>15342000</v>
       </c>
     </row>
-    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>2594000</v>
+      </c>
+      <c r="E45" s="3">
         <v>1837000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>2113000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2234000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1940000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1598000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1997000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2176000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2171000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1906000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1905000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2039000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2098000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1807000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>2375000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>2654000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1862000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1189000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1664000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1562000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1568000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1098000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>2002000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1747000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1465000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1469000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1759000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1563000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>1553000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>1272000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>1665000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>1649000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>1456000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>1368000</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>1480000</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>1544000</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>1519000</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>1285000</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>2122000</v>
       </c>
     </row>
-    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>97787000</v>
+      </c>
+      <c r="E46" s="3">
         <v>83382000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>88505000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>85108000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>91233000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>91990000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>94349000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>96238000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>99377000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>96609000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>101142000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>91760000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>97224000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>97631000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>99289000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>93163000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>77255000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>59154000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>55555000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>52842000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>48195000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>44893000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>48693000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>53016000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>50249000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>50052000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>50008000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>51743000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>51576000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>47973000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>53975000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>50555000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>48315000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>47134000</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>45752000</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>42180000</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>43131000</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>41416000</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>42945000</v>
       </c>
     </row>
-    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>40396000</v>
+      </c>
+      <c r="E47" s="3">
         <v>32924000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>39102000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>39019000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>40356000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>34353000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>41447000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>40791000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>39995000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>34257000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>40062000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>39564000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>40825000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>49793000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>50235000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>46820000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>46329000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>45195000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>45641000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>44774000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>44181000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>43515000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>43609000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>43192000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>42981000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>43164000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>42920000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>42533000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>42068000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>40790000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>40427000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>39691000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>40350000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>39160000</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>37649000</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>37719000</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>38268000</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>35102000</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>35553000</v>
       </c>
     </row>
-    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>298781000</v>
+      </c>
+      <c r="E48" s="3">
         <v>306597000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>298388000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>295356000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>292646000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>301441000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>299543000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>298283000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>213723000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>221789000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>205862000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>206736000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>206023000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>204692000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>203102000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>209159000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>212773000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>216552000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>218795000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>223012000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>224641000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>227553000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>250496000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>250524000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>248409000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>259651000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>257065000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>257118000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>253003000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>247101000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>249153000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>248209000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>250352000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>252630000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>255556000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>252987000</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>253147000</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>244224000</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>251923000</v>
       </c>
     </row>
-    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -5176,8 +5286,11 @@
       <c r="AO49" s="3">
         <v>0</v>
       </c>
+      <c r="AP49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5295,8 +5408,11 @@
       <c r="AO50" s="3">
         <v>0</v>
       </c>
+      <c r="AP50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5414,127 +5530,133 @@
       <c r="AO51" s="3">
         <v>0</v>
       </c>
+      <c r="AP51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>27446000</v>
+      </c>
+      <c r="E52" s="3">
         <v>22318000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>28345000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>28114000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>27673000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>21755000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>26577000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>25395000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>24823000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>20025000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>25193000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>25188000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>25299000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>16951000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>17526000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>18632000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>18414000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>18022000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>16697000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>16661000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>16753000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>16789000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>15245000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>14763000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>14165000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>9730000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>9368000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>9335000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>9542000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>10332000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>11073000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>10335000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>9809000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>9767000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>10470000</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>10126000</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>9663000</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>9572000</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>8965000</v>
       </c>
     </row>
-    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5652,127 +5774,133 @@
       <c r="AO53" s="3">
         <v>0</v>
       </c>
+      <c r="AP53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>464410000</v>
+      </c>
+      <c r="E54" s="3">
         <v>448980000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>454340000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>447597000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>451908000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>453475000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>461916000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>460707000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>377918000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>376317000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>372259000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>363248000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>369371000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>369067000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>370152000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>367774000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>354771000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>338923000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>336688000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>337289000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>333770000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>332750000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>358043000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>361495000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>355804000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>362597000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>359361000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>360729000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>356189000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>346196000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>354628000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>348790000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>348826000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>348691000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>349427000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>343012000</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>344209000</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>330314000</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>339386000</v>
       </c>
     </row>
-    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5814,8 +5942,9 @@
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
+      <c r="AP55" s="3"/>
     </row>
-    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5857,722 +5986,741 @@
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
+      <c r="AP56" s="3"/>
     </row>
-    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>77088000</v>
+      </c>
+      <c r="E57" s="3">
         <v>36049000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>65382000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>59725000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>63987000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>36145000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>60518000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>60107000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>59531000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>31249000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>62257000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>54404000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>59935000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>63197000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>62550000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>67958000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>63501000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>50766000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>47257000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>45780000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>41017000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>35221000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>33340000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>33216000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>35815000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>40605000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>39336000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>40324000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>41190000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>37268000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>41714000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>38490000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>37207000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>36796000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>34698000</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>31100000</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>32069000</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>31193000</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>30027000</v>
       </c>
     </row>
-    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>14531000</v>
+      </c>
+      <c r="E58" s="3">
         <v>11245000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>9212000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>5419000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>4728000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>6813000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>5632000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>6621000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>8227000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>5712000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>4743000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>3929000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>2296000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>634000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>6182000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>7367000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>4886000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>4276000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>12966000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>15293000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>18185000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>20458000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>21911000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>22952000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>27755000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>20593000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>21219000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>26227000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>21828000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>17258000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>19413000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>20500000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>19836000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>17930000</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>15741000</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>17185000</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>18483000</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>13830000</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>17239000</v>
       </c>
     </row>
-    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2759000</v>
+      </c>
+      <c r="E59" s="3">
         <v>21487000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>3256000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>3017000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>5114000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>23772000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>3843000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>4035000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>4163000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>24538000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>4186000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>3482000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>4435000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>5214000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>5325000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>4785000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>3672000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1601000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1633000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1165000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>948000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>684000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1217000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1102000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1203000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>2791000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>3640000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>3736000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>3614000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>2612000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>4161000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>3457000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>3263000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>3045000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>3338000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>2664000</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>2822000</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>2615000</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>2755000</v>
       </c>
     </row>
-    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>94378000</v>
+      </c>
+      <c r="E60" s="3">
         <v>72330000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>77850000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>68161000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>73829000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>70307000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>69993000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>70763000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>71921000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>65316000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>71186000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>61815000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>66666000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>69045000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>74057000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>80110000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>72059000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>56643000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>61856000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>62238000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>60150000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>56363000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>56468000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>57270000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>64773000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>63989000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>64195000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>70287000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>66632000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>57138000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>65288000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>62447000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>60306000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>57771000</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>53777000</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>50949000</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>53374000</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>47638000</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>50021000</v>
       </c>
     </row>
-    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>33130000</v>
+      </c>
+      <c r="E61" s="3">
         <v>39242000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>32824000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>33570000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>32823000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>41496000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>36918000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>36565000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>32213000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>41997000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>36510000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>37567000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>39150000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>40559000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>39246000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>39516000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>42651000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>43428000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>43639000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>45319000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>45137000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>47182000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>46888000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>46563000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>31857000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>26481000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>26089000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>19141000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>19177000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>20538000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>20624000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>20720000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>20781000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>24406000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>24869000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>24750000</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>25124000</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>28932000</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>28916000</v>
       </c>
     </row>
-    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>26948000</v>
+      </c>
+      <c r="E62" s="3">
         <v>21719000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>25107000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>26184000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>26344000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>22324000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>27647000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>26635000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>26151000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>21518000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>22944000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>23131000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>23763000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>56990000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>63806000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>63640000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>63535000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>63169000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>63687000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>64176000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>64382000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>65075000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>70075000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>70509000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>70431000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>73189000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>71968000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>72836000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>72359000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>69992000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>71885000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>72090000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>72828000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>72014000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>81583000</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>81475000</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>81940000</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>79914000</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>83439000</v>
       </c>
     </row>
-    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6690,8 +6838,11 @@
       <c r="AO63" s="3">
         <v>0</v>
       </c>
+      <c r="AP63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -6809,8 +6960,11 @@
       <c r="AO64" s="3">
         <v>0</v>
       </c>
+      <c r="AP64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6928,127 +7082,133 @@
       <c r="AO65" s="3">
         <v>0</v>
       </c>
+      <c r="AP65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>203414000</v>
+      </c>
+      <c r="E66" s="3">
         <v>182354000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>186117000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>177635000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>182102000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>182869000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>185516000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>184441000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>164866000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>163779000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>164726000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>156251000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>162957000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>174018000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>184052000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>190458000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>185556000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>170346000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>176099000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>178718000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>176796000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>175600000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>180643000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>181312000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>173725000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>170947000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>169446000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>169352000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>164967000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>154402000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>164263000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>161568000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>160631000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>161003000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>167151000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>163834000</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>167058000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>162989000</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>168789000</v>
       </c>
     </row>
-    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7090,8 +7250,9 @@
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
+      <c r="AP67" s="3"/>
     </row>
-    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7209,8 +7370,11 @@
       <c r="AO68" s="3">
         <v>0</v>
       </c>
+      <c r="AP68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7328,8 +7492,11 @@
       <c r="AO69" s="3">
         <v>0</v>
       </c>
+      <c r="AP69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7447,8 +7614,11 @@
       <c r="AO70" s="3">
         <v>0</v>
       </c>
+      <c r="AP70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7566,127 +7736,133 @@
       <c r="AO71" s="3">
         <v>0</v>
       </c>
+      <c r="AP71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>482344000</v>
+      </c>
+      <c r="E72" s="3">
         <v>482494000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>480367000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>477061000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>474290000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>470903000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>467664000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>463294000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>458339000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>453927000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>450138000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>444731000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>440552000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>432860000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>423877000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>407902000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>393779000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>392059000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>386952000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>383922000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>382953000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>383943000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>407728000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>412124000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>416919000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>421341000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>419367000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>419913000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>420498000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>421653000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>419155000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>416418000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>415970000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>414540000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>409449000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>408768000</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>408707000</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>407831000</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>409284000</v>
       </c>
     </row>
-    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7804,8 +7980,11 @@
       <c r="AO73" s="3">
         <v>0</v>
       </c>
+      <c r="AP73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7923,8 +8102,11 @@
       <c r="AO74" s="3">
         <v>0</v>
       </c>
+      <c r="AP74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8042,127 +8224,133 @@
       <c r="AO75" s="3">
         <v>0</v>
       </c>
+      <c r="AP75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>254381000</v>
+      </c>
+      <c r="E76" s="3">
         <v>259386000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>260561000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>262593000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>262720000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>263705000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>268592000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>268405000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>205250000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>204802000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>199703000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>199046000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>198685000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>195049000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>186100000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>177316000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>169215000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>168577000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>160589000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>158571000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>156974000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>157150000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>177400000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>180183000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>182079000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>191650000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>189915000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>191377000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>191222000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>191794000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>190365000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>187222000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>188195000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>187688000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>182276000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>179178000</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>177151000</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>167325000</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>170597000</v>
       </c>
     </row>
-    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8280,251 +8468,260 @@
       <c r="AO77" s="3">
         <v>0</v>
       </c>
+      <c r="AP77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43921</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43830</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43738</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43646</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43555</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43465</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43373</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43281</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43100</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43008</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42916</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42825</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42735</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>4183000</v>
+      </c>
+      <c r="E81" s="3">
         <v>6501000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>7548000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>7082000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>7713000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>7610000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>8610000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>9240000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>8220000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>7630000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>9070000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>7880000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>11430000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>12750000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>19660000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>17850000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>5480000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>8870000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>6750000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>4690000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>2730000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-20070000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-680000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-1080000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-610000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>5690000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>3170000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>3130000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>2350000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>6000000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>6240000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>3950000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>4650000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>8380000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>3970000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>3350000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>4010000</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>1680000</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>2650000</v>
       </c>
     </row>
-    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8566,127 +8763,131 @@
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
+      <c r="AP82" s="3"/>
     </row>
-    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>5702000</v>
+      </c>
+      <c r="E83" s="3">
         <v>6585000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>6258000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>5787000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>4812000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>3740000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>4415000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>4242000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>4244000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>-3108000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>12289000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>4451000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>5908000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>5064000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>5642000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>4451000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>4283000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>5661000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>4990000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>4952000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>5004000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>30291000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>4983000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>4916000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>5819000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>4923000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>4873000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>4631000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>4571000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>5028000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>4658000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>4589000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>4470000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>5842000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>4880000</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>4652000</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>4519000</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>8117000</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>4605000</v>
       </c>
     </row>
-    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8804,8 +9005,11 @@
       <c r="AO84" s="3">
         <v>0</v>
       </c>
+      <c r="AP84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8923,8 +9127,11 @@
       <c r="AO85" s="3">
         <v>0</v>
       </c>
+      <c r="AP85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9042,8 +9249,11 @@
       <c r="AO86" s="3">
         <v>0</v>
       </c>
+      <c r="AP86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9161,8 +9371,11 @@
       <c r="AO87" s="3">
         <v>0</v>
       </c>
+      <c r="AP87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9280,127 +9493,133 @@
       <c r="AO88" s="3">
         <v>0</v>
       </c>
+      <c r="AP88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>8705000</v>
+      </c>
+      <c r="E89" s="3">
         <v>12679000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>14788000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>11550000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>12953000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>12229000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>17569000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>10560000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>14664000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>13682000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>15963000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>9383000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>16341000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>17621000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>24425000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>19963000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>14788000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>17124000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>12091000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>9650000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>9264000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>4005000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>4389000</v>
       </c>
-      <c r="Z89" s="3">
-        <v>0</v>
-      </c>
       <c r="AA89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB89" s="3">
         <v>6274000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>6352000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>9079000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>5947000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>8338000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>8607000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>11108000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>7780000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>8519000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>7411000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>7535000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>6947000</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>8173000</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>7396000</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>5355000</v>
       </c>
     </row>
-    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9442,127 +9661,131 @@
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
+      <c r="AP90" s="3"/>
     </row>
-    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-6470000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-7450000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-8727000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-6283000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-5898000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-6837000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-6160000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-6235000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-5074000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-6228000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-4920000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-5359000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-5412000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-5783000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-4876000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-3837000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-3911000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-4089000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-2840000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-2747000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-2400000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-3629000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-3291000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-4417000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-5945000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-6704000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-6285000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-6173000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-5199000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-6094000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-5204000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-4927000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-3349000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-4501000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-4913000</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-3098000</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-2890000</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-3887000</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-3404000</v>
       </c>
     </row>
-    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9680,8 +9903,11 @@
       <c r="AO92" s="3">
         <v>0</v>
       </c>
+      <c r="AP92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9799,127 +10025,133 @@
       <c r="AO93" s="3">
         <v>0</v>
       </c>
+      <c r="AP93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-6006000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-7133000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-8479000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-6180000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-4135000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-4252000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-6240000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-4869000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-4577000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-5714000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-4279000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-4356000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-4925000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-5355000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-2378000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-3064000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-3945000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-2110000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-3054000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-2716000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-2355000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-3302000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-3709000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-5081000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-6367000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-4264000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-6150000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-6877000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-5793000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-5584000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-3907000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-5096000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-1859000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-6536000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-2555000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-2878000</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-3761000</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-1672000</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-3235000</v>
       </c>
     </row>
-    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9961,109 +10193,110 @@
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
+      <c r="AP95" s="3"/>
     </row>
-    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>4334000</v>
+      </c>
+      <c r="E96" s="3">
         <v>4366000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>4242000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>4288000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>4335000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>4371000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>4240000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>4285000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>3808000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>3839000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>3663000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>3701000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>3738000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-3767000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-3685000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-3727000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-3760000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-3763000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-3720000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-3721000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-3720000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-3715000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-3716000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-3715000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-3719000</v>
-      </c>
-      <c r="AB96" s="3">
-        <v>-3716000</v>
       </c>
       <c r="AC96" s="3">
         <v>-3716000</v>
       </c>
       <c r="AD96" s="3">
+        <v>-3716000</v>
+      </c>
+      <c r="AE96" s="3">
         <v>-3715000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-3505000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-3502000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-3503000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-3502000</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-3291000</v>
-      </c>
-      <c r="AJ96" s="3">
-        <v>-3289000</v>
       </c>
       <c r="AK96" s="3">
         <v>-3289000</v>
@@ -10072,16 +10305,19 @@
         <v>-3289000</v>
       </c>
       <c r="AM96" s="3">
+        <v>-3289000</v>
+      </c>
+      <c r="AN96" s="3">
         <v>-3134000</v>
-      </c>
-      <c r="AN96" s="3">
-        <v>-3133000</v>
       </c>
       <c r="AO96" s="3">
         <v>-3133000</v>
       </c>
+      <c r="AP96" s="3">
+        <v>-3133000</v>
+      </c>
     </row>
-    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10199,8 +10435,11 @@
       <c r="AO97" s="3">
         <v>0</v>
       </c>
+      <c r="AP97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10318,8 +10557,11 @@
       <c r="AO98" s="3">
         <v>0</v>
       </c>
+      <c r="AP98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10437,361 +10679,373 @@
       <c r="AO99" s="3">
         <v>0</v>
       </c>
+      <c r="AP99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-4900000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-8734000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-8083000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-8685000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-13579000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-11143000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-11106000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-12558000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-7982000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-9555000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-8059000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-8176000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-8507000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-13937000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-9793000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-8671000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-6713000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-12959000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-7657000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-7022000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-7785000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-5283000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-4494000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>6277000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>8785000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-4456000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-1666000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>548000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-1044000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-5501000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-4959000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-3244000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-5742000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-1837000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-4988000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-5059000</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-3246000</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-6746000</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-1296000</v>
       </c>
     </row>
-    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>86000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-619000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>261000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>6000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-324000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>182000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-209000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>30000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>102000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>872000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-651000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-441000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>142000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>872000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-651000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-441000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>142000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-21000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-77000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>38000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>27000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>112000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>70000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-32000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-369000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>106000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-125000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>9000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>43000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-149000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-3000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-135000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>30000</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-127000</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>232000</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>135000</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>74000</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>-414000</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>-89000</v>
       </c>
     </row>
-    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-2246000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-3188000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1842000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-2801000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-4675000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-3785000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>484000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-6861000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1781000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1405000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>3416000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-3119000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>3011000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-799000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>11603000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>7787000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>4272000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>2034000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>1303000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-50000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-849000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-4468000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-3744000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>1164000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>8323000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-2262000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>1138000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-373000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>1544000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-2627000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>2239000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-695000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>948000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-1089000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>224000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-855000</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>1240000</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-1436000</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>735000</v>
       </c>
     </row>
